--- a/data/out/test2/001317375_Python版_1pt.xlsx
+++ b/data/out/test2/001317375_Python版_1pt.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet'!$A$1:$DY$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet'!$A$1:$DZ$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -163,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -176,6 +176,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -183,15 +184,13 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -201,33 +200,37 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -616,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:DX45"/>
+  <dimension ref="B2:DY45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="1.625" defaultRowHeight="18.25" customHeight="1"/>
   <sheetData>
     <row r="2">
@@ -690,9 +693,10 @@
       <c r="AV3" s="4"/>
       <c r="AW3" s="4"/>
       <c r="AX3" s="5"/>
+      <c r="AY3" s="6"/>
     </row>
     <row r="4">
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>業務名</t>
         </is>
@@ -706,7 +710,7 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>○○管内交通量検討業務</t>
         </is>
@@ -715,7 +719,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>10,800,000円（消費税込み）</t>
         </is>
@@ -733,8 +737,8 @@
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
       <c r="AD4" s="5"/>
-      <c r="AE4" s="8"/>
-      <c r="AF4" s="7" t="inlineStr">
+      <c r="AE4" s="9"/>
+      <c r="AF4" s="8" t="inlineStr">
         <is>
           <t>管理技術者</t>
         </is>
@@ -745,7 +749,7 @@
       <c r="AJ4" s="4"/>
       <c r="AK4" s="4"/>
       <c r="AL4" s="5"/>
-      <c r="AM4" s="6" t="inlineStr">
+      <c r="AM4" s="7" t="inlineStr">
         <is>
           <t>○○○○</t>
         </is>
@@ -761,31 +765,78 @@
       <c r="AV4" s="4"/>
       <c r="AW4" s="4"/>
       <c r="AX4" s="5"/>
+      <c r="AY4" s="6"/>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>工期（自）</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="8" t="inlineStr">
         <is>
           <t>H31.1.10</t>
         </is>
       </c>
-      <c r="AE5" s="9" t="inlineStr">
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="10" t="inlineStr">
         <is>
           <t>担当技術者（副）</t>
         </is>
       </c>
-      <c r="AM5" s="9" t="inlineStr">
+      <c r="AF5" s="4"/>
+      <c r="AG5" s="4"/>
+      <c r="AH5" s="4"/>
+      <c r="AI5" s="4"/>
+      <c r="AJ5" s="4"/>
+      <c r="AK5" s="4"/>
+      <c r="AL5" s="5"/>
+      <c r="AM5" s="10" t="inlineStr">
         <is>
           <t>□□□□</t>
         </is>
       </c>
+      <c r="AN5" s="4"/>
+      <c r="AO5" s="4"/>
+      <c r="AP5" s="4"/>
+      <c r="AQ5" s="4"/>
+      <c r="AR5" s="4"/>
+      <c r="AS5" s="4"/>
+      <c r="AT5" s="4"/>
+      <c r="AU5" s="4"/>
+      <c r="AV5" s="4"/>
+      <c r="AW5" s="4"/>
+      <c r="AX5" s="5"/>
+      <c r="AY5" s="6"/>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>工期（至）</t>
         </is>
@@ -806,7 +857,7 @@
       </c>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="O6" s="8" t="inlineStr">
         <is>
           <t>R1.12.20</t>
         </is>
@@ -816,6 +867,37 @@
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="5"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="11"/>
+      <c r="AB6" s="11"/>
+      <c r="AC6" s="11"/>
+      <c r="AD6" s="11"/>
+      <c r="AE6" s="6"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="6"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="6"/>
     </row>
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
@@ -832,7 +914,7 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
+      <c r="L7" s="9"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
@@ -841,7 +923,7 @@
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
+      <c r="U7" s="9"/>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
@@ -949,66 +1031,67 @@
       <c r="DV7" s="4"/>
       <c r="DW7" s="4"/>
       <c r="DX7" s="5"/>
+      <c r="DY7" s="12"/>
     </row>
     <row r="8">
-      <c r="B8" s="11"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="12"/>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="11"/>
+      <c r="AA8" s="11"/>
+      <c r="AB8" s="11"/>
+      <c r="AC8" s="11"/>
       <c r="AD8" s="13"/>
-      <c r="AE8" s="11"/>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="13"/>
-      <c r="AI8" s="11"/>
-      <c r="AJ8" s="12"/>
-      <c r="AK8" s="12"/>
+      <c r="AE8" s="6"/>
+      <c r="AF8" s="11"/>
+      <c r="AG8" s="11"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="6"/>
+      <c r="AJ8" s="11"/>
+      <c r="AK8" s="11"/>
       <c r="AL8" s="13"/>
-      <c r="AM8" s="14" t="inlineStr">
+      <c r="AM8" s="15" t="inlineStr">
         <is>
           <t>着手日</t>
         </is>
       </c>
-      <c r="AN8" s="12"/>
-      <c r="AO8" s="12"/>
-      <c r="AP8" s="13"/>
-      <c r="AQ8" s="14" t="inlineStr">
+      <c r="AN8" s="11"/>
+      <c r="AO8" s="11"/>
+      <c r="AP8" s="14"/>
+      <c r="AQ8" s="15" t="inlineStr">
         <is>
           <t>完了日</t>
         </is>
       </c>
-      <c r="AR8" s="12"/>
-      <c r="AS8" s="12"/>
+      <c r="AR8" s="11"/>
+      <c r="AS8" s="11"/>
       <c r="AT8" s="13"/>
-      <c r="AU8" s="11"/>
-      <c r="AV8" s="12"/>
-      <c r="AW8" s="12"/>
+      <c r="AU8" s="6"/>
+      <c r="AV8" s="11"/>
+      <c r="AW8" s="11"/>
       <c r="AX8" s="13"/>
-      <c r="AY8" s="8"/>
+      <c r="AY8" s="9"/>
       <c r="AZ8" s="4"/>
       <c r="BA8" s="4"/>
       <c r="BB8" s="4"/>
@@ -1046,7 +1129,7 @@
       <c r="CH8" s="4"/>
       <c r="CI8" s="4"/>
       <c r="CJ8" s="4"/>
-      <c r="CK8" s="7" t="inlineStr">
+      <c r="CK8" s="8" t="inlineStr">
         <is>
           <t>2019年</t>
         </is>
@@ -1090,80 +1173,81 @@
       <c r="DV8" s="4"/>
       <c r="DW8" s="4"/>
       <c r="DX8" s="5"/>
+      <c r="DY8" s="12"/>
     </row>
     <row r="9">
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="B9" s="16"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="18" t="inlineStr">
         <is>
           <t>作業項目</t>
         </is>
       </c>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="18"/>
-      <c r="AE9" s="15"/>
-      <c r="AF9" s="17" t="inlineStr">
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+      <c r="AC9" s="17"/>
+      <c r="AD9" s="19"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="18" t="inlineStr">
         <is>
           <t>実施状況</t>
         </is>
       </c>
-      <c r="AG9" s="16"/>
-      <c r="AH9" s="18"/>
-      <c r="AI9" s="15"/>
-      <c r="AJ9" s="17" t="inlineStr">
+      <c r="AG9" s="17"/>
+      <c r="AH9" s="20"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="18" t="inlineStr">
         <is>
           <t>区分上段：計画下段：実績</t>
         </is>
       </c>
-      <c r="AK9" s="16"/>
-      <c r="AL9" s="18"/>
-      <c r="AM9" s="15"/>
-      <c r="AN9" s="16"/>
-      <c r="AO9" s="16"/>
-      <c r="AP9" s="18"/>
-      <c r="AQ9" s="19" t="inlineStr">
+      <c r="AK9" s="17"/>
+      <c r="AL9" s="19"/>
+      <c r="AM9" s="16"/>
+      <c r="AN9" s="17"/>
+      <c r="AO9" s="17"/>
+      <c r="AP9" s="20"/>
+      <c r="AQ9" s="21" t="inlineStr">
         <is>
           <t>上段：計画下段：実績</t>
         </is>
       </c>
-      <c r="AR9" s="16"/>
-      <c r="AS9" s="16"/>
-      <c r="AT9" s="18"/>
-      <c r="AU9" s="19" t="inlineStr">
+      <c r="AR9" s="17"/>
+      <c r="AS9" s="17"/>
+      <c r="AT9" s="19"/>
+      <c r="AU9" s="21" t="inlineStr">
         <is>
           <t>期間（日）</t>
         </is>
       </c>
-      <c r="AV9" s="16"/>
-      <c r="AW9" s="16"/>
-      <c r="AX9" s="18"/>
-      <c r="AY9" s="8"/>
+      <c r="AV9" s="17"/>
+      <c r="AW9" s="17"/>
+      <c r="AX9" s="19"/>
+      <c r="AY9" s="9"/>
       <c r="AZ9" s="4"/>
-      <c r="BA9" s="7" t="inlineStr">
+      <c r="BA9" s="8" t="inlineStr">
         <is>
           <t>1月</t>
         </is>
@@ -1171,10 +1255,10 @@
       <c r="BB9" s="4"/>
       <c r="BC9" s="4"/>
       <c r="BD9" s="5"/>
-      <c r="BE9" s="8"/>
+      <c r="BE9" s="9"/>
       <c r="BF9" s="4"/>
       <c r="BG9" s="4"/>
-      <c r="BH9" s="7" t="inlineStr">
+      <c r="BH9" s="8" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
@@ -1182,20 +1266,20 @@
       <c r="BI9" s="4"/>
       <c r="BJ9" s="4"/>
       <c r="BK9" s="5"/>
-      <c r="BL9" s="8"/>
+      <c r="BL9" s="9"/>
       <c r="BM9" s="4"/>
       <c r="BN9" s="4"/>
-      <c r="BO9" s="7" t="inlineStr">
+      <c r="BO9" s="8" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
       <c r="BP9" s="4"/>
       <c r="BQ9" s="5"/>
-      <c r="BR9" s="8"/>
-      <c r="BS9" s="4"/>
+      <c r="BR9" s="9"/>
+      <c r="BS9" s="9"/>
       <c r="BT9" s="4"/>
-      <c r="BU9" s="7" t="inlineStr">
+      <c r="BU9" s="8" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
@@ -1203,20 +1287,20 @@
       <c r="BV9" s="4"/>
       <c r="BW9" s="4"/>
       <c r="BX9" s="5"/>
-      <c r="BY9" s="8"/>
+      <c r="BY9" s="9"/>
       <c r="BZ9" s="4"/>
       <c r="CA9" s="4"/>
-      <c r="CB9" s="7" t="inlineStr">
+      <c r="CB9" s="8" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
       <c r="CC9" s="4"/>
       <c r="CD9" s="5"/>
-      <c r="CE9" s="8"/>
-      <c r="CF9" s="4"/>
+      <c r="CE9" s="9"/>
+      <c r="CF9" s="9"/>
       <c r="CG9" s="4"/>
-      <c r="CH9" s="7" t="inlineStr">
+      <c r="CH9" s="8" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
@@ -1224,10 +1308,10 @@
       <c r="CI9" s="4"/>
       <c r="CJ9" s="4"/>
       <c r="CK9" s="4"/>
-      <c r="CL9" s="5"/>
-      <c r="CM9" s="8"/>
+      <c r="CL9" s="22"/>
+      <c r="CM9" s="9"/>
       <c r="CN9" s="4"/>
-      <c r="CO9" s="7" t="inlineStr">
+      <c r="CO9" s="8" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
@@ -1235,20 +1319,20 @@
       <c r="CP9" s="4"/>
       <c r="CQ9" s="4"/>
       <c r="CR9" s="5"/>
-      <c r="CS9" s="8"/>
+      <c r="CS9" s="9"/>
       <c r="CT9" s="4"/>
       <c r="CU9" s="4"/>
-      <c r="CV9" s="7" t="inlineStr">
+      <c r="CV9" s="8" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
       <c r="CW9" s="4"/>
       <c r="CX9" s="4"/>
-      <c r="CY9" s="5"/>
-      <c r="CZ9" s="8"/>
+      <c r="CY9" s="22"/>
+      <c r="CZ9" s="9"/>
       <c r="DA9" s="4"/>
-      <c r="DB9" s="7" t="inlineStr">
+      <c r="DB9" s="8" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
@@ -1256,10 +1340,10 @@
       <c r="DC9" s="4"/>
       <c r="DD9" s="4"/>
       <c r="DE9" s="5"/>
-      <c r="DF9" s="8"/>
+      <c r="DF9" s="9"/>
       <c r="DG9" s="4"/>
       <c r="DH9" s="4"/>
-      <c r="DI9" s="7" t="inlineStr">
+      <c r="DI9" s="8" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
@@ -1267,9 +1351,9 @@
       <c r="DJ9" s="4"/>
       <c r="DK9" s="4"/>
       <c r="DL9" s="5"/>
-      <c r="DM9" s="8"/>
+      <c r="DM9" s="9"/>
       <c r="DN9" s="4"/>
-      <c r="DO9" s="7" t="inlineStr">
+      <c r="DO9" s="8" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
@@ -1277,9 +1361,9 @@
       <c r="DP9" s="4"/>
       <c r="DQ9" s="4"/>
       <c r="DR9" s="5"/>
-      <c r="DS9" s="8"/>
+      <c r="DS9" s="9"/>
       <c r="DT9" s="4"/>
-      <c r="DU9" s="7" t="inlineStr">
+      <c r="DU9" s="8" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
@@ -1287,311 +1371,314 @@
       <c r="DV9" s="4"/>
       <c r="DW9" s="4"/>
       <c r="DX9" s="5"/>
+      <c r="DY9" s="12"/>
     </row>
     <row r="10">
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="12"/>
-      <c r="AA10" s="12"/>
-      <c r="AB10" s="12"/>
-      <c r="AC10" s="12"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
+      <c r="AA10" s="11"/>
+      <c r="AB10" s="11"/>
+      <c r="AC10" s="11"/>
       <c r="AD10" s="13"/>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="12"/>
-      <c r="AG10" s="12"/>
-      <c r="AH10" s="13"/>
-      <c r="AI10" s="11"/>
-      <c r="AJ10" s="12"/>
-      <c r="AK10" s="12"/>
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="11"/>
+      <c r="AG10" s="11"/>
+      <c r="AH10" s="14"/>
+      <c r="AI10" s="6"/>
+      <c r="AJ10" s="11"/>
+      <c r="AK10" s="11"/>
       <c r="AL10" s="13"/>
-      <c r="AM10" s="11"/>
-      <c r="AN10" s="12"/>
-      <c r="AO10" s="12"/>
-      <c r="AP10" s="13"/>
-      <c r="AQ10" s="11"/>
-      <c r="AR10" s="12"/>
-      <c r="AS10" s="12"/>
+      <c r="AM10" s="6"/>
+      <c r="AN10" s="11"/>
+      <c r="AO10" s="11"/>
+      <c r="AP10" s="14"/>
+      <c r="AQ10" s="6"/>
+      <c r="AR10" s="11"/>
+      <c r="AS10" s="11"/>
       <c r="AT10" s="13"/>
-      <c r="AU10" s="11"/>
-      <c r="AV10" s="12"/>
-      <c r="AW10" s="12"/>
+      <c r="AU10" s="6"/>
+      <c r="AV10" s="11"/>
+      <c r="AW10" s="11"/>
       <c r="AX10" s="13"/>
-      <c r="AY10" s="11"/>
+      <c r="AY10" s="6"/>
       <c r="AZ10" s="13"/>
-      <c r="BA10" s="11"/>
-      <c r="BB10" s="12"/>
-      <c r="BC10" s="12"/>
-      <c r="BD10" s="12"/>
-      <c r="BE10" s="12"/>
-      <c r="BF10" s="12"/>
-      <c r="BG10" s="12"/>
-      <c r="BH10" s="12"/>
+      <c r="BA10" s="6"/>
+      <c r="BB10" s="11"/>
+      <c r="BC10" s="11"/>
+      <c r="BD10" s="11"/>
+      <c r="BE10" s="6"/>
+      <c r="BF10" s="11"/>
+      <c r="BG10" s="11"/>
+      <c r="BH10" s="11"/>
       <c r="BI10" s="13"/>
-      <c r="BJ10" s="11"/>
+      <c r="BJ10" s="6"/>
       <c r="BK10" s="13"/>
-      <c r="BL10" s="11"/>
+      <c r="BL10" s="6"/>
       <c r="BM10" s="13"/>
-      <c r="BN10" s="11"/>
+      <c r="BN10" s="6"/>
       <c r="BO10" s="13"/>
-      <c r="BP10" s="11"/>
+      <c r="BP10" s="6"/>
       <c r="BQ10" s="13"/>
-      <c r="BR10" s="11"/>
-      <c r="BS10" s="12"/>
+      <c r="BR10" s="6"/>
+      <c r="BS10" s="6"/>
       <c r="BT10" s="13"/>
-      <c r="BU10" s="11"/>
+      <c r="BU10" s="6"/>
       <c r="BV10" s="13"/>
-      <c r="BW10" s="11"/>
+      <c r="BW10" s="6"/>
       <c r="BX10" s="13"/>
-      <c r="BY10" s="11"/>
+      <c r="BY10" s="6"/>
       <c r="BZ10" s="13"/>
-      <c r="CA10" s="11"/>
-      <c r="CB10" s="12"/>
-      <c r="CC10" s="13"/>
-      <c r="CD10" s="20"/>
-      <c r="CE10" s="11"/>
-      <c r="CF10" s="12"/>
+      <c r="CA10" s="6"/>
+      <c r="CB10" s="11"/>
+      <c r="CC10" s="14"/>
+      <c r="CD10" s="14"/>
+      <c r="CE10" s="6"/>
+      <c r="CF10" s="6"/>
       <c r="CG10" s="13"/>
-      <c r="CH10" s="11"/>
+      <c r="CH10" s="6"/>
       <c r="CI10" s="13"/>
-      <c r="CJ10" s="11"/>
-      <c r="CK10" s="12"/>
-      <c r="CL10" s="13"/>
-      <c r="CM10" s="11"/>
-      <c r="CN10" s="13"/>
-      <c r="CO10" s="11"/>
+      <c r="CJ10" s="6"/>
+      <c r="CK10" s="11"/>
+      <c r="CL10" s="14"/>
+      <c r="CM10" s="6"/>
+      <c r="CN10" s="14"/>
+      <c r="CO10" s="6"/>
       <c r="CP10" s="13"/>
-      <c r="CQ10" s="11"/>
+      <c r="CQ10" s="6"/>
       <c r="CR10" s="13"/>
-      <c r="CS10" s="11"/>
+      <c r="CS10" s="6"/>
       <c r="CT10" s="13"/>
-      <c r="CU10" s="11"/>
-      <c r="CV10" s="12"/>
-      <c r="CW10" s="12"/>
-      <c r="CX10" s="12"/>
-      <c r="CY10" s="12"/>
-      <c r="CZ10" s="12"/>
-      <c r="DA10" s="12"/>
-      <c r="DB10" s="12"/>
+      <c r="CU10" s="6"/>
+      <c r="CV10" s="11"/>
+      <c r="CW10" s="11"/>
+      <c r="CX10" s="11"/>
+      <c r="CY10" s="6"/>
+      <c r="CZ10" s="6"/>
+      <c r="DA10" s="11"/>
+      <c r="DB10" s="11"/>
       <c r="DC10" s="13"/>
-      <c r="DD10" s="11"/>
+      <c r="DD10" s="6"/>
       <c r="DE10" s="13"/>
-      <c r="DF10" s="11"/>
-      <c r="DG10" s="12"/>
-      <c r="DH10" s="12"/>
-      <c r="DI10" s="12"/>
-      <c r="DJ10" s="12"/>
-      <c r="DK10" s="12"/>
-      <c r="DL10" s="12"/>
-      <c r="DM10" s="12"/>
+      <c r="DF10" s="6"/>
+      <c r="DG10" s="11"/>
+      <c r="DH10" s="11"/>
+      <c r="DI10" s="11"/>
+      <c r="DJ10" s="11"/>
+      <c r="DK10" s="11"/>
+      <c r="DL10" s="11"/>
+      <c r="DM10" s="6"/>
       <c r="DN10" s="13"/>
-      <c r="DO10" s="11"/>
+      <c r="DO10" s="6"/>
       <c r="DP10" s="13"/>
-      <c r="DQ10" s="11"/>
+      <c r="DQ10" s="6"/>
       <c r="DR10" s="13"/>
-      <c r="DS10" s="11"/>
+      <c r="DS10" s="6"/>
       <c r="DT10" s="13"/>
-      <c r="DU10" s="11"/>
+      <c r="DU10" s="6"/>
       <c r="DV10" s="13"/>
-      <c r="DW10" s="11"/>
+      <c r="DW10" s="6"/>
       <c r="DX10" s="13"/>
+      <c r="DY10" s="12"/>
     </row>
     <row r="11">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>マイルストーン</t>
         </is>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="16"/>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="18"/>
-      <c r="AE11" s="15"/>
-      <c r="AF11" s="16"/>
-      <c r="AG11" s="16"/>
-      <c r="AH11" s="18"/>
-      <c r="AI11" s="15"/>
-      <c r="AJ11" s="16"/>
-      <c r="AK11" s="16"/>
-      <c r="AL11" s="18"/>
-      <c r="AM11" s="15"/>
-      <c r="AN11" s="16"/>
-      <c r="AO11" s="16"/>
-      <c r="AP11" s="18"/>
-      <c r="AQ11" s="15"/>
-      <c r="AR11" s="16"/>
-      <c r="AS11" s="16"/>
-      <c r="AT11" s="18"/>
-      <c r="AU11" s="15"/>
-      <c r="AV11" s="16"/>
-      <c r="AW11" s="16"/>
-      <c r="AX11" s="18"/>
-      <c r="AY11" s="15"/>
-      <c r="AZ11" s="18"/>
-      <c r="BA11" s="15"/>
-      <c r="BB11" s="17" t="inlineStr">
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="20"/>
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="17"/>
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="19"/>
+      <c r="AM11" s="16"/>
+      <c r="AN11" s="17"/>
+      <c r="AO11" s="17"/>
+      <c r="AP11" s="20"/>
+      <c r="AQ11" s="16"/>
+      <c r="AR11" s="17"/>
+      <c r="AS11" s="17"/>
+      <c r="AT11" s="19"/>
+      <c r="AU11" s="16"/>
+      <c r="AV11" s="17"/>
+      <c r="AW11" s="17"/>
+      <c r="AX11" s="19"/>
+      <c r="AY11" s="16"/>
+      <c r="AZ11" s="19"/>
+      <c r="BA11" s="16"/>
+      <c r="BB11" s="18" t="inlineStr">
         <is>
           <t>▼現況再現完了</t>
         </is>
       </c>
-      <c r="BC11" s="16"/>
-      <c r="BD11" s="16"/>
-      <c r="BE11" s="16"/>
-      <c r="BF11" s="16"/>
-      <c r="BG11" s="16"/>
-      <c r="BH11" s="16"/>
-      <c r="BI11" s="18"/>
-      <c r="BJ11" s="15"/>
-      <c r="BK11" s="18"/>
-      <c r="BL11" s="15"/>
-      <c r="BM11" s="18"/>
-      <c r="BN11" s="15"/>
-      <c r="BO11" s="18"/>
-      <c r="BP11" s="15"/>
-      <c r="BQ11" s="18"/>
-      <c r="BR11" s="15"/>
+      <c r="BC11" s="17"/>
+      <c r="BD11" s="17"/>
+      <c r="BE11" s="17"/>
+      <c r="BF11" s="17"/>
+      <c r="BG11" s="17"/>
+      <c r="BH11" s="17"/>
+      <c r="BI11" s="19"/>
+      <c r="BJ11" s="16"/>
+      <c r="BK11" s="19"/>
+      <c r="BL11" s="16"/>
+      <c r="BM11" s="19"/>
+      <c r="BN11" s="16"/>
+      <c r="BO11" s="19"/>
+      <c r="BP11" s="16"/>
+      <c r="BQ11" s="19"/>
+      <c r="BR11" s="16"/>
       <c r="BS11" s="16"/>
-      <c r="BT11" s="18"/>
-      <c r="BU11" s="15"/>
-      <c r="BV11" s="18"/>
-      <c r="BW11" s="15"/>
-      <c r="BX11" s="18"/>
-      <c r="BY11" s="15"/>
-      <c r="BZ11" s="18"/>
-      <c r="CA11" s="15"/>
-      <c r="CB11" s="16"/>
-      <c r="CC11" s="18"/>
-      <c r="CD11" s="21"/>
-      <c r="CE11" s="15"/>
+      <c r="BT11" s="19"/>
+      <c r="BU11" s="16"/>
+      <c r="BV11" s="19"/>
+      <c r="BW11" s="16"/>
+      <c r="BX11" s="19"/>
+      <c r="BY11" s="16"/>
+      <c r="BZ11" s="19"/>
+      <c r="CA11" s="16"/>
+      <c r="CB11" s="17"/>
+      <c r="CC11" s="20"/>
+      <c r="CD11" s="20"/>
+      <c r="CE11" s="16"/>
       <c r="CF11" s="16"/>
-      <c r="CG11" s="18"/>
-      <c r="CH11" s="15"/>
-      <c r="CI11" s="18"/>
-      <c r="CJ11" s="15"/>
-      <c r="CK11" s="16"/>
-      <c r="CL11" s="18"/>
-      <c r="CM11" s="15"/>
-      <c r="CN11" s="18"/>
-      <c r="CO11" s="15"/>
-      <c r="CP11" s="18"/>
-      <c r="CQ11" s="15"/>
-      <c r="CR11" s="18"/>
-      <c r="CS11" s="15"/>
-      <c r="CT11" s="18"/>
-      <c r="CU11" s="15"/>
-      <c r="CV11" s="17" t="inlineStr">
+      <c r="CG11" s="19"/>
+      <c r="CH11" s="16"/>
+      <c r="CI11" s="19"/>
+      <c r="CJ11" s="16"/>
+      <c r="CK11" s="17"/>
+      <c r="CL11" s="20"/>
+      <c r="CM11" s="16"/>
+      <c r="CN11" s="20"/>
+      <c r="CO11" s="16"/>
+      <c r="CP11" s="19"/>
+      <c r="CQ11" s="16"/>
+      <c r="CR11" s="19"/>
+      <c r="CS11" s="16"/>
+      <c r="CT11" s="19"/>
+      <c r="CU11" s="16"/>
+      <c r="CV11" s="18" t="inlineStr">
         <is>
           <t>▼将来配分完了</t>
         </is>
       </c>
-      <c r="CW11" s="16"/>
-      <c r="CX11" s="16"/>
-      <c r="CY11" s="16"/>
-      <c r="CZ11" s="16"/>
-      <c r="DA11" s="16"/>
-      <c r="DB11" s="16"/>
-      <c r="DC11" s="18"/>
-      <c r="DD11" s="15"/>
-      <c r="DE11" s="18"/>
-      <c r="DF11" s="19" t="inlineStr">
+      <c r="CW11" s="17"/>
+      <c r="CX11" s="17"/>
+      <c r="CY11" s="17"/>
+      <c r="CZ11" s="17"/>
+      <c r="DA11" s="17"/>
+      <c r="DB11" s="17"/>
+      <c r="DC11" s="19"/>
+      <c r="DD11" s="16"/>
+      <c r="DE11" s="19"/>
+      <c r="DF11" s="21" t="inlineStr">
         <is>
           <t>▼配分特性等整理完了</t>
         </is>
       </c>
-      <c r="DG11" s="16"/>
-      <c r="DH11" s="16"/>
-      <c r="DI11" s="16"/>
-      <c r="DJ11" s="16"/>
-      <c r="DK11" s="16"/>
-      <c r="DL11" s="16"/>
-      <c r="DM11" s="16"/>
-      <c r="DN11" s="18"/>
-      <c r="DO11" s="15"/>
-      <c r="DP11" s="18"/>
-      <c r="DQ11" s="15"/>
-      <c r="DR11" s="18"/>
-      <c r="DS11" s="15"/>
-      <c r="DT11" s="18"/>
-      <c r="DU11" s="15"/>
-      <c r="DV11" s="18"/>
-      <c r="DW11" s="15"/>
-      <c r="DX11" s="18"/>
+      <c r="DG11" s="17"/>
+      <c r="DH11" s="17"/>
+      <c r="DI11" s="17"/>
+      <c r="DJ11" s="17"/>
+      <c r="DK11" s="17"/>
+      <c r="DL11" s="17"/>
+      <c r="DM11" s="17"/>
+      <c r="DN11" s="19"/>
+      <c r="DO11" s="16"/>
+      <c r="DP11" s="19"/>
+      <c r="DQ11" s="16"/>
+      <c r="DR11" s="19"/>
+      <c r="DS11" s="16"/>
+      <c r="DT11" s="19"/>
+      <c r="DU11" s="16"/>
+      <c r="DV11" s="19"/>
+      <c r="DW11" s="16"/>
+      <c r="DX11" s="19"/>
+      <c r="DY11" s="12"/>
     </row>
     <row r="12">
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>打合せ</t>
         </is>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
       <c r="T12" s="13"/>
-      <c r="U12" s="8"/>
+      <c r="U12" s="9"/>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
-      <c r="Z12" s="7" t="inlineStr">
+      <c r="Z12" s="8" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
@@ -1600,27 +1687,27 @@
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="5"/>
-      <c r="AE12" s="8"/>
+      <c r="AE12" s="9"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="4"/>
-      <c r="AH12" s="5"/>
-      <c r="AI12" s="8"/>
+      <c r="AH12" s="22"/>
+      <c r="AI12" s="9"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="4"/>
       <c r="AL12" s="5"/>
-      <c r="AM12" s="8"/>
+      <c r="AM12" s="9"/>
       <c r="AN12" s="4"/>
       <c r="AO12" s="4"/>
-      <c r="AP12" s="5"/>
-      <c r="AQ12" s="8"/>
+      <c r="AP12" s="22"/>
+      <c r="AQ12" s="9"/>
       <c r="AR12" s="4"/>
       <c r="AS12" s="4"/>
       <c r="AT12" s="5"/>
-      <c r="AU12" s="8"/>
+      <c r="AU12" s="9"/>
       <c r="AV12" s="4"/>
       <c r="AW12" s="4"/>
       <c r="AX12" s="5"/>
-      <c r="AY12" s="8"/>
+      <c r="AY12" s="9"/>
       <c r="AZ12" s="4"/>
       <c r="BA12" s="7" t="inlineStr">
         <is>
@@ -1628,27 +1715,27 @@
         </is>
       </c>
       <c r="BB12" s="5"/>
-      <c r="BC12" s="8"/>
+      <c r="BC12" s="9"/>
       <c r="BD12" s="5"/>
-      <c r="BE12" s="8"/>
-      <c r="BF12" s="22" t="inlineStr">
+      <c r="BE12" s="9"/>
+      <c r="BF12" s="23" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BG12" s="8"/>
-      <c r="BH12" s="4"/>
+      <c r="BG12" s="9"/>
+      <c r="BH12" s="9"/>
       <c r="BI12" s="5"/>
-      <c r="BJ12" s="8"/>
+      <c r="BJ12" s="9"/>
       <c r="BK12" s="5"/>
-      <c r="BL12" s="8"/>
+      <c r="BL12" s="9"/>
       <c r="BM12" s="5"/>
-      <c r="BN12" s="8"/>
+      <c r="BN12" s="9"/>
       <c r="BO12" s="5"/>
-      <c r="BP12" s="8"/>
+      <c r="BP12" s="9"/>
       <c r="BQ12" s="5"/>
-      <c r="BR12" s="8"/>
-      <c r="BS12" s="4"/>
+      <c r="BR12" s="9"/>
+      <c r="BS12" s="9"/>
       <c r="BT12" s="4"/>
       <c r="BU12" s="7" t="inlineStr">
         <is>
@@ -1656,25 +1743,25 @@
         </is>
       </c>
       <c r="BV12" s="5"/>
-      <c r="BW12" s="8"/>
+      <c r="BW12" s="9"/>
       <c r="BX12" s="5"/>
-      <c r="BY12" s="8"/>
+      <c r="BY12" s="9"/>
       <c r="BZ12" s="5"/>
-      <c r="CA12" s="8"/>
+      <c r="CA12" s="9"/>
       <c r="CB12" s="4"/>
-      <c r="CC12" s="5"/>
-      <c r="CD12" s="23"/>
-      <c r="CE12" s="8"/>
-      <c r="CF12" s="4"/>
+      <c r="CC12" s="22"/>
+      <c r="CD12" s="22"/>
+      <c r="CE12" s="9"/>
+      <c r="CF12" s="9"/>
       <c r="CG12" s="5"/>
-      <c r="CH12" s="8"/>
+      <c r="CH12" s="9"/>
       <c r="CI12" s="5"/>
-      <c r="CJ12" s="8"/>
+      <c r="CJ12" s="9"/>
       <c r="CK12" s="4"/>
-      <c r="CL12" s="5"/>
-      <c r="CM12" s="8"/>
-      <c r="CN12" s="5"/>
-      <c r="CO12" s="8"/>
+      <c r="CL12" s="22"/>
+      <c r="CM12" s="9"/>
+      <c r="CN12" s="22"/>
+      <c r="CO12" s="9"/>
       <c r="CP12" s="4"/>
       <c r="CQ12" s="7" t="inlineStr">
         <is>
@@ -1682,16 +1769,16 @@
         </is>
       </c>
       <c r="CR12" s="5"/>
-      <c r="CS12" s="8"/>
+      <c r="CS12" s="9"/>
       <c r="CT12" s="5"/>
-      <c r="CU12" s="8"/>
+      <c r="CU12" s="9"/>
       <c r="CV12" s="5"/>
-      <c r="CW12" s="8"/>
+      <c r="CW12" s="9"/>
       <c r="CX12" s="4"/>
-      <c r="CY12" s="5"/>
-      <c r="CZ12" s="8"/>
+      <c r="CY12" s="22"/>
+      <c r="CZ12" s="9"/>
       <c r="DA12" s="5"/>
-      <c r="DB12" s="8"/>
+      <c r="DB12" s="9"/>
       <c r="DC12" s="4"/>
       <c r="DD12" s="7" t="inlineStr">
         <is>
@@ -1699,71 +1786,107 @@
         </is>
       </c>
       <c r="DE12" s="5"/>
-      <c r="DF12" s="8"/>
+      <c r="DF12" s="9"/>
       <c r="DG12" s="4"/>
-      <c r="DH12" s="7" t="inlineStr">
+      <c r="DH12" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
       <c r="DI12" s="4"/>
-      <c r="DJ12" s="5"/>
-      <c r="DK12" s="8"/>
+      <c r="DJ12" s="22"/>
+      <c r="DK12" s="9"/>
       <c r="DL12" s="5"/>
-      <c r="DM12" s="8"/>
+      <c r="DM12" s="9"/>
       <c r="DN12" s="5"/>
-      <c r="DO12" s="8"/>
+      <c r="DO12" s="9"/>
       <c r="DP12" s="5"/>
-      <c r="DQ12" s="8"/>
+      <c r="DQ12" s="9"/>
       <c r="DR12" s="5"/>
-      <c r="DS12" s="8"/>
+      <c r="DS12" s="9"/>
       <c r="DT12" s="5"/>
-      <c r="DU12" s="8"/>
+      <c r="DU12" s="9"/>
       <c r="DV12" s="5"/>
-      <c r="DW12" s="8"/>
+      <c r="DW12" s="9"/>
       <c r="DX12" s="5"/>
+      <c r="DY12" s="12"/>
     </row>
     <row r="13">
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>【事務所（△）・局（〇）・本省（◎）・委員会または検討会等（●）】</t>
         </is>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="18"/>
-      <c r="Z13" s="2" t="inlineStr">
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="BA13" s="2" t="inlineStr">
+      <c r="AA13" s="4"/>
+      <c r="AB13" s="4"/>
+      <c r="AC13" s="4"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="9"/>
+      <c r="AF13" s="4"/>
+      <c r="AG13" s="4"/>
+      <c r="AH13" s="22"/>
+      <c r="AI13" s="9"/>
+      <c r="AJ13" s="4"/>
+      <c r="AK13" s="4"/>
+      <c r="AL13" s="5"/>
+      <c r="AM13" s="9"/>
+      <c r="AN13" s="4"/>
+      <c r="AO13" s="4"/>
+      <c r="AP13" s="22"/>
+      <c r="AQ13" s="9"/>
+      <c r="AR13" s="4"/>
+      <c r="AS13" s="4"/>
+      <c r="AT13" s="5"/>
+      <c r="AU13" s="9"/>
+      <c r="AV13" s="4"/>
+      <c r="AW13" s="4"/>
+      <c r="AX13" s="5"/>
+      <c r="AY13" s="9"/>
+      <c r="AZ13" s="4"/>
+      <c r="BA13" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BF13" s="2" t="inlineStr">
+      <c r="BB13" s="5"/>
+      <c r="BC13" s="9"/>
+      <c r="BD13" s="5"/>
+      <c r="BE13" s="9"/>
+      <c r="BF13" s="23" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BG13" s="8"/>
-      <c r="BH13" s="4"/>
+      <c r="BG13" s="9"/>
+      <c r="BH13" s="9"/>
       <c r="BI13" s="4"/>
       <c r="BJ13" s="7" t="inlineStr">
         <is>
@@ -1771,367 +1894,417 @@
         </is>
       </c>
       <c r="BK13" s="5"/>
-      <c r="BR13" s="8"/>
-      <c r="BS13" s="4"/>
+      <c r="BL13" s="9"/>
+      <c r="BM13" s="5"/>
+      <c r="BN13" s="9"/>
+      <c r="BO13" s="5"/>
+      <c r="BP13" s="9"/>
+      <c r="BQ13" s="5"/>
+      <c r="BR13" s="9"/>
+      <c r="BS13" s="9"/>
       <c r="BT13" s="5"/>
-      <c r="BU13" s="8"/>
-      <c r="BV13" s="7" t="inlineStr">
+      <c r="BU13" s="9"/>
+      <c r="BV13" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BW13" s="4"/>
+      <c r="BW13" s="9"/>
       <c r="BX13" s="5"/>
-      <c r="CO13" s="8"/>
+      <c r="BY13" s="9"/>
+      <c r="BZ13" s="5"/>
+      <c r="CA13" s="9"/>
+      <c r="CB13" s="4"/>
+      <c r="CC13" s="22"/>
+      <c r="CD13" s="22"/>
+      <c r="CE13" s="9"/>
+      <c r="CF13" s="9"/>
+      <c r="CG13" s="5"/>
+      <c r="CH13" s="9"/>
+      <c r="CI13" s="5"/>
+      <c r="CJ13" s="9"/>
+      <c r="CK13" s="4"/>
+      <c r="CL13" s="22"/>
+      <c r="CM13" s="9"/>
+      <c r="CN13" s="22"/>
+      <c r="CO13" s="9"/>
       <c r="CP13" s="5"/>
-      <c r="CQ13" s="8"/>
+      <c r="CQ13" s="9"/>
       <c r="CR13" s="5"/>
-      <c r="DB13" s="8"/>
+      <c r="CS13" s="9"/>
+      <c r="CT13" s="5"/>
+      <c r="CU13" s="9"/>
+      <c r="CV13" s="5"/>
+      <c r="CW13" s="9"/>
+      <c r="CX13" s="4"/>
+      <c r="CY13" s="22"/>
+      <c r="CZ13" s="9"/>
+      <c r="DA13" s="5"/>
+      <c r="DB13" s="9"/>
       <c r="DC13" s="5"/>
-      <c r="DD13" s="8"/>
+      <c r="DD13" s="9"/>
       <c r="DE13" s="5"/>
-      <c r="DF13" s="8"/>
+      <c r="DF13" s="9"/>
       <c r="DG13" s="5"/>
-      <c r="DH13" s="8"/>
+      <c r="DH13" s="9"/>
       <c r="DI13" s="4"/>
-      <c r="DJ13" s="5"/>
+      <c r="DJ13" s="22"/>
+      <c r="DK13" s="9"/>
+      <c r="DL13" s="5"/>
+      <c r="DM13" s="9"/>
+      <c r="DN13" s="5"/>
+      <c r="DO13" s="9"/>
+      <c r="DP13" s="5"/>
+      <c r="DQ13" s="9"/>
+      <c r="DR13" s="5"/>
+      <c r="DS13" s="9"/>
+      <c r="DT13" s="5"/>
+      <c r="DU13" s="9"/>
+      <c r="DV13" s="5"/>
+      <c r="DW13" s="9"/>
+      <c r="DX13" s="5"/>
+      <c r="DY13" s="12"/>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>準備計画</t>
         </is>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
       <c r="T14" s="13"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="12"/>
-      <c r="AB14" s="12"/>
-      <c r="AC14" s="12"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11"/>
+      <c r="AA14" s="11"/>
+      <c r="AB14" s="11"/>
+      <c r="AC14" s="11"/>
       <c r="AD14" s="13"/>
-      <c r="AE14" s="11"/>
+      <c r="AE14" s="6"/>
       <c r="AF14" s="24" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="AG14" s="12"/>
-      <c r="AH14" s="13"/>
-      <c r="AI14" s="11"/>
-      <c r="AJ14" s="12"/>
-      <c r="AK14" s="12"/>
+      <c r="AG14" s="11"/>
+      <c r="AH14" s="14"/>
+      <c r="AI14" s="6"/>
+      <c r="AJ14" s="11"/>
+      <c r="AK14" s="11"/>
       <c r="AL14" s="13"/>
-      <c r="AM14" s="11"/>
-      <c r="AN14" s="12"/>
-      <c r="AO14" s="12"/>
-      <c r="AP14" s="13"/>
-      <c r="AQ14" s="11"/>
-      <c r="AR14" s="12"/>
-      <c r="AS14" s="12"/>
+      <c r="AM14" s="6"/>
+      <c r="AN14" s="11"/>
+      <c r="AO14" s="11"/>
+      <c r="AP14" s="14"/>
+      <c r="AQ14" s="6"/>
+      <c r="AR14" s="11"/>
+      <c r="AS14" s="11"/>
       <c r="AT14" s="13"/>
-      <c r="AU14" s="11"/>
-      <c r="AV14" s="12"/>
-      <c r="AW14" s="12"/>
+      <c r="AU14" s="6"/>
+      <c r="AV14" s="11"/>
+      <c r="AW14" s="11"/>
       <c r="AX14" s="13"/>
-      <c r="AY14" s="11"/>
+      <c r="AY14" s="6"/>
       <c r="AZ14" s="13"/>
-      <c r="BA14" s="11"/>
+      <c r="BA14" s="6"/>
       <c r="BB14" s="13"/>
-      <c r="BC14" s="11"/>
-      <c r="BD14" s="13"/>
-      <c r="BE14" s="11"/>
+      <c r="BC14" s="6"/>
+      <c r="BD14" s="14"/>
+      <c r="BE14" s="6"/>
       <c r="BF14" s="13"/>
-      <c r="BG14" s="11"/>
-      <c r="BH14" s="12"/>
+      <c r="BG14" s="6"/>
+      <c r="BH14" s="6"/>
       <c r="BI14" s="13"/>
-      <c r="BJ14" s="11"/>
+      <c r="BJ14" s="6"/>
       <c r="BK14" s="13"/>
-      <c r="BL14" s="11"/>
+      <c r="BL14" s="6"/>
       <c r="BM14" s="13"/>
-      <c r="BN14" s="11"/>
+      <c r="BN14" s="6"/>
       <c r="BO14" s="13"/>
-      <c r="BP14" s="11"/>
+      <c r="BP14" s="6"/>
       <c r="BQ14" s="13"/>
-      <c r="BR14" s="11"/>
-      <c r="BS14" s="12"/>
+      <c r="BR14" s="6"/>
+      <c r="BS14" s="6"/>
       <c r="BT14" s="13"/>
-      <c r="BU14" s="11"/>
+      <c r="BU14" s="6"/>
       <c r="BV14" s="13"/>
-      <c r="BW14" s="11"/>
+      <c r="BW14" s="6"/>
       <c r="BX14" s="13"/>
-      <c r="BY14" s="11"/>
+      <c r="BY14" s="6"/>
       <c r="BZ14" s="13"/>
-      <c r="CA14" s="11"/>
-      <c r="CB14" s="12"/>
-      <c r="CC14" s="13"/>
-      <c r="CD14" s="20"/>
-      <c r="CE14" s="11"/>
-      <c r="CF14" s="12"/>
+      <c r="CA14" s="6"/>
+      <c r="CB14" s="11"/>
+      <c r="CC14" s="14"/>
+      <c r="CD14" s="14"/>
+      <c r="CE14" s="6"/>
+      <c r="CF14" s="6"/>
       <c r="CG14" s="13"/>
-      <c r="CH14" s="11"/>
+      <c r="CH14" s="6"/>
       <c r="CI14" s="13"/>
-      <c r="CJ14" s="11"/>
-      <c r="CK14" s="12"/>
-      <c r="CL14" s="13"/>
-      <c r="CM14" s="20"/>
-      <c r="CN14" s="2" t="inlineStr">
+      <c r="CJ14" s="6"/>
+      <c r="CK14" s="11"/>
+      <c r="CL14" s="14"/>
+      <c r="CM14" s="14"/>
+      <c r="CN14" s="25" t="inlineStr">
         <is>
           <t>期間が複数になる場合は「セルの</t>
         </is>
       </c>
-      <c r="CO14" s="11"/>
+      <c r="CO14" s="6"/>
       <c r="CP14" s="13"/>
-      <c r="CQ14" s="25" t="inlineStr">
+      <c r="CQ14" s="26" t="inlineStr">
         <is>
           <t>複数に</t>
         </is>
       </c>
       <c r="CR14" s="13"/>
-      <c r="CS14" s="25" t="inlineStr">
+      <c r="CS14" s="26" t="inlineStr">
         <is>
           <t>なる場</t>
         </is>
       </c>
       <c r="CT14" s="13"/>
-      <c r="CU14" s="25" t="inlineStr">
+      <c r="CU14" s="26" t="inlineStr">
         <is>
           <t>合は「</t>
         </is>
       </c>
       <c r="CV14" s="13"/>
-      <c r="CW14" s="25" t="inlineStr">
+      <c r="CW14" s="26" t="inlineStr">
         <is>
           <t>セルの</t>
         </is>
       </c>
-      <c r="CX14" s="12"/>
-      <c r="CY14" s="13"/>
-      <c r="CZ14" s="20"/>
-      <c r="DB14" s="11"/>
+      <c r="CX14" s="11"/>
+      <c r="CY14" s="14"/>
+      <c r="CZ14" s="14"/>
+      <c r="DA14" s="14"/>
+      <c r="DB14" s="6"/>
       <c r="DC14" s="13"/>
-      <c r="DD14" s="11"/>
+      <c r="DD14" s="6"/>
       <c r="DE14" s="13"/>
-      <c r="DF14" s="11"/>
+      <c r="DF14" s="6"/>
       <c r="DG14" s="13"/>
-      <c r="DH14" s="11"/>
-      <c r="DI14" s="12"/>
-      <c r="DJ14" s="13"/>
-      <c r="DK14" s="11"/>
+      <c r="DH14" s="6"/>
+      <c r="DI14" s="11"/>
+      <c r="DJ14" s="14"/>
+      <c r="DK14" s="6"/>
       <c r="DL14" s="13"/>
-      <c r="DM14" s="11"/>
+      <c r="DM14" s="6"/>
       <c r="DN14" s="13"/>
-      <c r="DO14" s="11"/>
+      <c r="DO14" s="6"/>
       <c r="DP14" s="13"/>
-      <c r="DQ14" s="11"/>
+      <c r="DQ14" s="6"/>
       <c r="DR14" s="13"/>
-      <c r="DS14" s="11"/>
+      <c r="DS14" s="6"/>
       <c r="DT14" s="13"/>
-      <c r="DU14" s="11"/>
+      <c r="DU14" s="6"/>
       <c r="DV14" s="13"/>
-      <c r="DW14" s="11"/>
+      <c r="DW14" s="6"/>
       <c r="DX14" s="13"/>
+      <c r="DY14" s="12"/>
     </row>
     <row r="15">
-      <c r="B15" s="15"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="15"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="16"/>
-      <c r="AB15" s="16"/>
-      <c r="AC15" s="16"/>
-      <c r="AD15" s="18"/>
-      <c r="AE15" s="15"/>
-      <c r="AF15" s="16"/>
-      <c r="AG15" s="16"/>
-      <c r="AH15" s="18"/>
-      <c r="AI15" s="15"/>
-      <c r="AJ15" s="17" t="inlineStr">
+      <c r="B15" s="9"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="4"/>
+      <c r="AB15" s="4"/>
+      <c r="AC15" s="4"/>
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="9"/>
+      <c r="AF15" s="4"/>
+      <c r="AG15" s="4"/>
+      <c r="AH15" s="22"/>
+      <c r="AI15" s="9"/>
+      <c r="AJ15" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="AK15" s="16"/>
-      <c r="AL15" s="18"/>
-      <c r="AM15" s="19" t="inlineStr">
+      <c r="AK15" s="4"/>
+      <c r="AL15" s="5"/>
+      <c r="AM15" s="7" t="inlineStr">
         <is>
           <t>1月11日</t>
         </is>
       </c>
-      <c r="AN15" s="16"/>
-      <c r="AO15" s="16"/>
-      <c r="AP15" s="18"/>
-      <c r="AQ15" s="19" t="inlineStr">
+      <c r="AN15" s="4"/>
+      <c r="AO15" s="4"/>
+      <c r="AP15" s="22"/>
+      <c r="AQ15" s="7" t="inlineStr">
         <is>
           <t>1月28日</t>
         </is>
       </c>
-      <c r="AR15" s="16"/>
-      <c r="AS15" s="16"/>
-      <c r="AT15" s="18"/>
-      <c r="AU15" s="15"/>
-      <c r="AV15" s="16"/>
-      <c r="AW15" s="16"/>
-      <c r="AX15" s="26" t="inlineStr">
+      <c r="AR15" s="4"/>
+      <c r="AS15" s="4"/>
+      <c r="AT15" s="5"/>
+      <c r="AU15" s="9"/>
+      <c r="AV15" s="4"/>
+      <c r="AW15" s="4"/>
+      <c r="AX15" s="23" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="AY15" s="15"/>
-      <c r="AZ15" s="18"/>
-      <c r="BA15" s="15"/>
-      <c r="BB15" s="18"/>
-      <c r="BC15" s="15"/>
-      <c r="BD15" s="18"/>
-      <c r="BE15" s="15"/>
-      <c r="BF15" s="18"/>
-      <c r="BG15" s="15"/>
-      <c r="BH15" s="16"/>
-      <c r="BI15" s="18"/>
-      <c r="BJ15" s="15"/>
-      <c r="BK15" s="18"/>
-      <c r="BL15" s="15"/>
-      <c r="BM15" s="18"/>
-      <c r="BN15" s="15"/>
-      <c r="BO15" s="18"/>
-      <c r="BP15" s="15"/>
-      <c r="BQ15" s="18"/>
-      <c r="BR15" s="15"/>
-      <c r="BS15" s="16"/>
-      <c r="BT15" s="18"/>
-      <c r="BU15" s="15"/>
-      <c r="BV15" s="18"/>
-      <c r="BW15" s="15"/>
-      <c r="BX15" s="18"/>
-      <c r="BY15" s="15"/>
-      <c r="BZ15" s="18"/>
-      <c r="CA15" s="15"/>
-      <c r="CB15" s="16"/>
-      <c r="CC15" s="18"/>
-      <c r="CD15" s="21"/>
-      <c r="CE15" s="15"/>
-      <c r="CF15" s="16"/>
-      <c r="CG15" s="18"/>
-      <c r="CH15" s="15"/>
-      <c r="CI15" s="18"/>
-      <c r="CJ15" s="15"/>
-      <c r="CK15" s="16"/>
-      <c r="CL15" s="18"/>
-      <c r="CM15" s="21"/>
-      <c r="CN15" s="2" t="inlineStr">
+      <c r="AY15" s="9"/>
+      <c r="AZ15" s="5"/>
+      <c r="BA15" s="9"/>
+      <c r="BB15" s="5"/>
+      <c r="BC15" s="9"/>
+      <c r="BD15" s="5"/>
+      <c r="BE15" s="9"/>
+      <c r="BF15" s="5"/>
+      <c r="BG15" s="9"/>
+      <c r="BH15" s="9"/>
+      <c r="BI15" s="5"/>
+      <c r="BJ15" s="9"/>
+      <c r="BK15" s="5"/>
+      <c r="BL15" s="9"/>
+      <c r="BM15" s="5"/>
+      <c r="BN15" s="9"/>
+      <c r="BO15" s="5"/>
+      <c r="BP15" s="9"/>
+      <c r="BQ15" s="5"/>
+      <c r="BR15" s="9"/>
+      <c r="BS15" s="9"/>
+      <c r="BT15" s="5"/>
+      <c r="BU15" s="9"/>
+      <c r="BV15" s="5"/>
+      <c r="BW15" s="9"/>
+      <c r="BX15" s="5"/>
+      <c r="BY15" s="9"/>
+      <c r="BZ15" s="5"/>
+      <c r="CA15" s="9"/>
+      <c r="CB15" s="4"/>
+      <c r="CC15" s="22"/>
+      <c r="CD15" s="22"/>
+      <c r="CE15" s="9"/>
+      <c r="CF15" s="9"/>
+      <c r="CG15" s="5"/>
+      <c r="CH15" s="9"/>
+      <c r="CI15" s="22"/>
+      <c r="CJ15" s="9"/>
+      <c r="CK15" s="4"/>
+      <c r="CL15" s="22"/>
+      <c r="CM15" s="22"/>
+      <c r="CN15" s="27" t="inlineStr">
         <is>
           <t>書式設定」から色を設定することが</t>
         </is>
       </c>
-      <c r="CO15" s="15"/>
-      <c r="CP15" s="18"/>
-      <c r="CQ15" s="27" t="inlineStr">
+      <c r="CO15" s="9"/>
+      <c r="CP15" s="5"/>
+      <c r="CQ15" s="10" t="inlineStr">
         <is>
           <t>定」か</t>
         </is>
       </c>
-      <c r="CR15" s="18"/>
-      <c r="CS15" s="27" t="inlineStr">
+      <c r="CR15" s="5"/>
+      <c r="CS15" s="10" t="inlineStr">
         <is>
           <t>ら色を</t>
         </is>
       </c>
-      <c r="CT15" s="18"/>
-      <c r="CU15" s="27" t="inlineStr">
+      <c r="CT15" s="5"/>
+      <c r="CU15" s="10" t="inlineStr">
         <is>
           <t>設定す</t>
         </is>
       </c>
-      <c r="CV15" s="18"/>
-      <c r="CW15" s="27" t="inlineStr">
+      <c r="CV15" s="5"/>
+      <c r="CW15" s="10" t="inlineStr">
         <is>
           <t>ることが</t>
         </is>
       </c>
-      <c r="CX15" s="16"/>
-      <c r="CY15" s="18"/>
-      <c r="CZ15" s="21"/>
-      <c r="DB15" s="15"/>
-      <c r="DC15" s="18"/>
-      <c r="DD15" s="15"/>
-      <c r="DE15" s="18"/>
-      <c r="DF15" s="15"/>
-      <c r="DG15" s="18"/>
-      <c r="DH15" s="15"/>
-      <c r="DI15" s="16"/>
-      <c r="DJ15" s="18"/>
-      <c r="DK15" s="15"/>
-      <c r="DL15" s="18"/>
-      <c r="DM15" s="15"/>
-      <c r="DN15" s="18"/>
-      <c r="DO15" s="15"/>
-      <c r="DP15" s="18"/>
-      <c r="DQ15" s="15"/>
-      <c r="DR15" s="18"/>
-      <c r="DS15" s="15"/>
-      <c r="DT15" s="18"/>
-      <c r="DU15" s="15"/>
-      <c r="DV15" s="18"/>
-      <c r="DW15" s="15"/>
-      <c r="DX15" s="18"/>
+      <c r="CX15" s="4"/>
+      <c r="CY15" s="22"/>
+      <c r="CZ15" s="22"/>
+      <c r="DA15" s="22"/>
+      <c r="DB15" s="9"/>
+      <c r="DC15" s="5"/>
+      <c r="DD15" s="9"/>
+      <c r="DE15" s="5"/>
+      <c r="DF15" s="9"/>
+      <c r="DG15" s="5"/>
+      <c r="DH15" s="9"/>
+      <c r="DI15" s="4"/>
+      <c r="DJ15" s="22"/>
+      <c r="DK15" s="9"/>
+      <c r="DL15" s="5"/>
+      <c r="DM15" s="9"/>
+      <c r="DN15" s="5"/>
+      <c r="DO15" s="9"/>
+      <c r="DP15" s="5"/>
+      <c r="DQ15" s="9"/>
+      <c r="DR15" s="5"/>
+      <c r="DS15" s="9"/>
+      <c r="DT15" s="5"/>
+      <c r="DU15" s="9"/>
+      <c r="DV15" s="5"/>
+      <c r="DW15" s="9"/>
+      <c r="DX15" s="5"/>
+      <c r="DY15" s="12"/>
     </row>
     <row r="16">
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>基礎資料収集・整理</t>
         </is>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
       <c r="K16" s="13"/>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>資料収集</t>
         </is>
@@ -2144,8 +2317,8 @@
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="5"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="7" t="inlineStr">
+      <c r="U16" s="9"/>
+      <c r="V16" s="8" t="inlineStr">
         <is>
           <t>作業項目の欄は、柔軟に対応できるようテキスト、罫線完了</t>
         </is>
@@ -2165,245 +2338,290 @@
       </c>
       <c r="AF16" s="4"/>
       <c r="AG16" s="4"/>
-      <c r="AH16" s="5"/>
-      <c r="AI16" s="8"/>
-      <c r="AJ16" s="7" t="inlineStr">
+      <c r="AH16" s="22"/>
+      <c r="AI16" s="9"/>
+      <c r="AJ16" s="8" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
       <c r="AK16" s="4"/>
       <c r="AL16" s="5"/>
-      <c r="AM16" s="8"/>
+      <c r="AM16" s="9"/>
       <c r="AN16" s="4"/>
       <c r="AO16" s="4"/>
-      <c r="AP16" s="5"/>
-      <c r="AQ16" s="8"/>
+      <c r="AP16" s="22"/>
+      <c r="AQ16" s="9"/>
       <c r="AR16" s="4"/>
       <c r="AS16" s="4"/>
       <c r="AT16" s="5"/>
-      <c r="AU16" s="8"/>
+      <c r="AU16" s="9"/>
       <c r="AV16" s="4"/>
       <c r="AW16" s="4"/>
-      <c r="AX16" s="22" t="inlineStr">
+      <c r="AX16" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AY16" s="8"/>
+      <c r="AY16" s="9"/>
       <c r="AZ16" s="5"/>
-      <c r="BA16" s="8"/>
+      <c r="BA16" s="9"/>
       <c r="BB16" s="5"/>
-      <c r="BC16" s="8"/>
+      <c r="BC16" s="9"/>
       <c r="BD16" s="5"/>
-      <c r="BE16" s="8"/>
+      <c r="BE16" s="9"/>
       <c r="BF16" s="5"/>
-      <c r="BG16" s="8"/>
-      <c r="BH16" s="4"/>
-      <c r="BI16" s="5"/>
-      <c r="BJ16" s="8"/>
+      <c r="BG16" s="9"/>
+      <c r="BH16" s="9"/>
+      <c r="BI16" s="22"/>
+      <c r="BJ16" s="9"/>
       <c r="BK16" s="5"/>
-      <c r="BL16" s="8"/>
+      <c r="BL16" s="9"/>
       <c r="BM16" s="5"/>
-      <c r="BN16" s="8"/>
+      <c r="BN16" s="9"/>
       <c r="BO16" s="5"/>
-      <c r="BP16" s="8"/>
+      <c r="BP16" s="9"/>
       <c r="BQ16" s="5"/>
-      <c r="BR16" s="8"/>
-      <c r="BS16" s="4"/>
+      <c r="BR16" s="9"/>
+      <c r="BS16" s="9"/>
       <c r="BT16" s="5"/>
-      <c r="BU16" s="8"/>
-      <c r="BV16" s="5"/>
-      <c r="BW16" s="8"/>
+      <c r="BU16" s="9"/>
+      <c r="BV16" s="22"/>
+      <c r="BW16" s="9"/>
       <c r="BX16" s="5"/>
-      <c r="BY16" s="8"/>
+      <c r="BY16" s="9"/>
       <c r="BZ16" s="5"/>
-      <c r="CA16" s="8"/>
+      <c r="CA16" s="9"/>
       <c r="CB16" s="4"/>
-      <c r="CC16" s="5"/>
-      <c r="CD16" s="23"/>
-      <c r="CE16" s="8"/>
-      <c r="CF16" s="4"/>
+      <c r="CC16" s="22"/>
+      <c r="CD16" s="22"/>
+      <c r="CE16" s="9"/>
+      <c r="CF16" s="9"/>
       <c r="CG16" s="5"/>
-      <c r="CH16" s="23"/>
-      <c r="CJ16" s="8"/>
+      <c r="CH16" s="22"/>
+      <c r="CI16" s="22"/>
+      <c r="CJ16" s="9"/>
       <c r="CK16" s="4"/>
-      <c r="CL16" s="5"/>
-      <c r="CM16" s="8"/>
-      <c r="CN16" s="5"/>
-      <c r="CO16" s="8"/>
+      <c r="CL16" s="22"/>
+      <c r="CM16" s="9"/>
+      <c r="CN16" s="22"/>
+      <c r="CO16" s="9"/>
       <c r="CP16" s="5"/>
-      <c r="CQ16" s="8"/>
+      <c r="CQ16" s="9"/>
       <c r="CR16" s="5"/>
-      <c r="CS16" s="8"/>
+      <c r="CS16" s="9"/>
       <c r="CT16" s="5"/>
-      <c r="CU16" s="8"/>
+      <c r="CU16" s="9"/>
       <c r="CV16" s="5"/>
-      <c r="CW16" s="8"/>
+      <c r="CW16" s="9"/>
       <c r="CX16" s="4"/>
-      <c r="CY16" s="5"/>
-      <c r="CZ16" s="8"/>
-      <c r="DA16" s="5"/>
-      <c r="DB16" s="8"/>
+      <c r="CY16" s="22"/>
+      <c r="CZ16" s="9"/>
+      <c r="DA16" s="22"/>
+      <c r="DB16" s="9"/>
       <c r="DC16" s="5"/>
-      <c r="DD16" s="8"/>
+      <c r="DD16" s="9"/>
       <c r="DE16" s="5"/>
-      <c r="DF16" s="8"/>
+      <c r="DF16" s="9"/>
       <c r="DG16" s="5"/>
-      <c r="DH16" s="8"/>
+      <c r="DH16" s="9"/>
       <c r="DI16" s="4"/>
-      <c r="DJ16" s="5"/>
-      <c r="DK16" s="8"/>
+      <c r="DJ16" s="22"/>
+      <c r="DK16" s="9"/>
       <c r="DL16" s="5"/>
-      <c r="DM16" s="8"/>
+      <c r="DM16" s="9"/>
       <c r="DN16" s="5"/>
-      <c r="DO16" s="8"/>
+      <c r="DO16" s="9"/>
       <c r="DP16" s="5"/>
-      <c r="DQ16" s="8"/>
+      <c r="DQ16" s="9"/>
       <c r="DR16" s="5"/>
-      <c r="DS16" s="8"/>
+      <c r="DS16" s="9"/>
       <c r="DT16" s="5"/>
-      <c r="DU16" s="8"/>
+      <c r="DU16" s="9"/>
       <c r="DV16" s="5"/>
-      <c r="DW16" s="8"/>
+      <c r="DW16" s="9"/>
       <c r="DX16" s="5"/>
+      <c r="DY16" s="12"/>
     </row>
     <row r="17">
-      <c r="B17" s="28"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="25" t="inlineStr">
+      <c r="B17" s="12"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="26" t="inlineStr">
         <is>
           <t>資料整理</t>
         </is>
       </c>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
       <c r="T17" s="13"/>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U17" s="9"/>
+      <c r="V17" s="8" t="inlineStr">
         <is>
           <t>等の編集が可能</t>
         </is>
       </c>
-      <c r="AE17" s="25" t="inlineStr">
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="4"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="5"/>
+      <c r="AE17" s="26" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="AF17" s="30" t="inlineStr">
+      <c r="AF17" s="29" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="AG17" s="12"/>
-      <c r="AH17" s="13"/>
-      <c r="AJ17" s="2" t="inlineStr">
+      <c r="AG17" s="11"/>
+      <c r="AH17" s="14"/>
+      <c r="AI17" s="9"/>
+      <c r="AJ17" s="8" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="AM17" s="2" t="inlineStr">
+      <c r="AK17" s="4"/>
+      <c r="AL17" s="5"/>
+      <c r="AM17" s="7" t="inlineStr">
         <is>
           <t>2月20日</t>
         </is>
       </c>
-      <c r="AQ17" s="2" t="inlineStr">
+      <c r="AN17" s="4"/>
+      <c r="AO17" s="4"/>
+      <c r="AP17" s="22"/>
+      <c r="AQ17" s="7" t="inlineStr">
         <is>
           <t>6月10日</t>
         </is>
       </c>
-      <c r="AU17" s="11"/>
-      <c r="AV17" s="12"/>
+      <c r="AR17" s="4"/>
+      <c r="AS17" s="4"/>
+      <c r="AT17" s="5"/>
+      <c r="AU17" s="6"/>
+      <c r="AV17" s="11"/>
       <c r="AW17" s="24" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
       <c r="AX17" s="13"/>
-      <c r="AY17" s="11"/>
+      <c r="AY17" s="6"/>
       <c r="AZ17" s="13"/>
-      <c r="BA17" s="11"/>
+      <c r="BA17" s="6"/>
       <c r="BB17" s="13"/>
-      <c r="BC17" s="11"/>
+      <c r="BC17" s="6"/>
       <c r="BD17" s="13"/>
-      <c r="BE17" s="11"/>
+      <c r="BE17" s="6"/>
       <c r="BF17" s="13"/>
-      <c r="BG17" s="11"/>
-      <c r="BH17" s="12"/>
+      <c r="BG17" s="6"/>
+      <c r="BH17" s="6"/>
       <c r="BI17" s="13"/>
-      <c r="CH17" s="11"/>
-      <c r="CI17" s="13"/>
-      <c r="CJ17" s="11"/>
-      <c r="CK17" s="12"/>
-      <c r="CL17" s="13"/>
-      <c r="CM17" s="11"/>
-      <c r="CN17" s="13"/>
-      <c r="CO17" s="11"/>
+      <c r="BJ17" s="9"/>
+      <c r="BK17" s="5"/>
+      <c r="BL17" s="9"/>
+      <c r="BM17" s="5"/>
+      <c r="BN17" s="9"/>
+      <c r="BO17" s="5"/>
+      <c r="BP17" s="9"/>
+      <c r="BQ17" s="5"/>
+      <c r="BR17" s="9"/>
+      <c r="BS17" s="9"/>
+      <c r="BT17" s="5"/>
+      <c r="BU17" s="9"/>
+      <c r="BV17" s="22"/>
+      <c r="BW17" s="9"/>
+      <c r="BX17" s="5"/>
+      <c r="BY17" s="9"/>
+      <c r="BZ17" s="5"/>
+      <c r="CA17" s="9"/>
+      <c r="CB17" s="4"/>
+      <c r="CC17" s="22"/>
+      <c r="CD17" s="22"/>
+      <c r="CE17" s="9"/>
+      <c r="CF17" s="9"/>
+      <c r="CG17" s="5"/>
+      <c r="CH17" s="6"/>
+      <c r="CI17" s="14"/>
+      <c r="CJ17" s="6"/>
+      <c r="CK17" s="11"/>
+      <c r="CL17" s="14"/>
+      <c r="CM17" s="6"/>
+      <c r="CN17" s="14"/>
+      <c r="CO17" s="6"/>
       <c r="CP17" s="13"/>
-      <c r="CQ17" s="11"/>
+      <c r="CQ17" s="6"/>
       <c r="CR17" s="13"/>
-      <c r="CS17" s="11"/>
+      <c r="CS17" s="6"/>
       <c r="CT17" s="13"/>
-      <c r="CU17" s="11"/>
+      <c r="CU17" s="6"/>
       <c r="CV17" s="13"/>
-      <c r="CW17" s="11"/>
-      <c r="CX17" s="12"/>
-      <c r="CY17" s="13"/>
-      <c r="CZ17" s="11"/>
+      <c r="CW17" s="6"/>
+      <c r="CX17" s="11"/>
+      <c r="CY17" s="14"/>
+      <c r="CZ17" s="6"/>
       <c r="DA17" s="13"/>
-      <c r="DB17" s="11"/>
+      <c r="DB17" s="6"/>
       <c r="DC17" s="13"/>
-      <c r="DD17" s="11"/>
+      <c r="DD17" s="6"/>
       <c r="DE17" s="13"/>
-      <c r="DF17" s="11"/>
+      <c r="DF17" s="6"/>
       <c r="DG17" s="13"/>
-      <c r="DH17" s="11"/>
-      <c r="DI17" s="12"/>
-      <c r="DJ17" s="13"/>
-      <c r="DK17" s="11"/>
+      <c r="DH17" s="6"/>
+      <c r="DI17" s="11"/>
+      <c r="DJ17" s="14"/>
+      <c r="DK17" s="6"/>
       <c r="DL17" s="13"/>
-      <c r="DM17" s="11"/>
+      <c r="DM17" s="6"/>
       <c r="DN17" s="13"/>
-      <c r="DO17" s="11"/>
+      <c r="DO17" s="6"/>
       <c r="DP17" s="13"/>
-      <c r="DQ17" s="11"/>
+      <c r="DQ17" s="6"/>
       <c r="DR17" s="13"/>
-      <c r="DS17" s="11"/>
+      <c r="DS17" s="6"/>
       <c r="DT17" s="13"/>
-      <c r="DU17" s="11"/>
+      <c r="DU17" s="6"/>
       <c r="DV17" s="13"/>
-      <c r="DW17" s="11"/>
+      <c r="DW17" s="6"/>
       <c r="DX17" s="13"/>
+      <c r="DY17" s="12"/>
     </row>
     <row r="18">
-      <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="19" t="inlineStr">
+      <c r="B18" s="16"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t>資料整理</t>
         </is>
       </c>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="18"/>
-      <c r="U18" s="8"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="9"/>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
@@ -2413,27 +2631,27 @@
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="5"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="16"/>
-      <c r="AG18" s="16"/>
-      <c r="AH18" s="18"/>
-      <c r="AI18" s="8"/>
-      <c r="AJ18" s="7" t="inlineStr">
+      <c r="AE18" s="9"/>
+      <c r="AF18" s="17"/>
+      <c r="AG18" s="17"/>
+      <c r="AH18" s="20"/>
+      <c r="AI18" s="9"/>
+      <c r="AJ18" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
       <c r="AK18" s="4"/>
       <c r="AL18" s="5"/>
-      <c r="AM18" s="6" t="inlineStr">
+      <c r="AM18" s="7" t="inlineStr">
         <is>
           <t>2月22日</t>
         </is>
       </c>
       <c r="AN18" s="4"/>
       <c r="AO18" s="4"/>
-      <c r="AP18" s="5"/>
-      <c r="AQ18" s="6" t="inlineStr">
+      <c r="AP18" s="22"/>
+      <c r="AQ18" s="7" t="inlineStr">
         <is>
           <t>3月10日</t>
         </is>
@@ -2441,419 +2659,422 @@
       <c r="AR18" s="4"/>
       <c r="AS18" s="4"/>
       <c r="AT18" s="5"/>
-      <c r="AU18" s="15"/>
-      <c r="AV18" s="16"/>
-      <c r="AW18" s="16"/>
-      <c r="AX18" s="26" t="inlineStr">
+      <c r="AU18" s="9"/>
+      <c r="AV18" s="17"/>
+      <c r="AW18" s="17"/>
+      <c r="AX18" s="30" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="AY18" s="15"/>
-      <c r="AZ18" s="18"/>
-      <c r="BA18" s="15"/>
-      <c r="BB18" s="18"/>
-      <c r="BC18" s="15"/>
-      <c r="BD18" s="18"/>
-      <c r="BE18" s="15"/>
-      <c r="BF18" s="18"/>
-      <c r="BG18" s="15"/>
+      <c r="AY18" s="16"/>
+      <c r="AZ18" s="19"/>
+      <c r="BA18" s="16"/>
+      <c r="BB18" s="19"/>
+      <c r="BC18" s="16"/>
+      <c r="BD18" s="19"/>
+      <c r="BE18" s="16"/>
+      <c r="BF18" s="19"/>
+      <c r="BG18" s="16"/>
       <c r="BH18" s="16"/>
-      <c r="BI18" s="18"/>
-      <c r="BJ18" s="8"/>
+      <c r="BI18" s="19"/>
+      <c r="BJ18" s="9"/>
       <c r="BK18" s="5"/>
-      <c r="BL18" s="8"/>
+      <c r="BL18" s="9"/>
       <c r="BM18" s="5"/>
-      <c r="BN18" s="8"/>
+      <c r="BN18" s="9"/>
       <c r="BO18" s="5"/>
-      <c r="BP18" s="8"/>
+      <c r="BP18" s="9"/>
       <c r="BQ18" s="5"/>
-      <c r="BR18" s="8"/>
-      <c r="BS18" s="4"/>
+      <c r="BR18" s="9"/>
+      <c r="BS18" s="9"/>
       <c r="BT18" s="5"/>
-      <c r="BU18" s="8"/>
+      <c r="BU18" s="9"/>
       <c r="BV18" s="5"/>
-      <c r="BW18" s="8"/>
+      <c r="BW18" s="9"/>
       <c r="BX18" s="5"/>
-      <c r="BY18" s="8"/>
+      <c r="BY18" s="9"/>
       <c r="BZ18" s="5"/>
-      <c r="CA18" s="8"/>
+      <c r="CA18" s="9"/>
       <c r="CB18" s="4"/>
-      <c r="CC18" s="5"/>
-      <c r="CD18" s="23"/>
-      <c r="CE18" s="8"/>
-      <c r="CF18" s="4"/>
+      <c r="CC18" s="22"/>
+      <c r="CD18" s="22"/>
+      <c r="CE18" s="9"/>
+      <c r="CF18" s="9"/>
       <c r="CG18" s="5"/>
-      <c r="CH18" s="15"/>
-      <c r="CI18" s="18"/>
-      <c r="CJ18" s="15"/>
-      <c r="CK18" s="16"/>
-      <c r="CL18" s="18"/>
-      <c r="CM18" s="15"/>
-      <c r="CN18" s="18"/>
-      <c r="CO18" s="15"/>
-      <c r="CP18" s="18"/>
-      <c r="CQ18" s="15"/>
-      <c r="CR18" s="18"/>
-      <c r="CS18" s="15"/>
-      <c r="CT18" s="18"/>
-      <c r="CU18" s="15"/>
-      <c r="CV18" s="18"/>
-      <c r="CW18" s="15"/>
-      <c r="CX18" s="16"/>
-      <c r="CY18" s="18"/>
-      <c r="CZ18" s="15"/>
-      <c r="DA18" s="18"/>
-      <c r="DB18" s="15"/>
-      <c r="DC18" s="18"/>
-      <c r="DD18" s="15"/>
-      <c r="DE18" s="18"/>
-      <c r="DF18" s="15"/>
-      <c r="DG18" s="18"/>
-      <c r="DH18" s="15"/>
-      <c r="DI18" s="16"/>
-      <c r="DJ18" s="18"/>
-      <c r="DK18" s="15"/>
-      <c r="DL18" s="18"/>
-      <c r="DM18" s="15"/>
-      <c r="DN18" s="18"/>
-      <c r="DO18" s="15"/>
-      <c r="DP18" s="18"/>
-      <c r="DQ18" s="15"/>
-      <c r="DR18" s="18"/>
-      <c r="DS18" s="15"/>
-      <c r="DT18" s="18"/>
-      <c r="DU18" s="15"/>
-      <c r="DV18" s="18"/>
-      <c r="DW18" s="15"/>
-      <c r="DX18" s="18"/>
+      <c r="CH18" s="9"/>
+      <c r="CI18" s="19"/>
+      <c r="CJ18" s="16"/>
+      <c r="CK18" s="17"/>
+      <c r="CL18" s="20"/>
+      <c r="CM18" s="16"/>
+      <c r="CN18" s="20"/>
+      <c r="CO18" s="16"/>
+      <c r="CP18" s="19"/>
+      <c r="CQ18" s="16"/>
+      <c r="CR18" s="19"/>
+      <c r="CS18" s="16"/>
+      <c r="CT18" s="19"/>
+      <c r="CU18" s="16"/>
+      <c r="CV18" s="19"/>
+      <c r="CW18" s="16"/>
+      <c r="CX18" s="17"/>
+      <c r="CY18" s="20"/>
+      <c r="CZ18" s="16"/>
+      <c r="DA18" s="19"/>
+      <c r="DB18" s="16"/>
+      <c r="DC18" s="19"/>
+      <c r="DD18" s="16"/>
+      <c r="DE18" s="19"/>
+      <c r="DF18" s="16"/>
+      <c r="DG18" s="19"/>
+      <c r="DH18" s="16"/>
+      <c r="DI18" s="17"/>
+      <c r="DJ18" s="20"/>
+      <c r="DK18" s="16"/>
+      <c r="DL18" s="19"/>
+      <c r="DM18" s="16"/>
+      <c r="DN18" s="19"/>
+      <c r="DO18" s="16"/>
+      <c r="DP18" s="19"/>
+      <c r="DQ18" s="16"/>
+      <c r="DR18" s="19"/>
+      <c r="DS18" s="16"/>
+      <c r="DT18" s="19"/>
+      <c r="DU18" s="16"/>
+      <c r="DV18" s="19"/>
+      <c r="DW18" s="16"/>
+      <c r="DX18" s="19"/>
+      <c r="DY18" s="12"/>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>交通量配分用データの作成OD表</t>
         </is>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
       <c r="K19" s="13"/>
-      <c r="L19" s="25" t="inlineStr">
+      <c r="L19" s="26" t="inlineStr">
         <is>
           <t>OD表</t>
         </is>
       </c>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
       <c r="T19" s="13"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="12"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="12"/>
-      <c r="Z19" s="12"/>
-      <c r="AA19" s="12"/>
-      <c r="AB19" s="12"/>
-      <c r="AC19" s="12"/>
+      <c r="U19" s="6"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
+      <c r="AA19" s="11"/>
+      <c r="AB19" s="11"/>
+      <c r="AC19" s="11"/>
       <c r="AD19" s="13"/>
-      <c r="AE19" s="11"/>
+      <c r="AE19" s="6"/>
       <c r="AF19" s="24" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="AG19" s="12"/>
-      <c r="AH19" s="13"/>
-      <c r="AI19" s="11"/>
-      <c r="AJ19" s="12"/>
-      <c r="AK19" s="12"/>
+      <c r="AG19" s="11"/>
+      <c r="AH19" s="14"/>
+      <c r="AI19" s="6"/>
+      <c r="AJ19" s="11"/>
+      <c r="AK19" s="11"/>
       <c r="AL19" s="13"/>
-      <c r="AM19" s="11"/>
-      <c r="AN19" s="12"/>
-      <c r="AO19" s="12"/>
-      <c r="AP19" s="13"/>
-      <c r="AQ19" s="11"/>
-      <c r="AR19" s="12"/>
-      <c r="AS19" s="12"/>
+      <c r="AM19" s="6"/>
+      <c r="AN19" s="11"/>
+      <c r="AO19" s="11"/>
+      <c r="AP19" s="14"/>
+      <c r="AQ19" s="6"/>
+      <c r="AR19" s="11"/>
+      <c r="AS19" s="11"/>
       <c r="AT19" s="13"/>
-      <c r="AU19" s="11"/>
-      <c r="AV19" s="12"/>
-      <c r="AW19" s="12"/>
+      <c r="AU19" s="6"/>
+      <c r="AV19" s="11"/>
+      <c r="AW19" s="11"/>
       <c r="AX19" s="13"/>
-      <c r="AY19" s="11"/>
+      <c r="AY19" s="6"/>
       <c r="AZ19" s="13"/>
-      <c r="BA19" s="11"/>
+      <c r="BA19" s="6"/>
       <c r="BB19" s="13"/>
-      <c r="BC19" s="11"/>
+      <c r="BC19" s="6"/>
       <c r="BD19" s="13"/>
-      <c r="BE19" s="11"/>
+      <c r="BE19" s="6"/>
       <c r="BF19" s="13"/>
-      <c r="BG19" s="11"/>
-      <c r="BH19" s="12"/>
+      <c r="BG19" s="6"/>
+      <c r="BH19" s="6"/>
       <c r="BI19" s="13"/>
-      <c r="BJ19" s="11"/>
+      <c r="BJ19" s="6"/>
       <c r="BK19" s="13"/>
-      <c r="BL19" s="11"/>
+      <c r="BL19" s="6"/>
       <c r="BM19" s="13"/>
-      <c r="BN19" s="11"/>
+      <c r="BN19" s="6"/>
       <c r="BO19" s="13"/>
-      <c r="BP19" s="11"/>
+      <c r="BP19" s="6"/>
       <c r="BQ19" s="13"/>
-      <c r="BR19" s="11"/>
-      <c r="BS19" s="12"/>
+      <c r="BR19" s="6"/>
+      <c r="BS19" s="6"/>
       <c r="BT19" s="13"/>
-      <c r="BU19" s="25" t="inlineStr">
+      <c r="BU19" s="26" t="inlineStr">
         <is>
           <t>ャート</t>
         </is>
       </c>
       <c r="BV19" s="13"/>
-      <c r="BW19" s="25" t="inlineStr">
+      <c r="BW19" s="26" t="inlineStr">
         <is>
           <t>は入力</t>
         </is>
       </c>
       <c r="BX19" s="13"/>
-      <c r="BY19" s="25" t="inlineStr">
+      <c r="BY19" s="26" t="inlineStr">
         <is>
           <t>した着</t>
         </is>
       </c>
       <c r="BZ19" s="13"/>
-      <c r="CA19" s="25" t="inlineStr">
+      <c r="CA19" s="26" t="inlineStr">
         <is>
           <t>手日、</t>
         </is>
       </c>
-      <c r="CB19" s="12"/>
-      <c r="CC19" s="13"/>
+      <c r="CB19" s="11"/>
+      <c r="CC19" s="14"/>
       <c r="CD19" s="31" t="inlineStr">
         <is>
           <t>完</t>
         </is>
       </c>
-      <c r="CE19" s="11"/>
-      <c r="CF19" s="12"/>
+      <c r="CE19" s="6"/>
+      <c r="CF19" s="6"/>
       <c r="CG19" s="13"/>
-      <c r="CH19" s="11"/>
+      <c r="CH19" s="6"/>
       <c r="CI19" s="13"/>
-      <c r="CJ19" s="11"/>
-      <c r="CK19" s="12"/>
-      <c r="CL19" s="13"/>
-      <c r="CM19" s="11"/>
-      <c r="CN19" s="13"/>
-      <c r="CO19" s="11"/>
+      <c r="CJ19" s="6"/>
+      <c r="CK19" s="11"/>
+      <c r="CL19" s="14"/>
+      <c r="CM19" s="6"/>
+      <c r="CN19" s="14"/>
+      <c r="CO19" s="6"/>
       <c r="CP19" s="13"/>
-      <c r="CQ19" s="11"/>
+      <c r="CQ19" s="6"/>
       <c r="CR19" s="13"/>
-      <c r="CS19" s="11"/>
+      <c r="CS19" s="6"/>
       <c r="CT19" s="13"/>
-      <c r="CU19" s="11"/>
+      <c r="CU19" s="6"/>
       <c r="CV19" s="13"/>
-      <c r="CW19" s="11"/>
-      <c r="CX19" s="12"/>
-      <c r="CY19" s="13"/>
-      <c r="CZ19" s="11"/>
+      <c r="CW19" s="6"/>
+      <c r="CX19" s="11"/>
+      <c r="CY19" s="14"/>
+      <c r="CZ19" s="6"/>
       <c r="DA19" s="13"/>
-      <c r="DB19" s="11"/>
+      <c r="DB19" s="6"/>
       <c r="DC19" s="13"/>
-      <c r="DD19" s="11"/>
+      <c r="DD19" s="6"/>
       <c r="DE19" s="13"/>
-      <c r="DF19" s="11"/>
+      <c r="DF19" s="6"/>
       <c r="DG19" s="13"/>
-      <c r="DH19" s="11"/>
-      <c r="DI19" s="12"/>
-      <c r="DJ19" s="13"/>
-      <c r="DK19" s="11"/>
+      <c r="DH19" s="6"/>
+      <c r="DI19" s="11"/>
+      <c r="DJ19" s="14"/>
+      <c r="DK19" s="6"/>
       <c r="DL19" s="13"/>
-      <c r="DM19" s="11"/>
+      <c r="DM19" s="6"/>
       <c r="DN19" s="13"/>
-      <c r="DO19" s="11"/>
+      <c r="DO19" s="6"/>
       <c r="DP19" s="13"/>
-      <c r="DQ19" s="11"/>
+      <c r="DQ19" s="6"/>
       <c r="DR19" s="13"/>
-      <c r="DS19" s="11"/>
+      <c r="DS19" s="6"/>
       <c r="DT19" s="13"/>
-      <c r="DU19" s="11"/>
+      <c r="DU19" s="6"/>
       <c r="DV19" s="13"/>
-      <c r="DW19" s="11"/>
+      <c r="DW19" s="6"/>
       <c r="DX19" s="13"/>
+      <c r="DY19" s="12"/>
     </row>
     <row r="20">
-      <c r="B20" s="28"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="16"/>
-      <c r="Z20" s="16"/>
-      <c r="AA20" s="16"/>
-      <c r="AB20" s="16"/>
-      <c r="AC20" s="16"/>
-      <c r="AD20" s="18"/>
-      <c r="AE20" s="15"/>
-      <c r="AF20" s="16"/>
-      <c r="AG20" s="16"/>
-      <c r="AH20" s="18"/>
-      <c r="AI20" s="15"/>
-      <c r="AJ20" s="17" t="inlineStr">
+      <c r="B20" s="12"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="19"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="17"/>
+      <c r="AA20" s="17"/>
+      <c r="AB20" s="17"/>
+      <c r="AC20" s="17"/>
+      <c r="AD20" s="19"/>
+      <c r="AE20" s="16"/>
+      <c r="AF20" s="17"/>
+      <c r="AG20" s="17"/>
+      <c r="AH20" s="20"/>
+      <c r="AI20" s="9"/>
+      <c r="AJ20" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="AK20" s="16"/>
-      <c r="AL20" s="18"/>
-      <c r="AM20" s="19" t="inlineStr">
+      <c r="AK20" s="4"/>
+      <c r="AL20" s="5"/>
+      <c r="AM20" s="7" t="inlineStr">
         <is>
           <t>2月5日</t>
         </is>
       </c>
-      <c r="AN20" s="16"/>
-      <c r="AO20" s="16"/>
-      <c r="AP20" s="18"/>
-      <c r="AQ20" s="19" t="inlineStr">
+      <c r="AN20" s="4"/>
+      <c r="AO20" s="4"/>
+      <c r="AP20" s="22"/>
+      <c r="AQ20" s="7" t="inlineStr">
         <is>
           <t>3月5日</t>
         </is>
       </c>
-      <c r="AR20" s="16"/>
-      <c r="AS20" s="16"/>
-      <c r="AT20" s="18"/>
-      <c r="AU20" s="15"/>
-      <c r="AV20" s="16"/>
-      <c r="AW20" s="16"/>
-      <c r="AX20" s="26" t="inlineStr">
+      <c r="AR20" s="4"/>
+      <c r="AS20" s="4"/>
+      <c r="AT20" s="5"/>
+      <c r="AU20" s="9"/>
+      <c r="AV20" s="17"/>
+      <c r="AW20" s="17"/>
+      <c r="AX20" s="30" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="AY20" s="15"/>
-      <c r="AZ20" s="18"/>
-      <c r="BA20" s="15"/>
-      <c r="BB20" s="18"/>
-      <c r="BC20" s="15"/>
-      <c r="BD20" s="18"/>
-      <c r="BE20" s="15"/>
-      <c r="BF20" s="18"/>
-      <c r="BG20" s="15"/>
-      <c r="BH20" s="16"/>
-      <c r="BI20" s="18"/>
-      <c r="BJ20" s="15"/>
-      <c r="BK20" s="18"/>
-      <c r="BL20" s="15"/>
-      <c r="BM20" s="18"/>
-      <c r="BN20" s="15"/>
-      <c r="BO20" s="18"/>
-      <c r="BP20" s="15"/>
-      <c r="BQ20" s="18"/>
-      <c r="BR20" s="15"/>
-      <c r="BS20" s="17" t="inlineStr">
+      <c r="AY20" s="16"/>
+      <c r="AZ20" s="19"/>
+      <c r="BA20" s="16"/>
+      <c r="BB20" s="19"/>
+      <c r="BC20" s="16"/>
+      <c r="BD20" s="19"/>
+      <c r="BE20" s="16"/>
+      <c r="BF20" s="22"/>
+      <c r="BG20" s="9"/>
+      <c r="BH20" s="9"/>
+      <c r="BI20" s="5"/>
+      <c r="BJ20" s="9"/>
+      <c r="BK20" s="5"/>
+      <c r="BL20" s="9"/>
+      <c r="BM20" s="22"/>
+      <c r="BN20" s="16"/>
+      <c r="BO20" s="19"/>
+      <c r="BP20" s="16"/>
+      <c r="BQ20" s="19"/>
+      <c r="BR20" s="16"/>
+      <c r="BS20" s="21" t="inlineStr">
         <is>
           <t>バーチャートは入力した着手日、完了日をもとにマクロを使用して表示</t>
         </is>
       </c>
-      <c r="BT20" s="18"/>
-      <c r="BU20" s="27" t="inlineStr">
+      <c r="BT20" s="19"/>
+      <c r="BU20" s="32" t="inlineStr">
         <is>
           <t>もとに</t>
         </is>
       </c>
-      <c r="BV20" s="18"/>
-      <c r="BW20" s="27" t="inlineStr">
+      <c r="BV20" s="19"/>
+      <c r="BW20" s="32" t="inlineStr">
         <is>
           <t>マクロ</t>
         </is>
       </c>
-      <c r="BX20" s="18"/>
-      <c r="BY20" s="27" t="inlineStr">
+      <c r="BX20" s="19"/>
+      <c r="BY20" s="32" t="inlineStr">
         <is>
           <t>を使用</t>
         </is>
       </c>
-      <c r="BZ20" s="18"/>
-      <c r="CA20" s="27" t="inlineStr">
+      <c r="BZ20" s="19"/>
+      <c r="CA20" s="32" t="inlineStr">
         <is>
           <t>して表</t>
         </is>
       </c>
-      <c r="CB20" s="16"/>
-      <c r="CC20" s="18"/>
-      <c r="CD20" s="32" t="inlineStr">
+      <c r="CB20" s="17"/>
+      <c r="CC20" s="20"/>
+      <c r="CD20" s="33" t="inlineStr">
         <is>
           <t>示</t>
         </is>
       </c>
-      <c r="CE20" s="15"/>
+      <c r="CE20" s="16"/>
       <c r="CF20" s="16"/>
-      <c r="CG20" s="18"/>
-      <c r="CH20" s="15"/>
-      <c r="CI20" s="18"/>
-      <c r="CJ20" s="15"/>
-      <c r="CK20" s="16"/>
-      <c r="CL20" s="18"/>
-      <c r="CM20" s="15"/>
-      <c r="CN20" s="18"/>
-      <c r="CO20" s="15"/>
-      <c r="CP20" s="18"/>
-      <c r="CQ20" s="15"/>
-      <c r="CR20" s="18"/>
-      <c r="CS20" s="15"/>
-      <c r="CT20" s="18"/>
-      <c r="CU20" s="15"/>
-      <c r="CV20" s="18"/>
-      <c r="CW20" s="15"/>
-      <c r="CX20" s="16"/>
-      <c r="CY20" s="18"/>
-      <c r="CZ20" s="15"/>
-      <c r="DA20" s="18"/>
-      <c r="DB20" s="15"/>
-      <c r="DC20" s="18"/>
-      <c r="DD20" s="15"/>
-      <c r="DE20" s="18"/>
-      <c r="DF20" s="15"/>
-      <c r="DG20" s="18"/>
-      <c r="DH20" s="15"/>
-      <c r="DI20" s="16"/>
-      <c r="DJ20" s="18"/>
-      <c r="DK20" s="15"/>
-      <c r="DL20" s="18"/>
-      <c r="DM20" s="15"/>
-      <c r="DN20" s="18"/>
-      <c r="DO20" s="15"/>
-      <c r="DP20" s="18"/>
-      <c r="DQ20" s="15"/>
-      <c r="DR20" s="18"/>
-      <c r="DS20" s="15"/>
-      <c r="DT20" s="18"/>
-      <c r="DU20" s="15"/>
-      <c r="DV20" s="18"/>
-      <c r="DW20" s="15"/>
-      <c r="DX20" s="18"/>
+      <c r="CG20" s="19"/>
+      <c r="CH20" s="16"/>
+      <c r="CI20" s="19"/>
+      <c r="CJ20" s="16"/>
+      <c r="CK20" s="17"/>
+      <c r="CL20" s="20"/>
+      <c r="CM20" s="16"/>
+      <c r="CN20" s="20"/>
+      <c r="CO20" s="16"/>
+      <c r="CP20" s="19"/>
+      <c r="CQ20" s="16"/>
+      <c r="CR20" s="19"/>
+      <c r="CS20" s="16"/>
+      <c r="CT20" s="19"/>
+      <c r="CU20" s="16"/>
+      <c r="CV20" s="19"/>
+      <c r="CW20" s="16"/>
+      <c r="CX20" s="17"/>
+      <c r="CY20" s="20"/>
+      <c r="CZ20" s="16"/>
+      <c r="DA20" s="19"/>
+      <c r="DB20" s="16"/>
+      <c r="DC20" s="19"/>
+      <c r="DD20" s="16"/>
+      <c r="DE20" s="19"/>
+      <c r="DF20" s="16"/>
+      <c r="DG20" s="19"/>
+      <c r="DH20" s="16"/>
+      <c r="DI20" s="17"/>
+      <c r="DJ20" s="20"/>
+      <c r="DK20" s="16"/>
+      <c r="DL20" s="19"/>
+      <c r="DM20" s="16"/>
+      <c r="DN20" s="19"/>
+      <c r="DO20" s="16"/>
+      <c r="DP20" s="19"/>
+      <c r="DQ20" s="16"/>
+      <c r="DR20" s="19"/>
+      <c r="DS20" s="16"/>
+      <c r="DT20" s="19"/>
+      <c r="DU20" s="16"/>
+      <c r="DV20" s="19"/>
+      <c r="DW20" s="16"/>
+      <c r="DX20" s="19"/>
+      <c r="DY20" s="12"/>
     </row>
     <row r="21">
-      <c r="B21" s="28"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="6" t="inlineStr">
+      <c r="B21" s="12"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>ゾーニング</t>
         </is>
@@ -2866,7 +3087,7 @@
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
       <c r="T21" s="5"/>
-      <c r="U21" s="8"/>
+      <c r="U21" s="9"/>
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
       <c r="X21" s="4"/>
@@ -2876,31 +3097,31 @@
       <c r="AB21" s="4"/>
       <c r="AC21" s="4"/>
       <c r="AD21" s="5"/>
-      <c r="AE21" s="8"/>
-      <c r="AF21" s="7" t="inlineStr">
+      <c r="AE21" s="9"/>
+      <c r="AF21" s="8" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
       <c r="AG21" s="4"/>
-      <c r="AH21" s="5"/>
-      <c r="AI21" s="8"/>
-      <c r="AJ21" s="7" t="inlineStr">
+      <c r="AH21" s="22"/>
+      <c r="AI21" s="9"/>
+      <c r="AJ21" s="8" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
       <c r="AK21" s="4"/>
       <c r="AL21" s="5"/>
-      <c r="AM21" s="6" t="inlineStr">
+      <c r="AM21" s="7" t="inlineStr">
         <is>
           <t>2月10日</t>
         </is>
       </c>
       <c r="AN21" s="4"/>
       <c r="AO21" s="4"/>
-      <c r="AP21" s="5"/>
-      <c r="AQ21" s="6" t="inlineStr">
+      <c r="AP21" s="22"/>
+      <c r="AQ21" s="7" t="inlineStr">
         <is>
           <t>3月10日</t>
         </is>
@@ -2908,56 +3129,56 @@
       <c r="AR21" s="4"/>
       <c r="AS21" s="4"/>
       <c r="AT21" s="5"/>
-      <c r="AU21" s="8"/>
+      <c r="AU21" s="9"/>
       <c r="AV21" s="4"/>
       <c r="AW21" s="4"/>
-      <c r="AX21" s="22" t="inlineStr">
+      <c r="AX21" s="23" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="AY21" s="8"/>
+      <c r="AY21" s="9"/>
       <c r="AZ21" s="5"/>
-      <c r="BA21" s="8"/>
+      <c r="BA21" s="9"/>
       <c r="BB21" s="5"/>
-      <c r="BC21" s="8"/>
+      <c r="BC21" s="9"/>
       <c r="BD21" s="5"/>
-      <c r="BE21" s="8"/>
+      <c r="BE21" s="9"/>
       <c r="BF21" s="5"/>
-      <c r="BG21" s="8"/>
-      <c r="BH21" s="4"/>
+      <c r="BG21" s="9"/>
+      <c r="BH21" s="9"/>
       <c r="BI21" s="5"/>
-      <c r="BJ21" s="8"/>
+      <c r="BJ21" s="9"/>
       <c r="BK21" s="5"/>
-      <c r="BL21" s="8"/>
+      <c r="BL21" s="9"/>
       <c r="BM21" s="5"/>
-      <c r="BN21" s="8"/>
+      <c r="BN21" s="9"/>
       <c r="BO21" s="5"/>
-      <c r="BP21" s="8"/>
+      <c r="BP21" s="9"/>
       <c r="BQ21" s="5"/>
-      <c r="BR21" s="8"/>
-      <c r="BS21" s="4"/>
+      <c r="BR21" s="9"/>
+      <c r="BS21" s="9"/>
       <c r="BT21" s="5"/>
-      <c r="BU21" s="8"/>
+      <c r="BU21" s="9"/>
       <c r="BV21" s="5"/>
-      <c r="BW21" s="8"/>
+      <c r="BW21" s="9"/>
       <c r="BX21" s="5"/>
-      <c r="BY21" s="8"/>
+      <c r="BY21" s="9"/>
       <c r="BZ21" s="5"/>
-      <c r="CA21" s="8"/>
+      <c r="CA21" s="9"/>
       <c r="CB21" s="4"/>
-      <c r="CC21" s="5"/>
-      <c r="CD21" s="23"/>
-      <c r="CE21" s="8"/>
-      <c r="CF21" s="4"/>
+      <c r="CC21" s="22"/>
+      <c r="CD21" s="22"/>
+      <c r="CE21" s="9"/>
+      <c r="CF21" s="9"/>
       <c r="CG21" s="5"/>
-      <c r="CH21" s="8"/>
+      <c r="CH21" s="9"/>
       <c r="CI21" s="5"/>
-      <c r="CJ21" s="8"/>
+      <c r="CJ21" s="9"/>
       <c r="CK21" s="4"/>
-      <c r="CL21" s="5"/>
-      <c r="CM21" s="8"/>
-      <c r="CN21" s="22" t="inlineStr">
+      <c r="CL21" s="22"/>
+      <c r="CM21" s="9"/>
+      <c r="CN21" s="27" t="inlineStr">
         <is>
           <t>更新日を赤線で自動表示</t>
         </is>
@@ -2986,197 +3207,237 @@
         </is>
       </c>
       <c r="CV21" s="5"/>
-      <c r="CW21" s="8"/>
+      <c r="CW21" s="9"/>
       <c r="CX21" s="4"/>
-      <c r="CY21" s="5"/>
-      <c r="CZ21" s="8"/>
+      <c r="CY21" s="22"/>
+      <c r="CZ21" s="9"/>
       <c r="DA21" s="5"/>
-      <c r="DB21" s="8"/>
+      <c r="DB21" s="9"/>
       <c r="DC21" s="5"/>
-      <c r="DD21" s="8"/>
+      <c r="DD21" s="9"/>
       <c r="DE21" s="5"/>
-      <c r="DF21" s="8"/>
+      <c r="DF21" s="9"/>
       <c r="DG21" s="5"/>
-      <c r="DH21" s="8"/>
+      <c r="DH21" s="9"/>
       <c r="DI21" s="4"/>
-      <c r="DJ21" s="5"/>
-      <c r="DK21" s="8"/>
+      <c r="DJ21" s="22"/>
+      <c r="DK21" s="9"/>
       <c r="DL21" s="5"/>
-      <c r="DM21" s="8"/>
+      <c r="DM21" s="9"/>
       <c r="DN21" s="5"/>
-      <c r="DO21" s="8"/>
+      <c r="DO21" s="9"/>
       <c r="DP21" s="5"/>
-      <c r="DQ21" s="8"/>
+      <c r="DQ21" s="9"/>
       <c r="DR21" s="5"/>
-      <c r="DS21" s="8"/>
+      <c r="DS21" s="9"/>
       <c r="DT21" s="5"/>
-      <c r="DU21" s="8"/>
+      <c r="DU21" s="9"/>
       <c r="DV21" s="5"/>
-      <c r="DW21" s="8"/>
+      <c r="DW21" s="9"/>
       <c r="DX21" s="5"/>
+      <c r="DY21" s="12"/>
     </row>
     <row r="22">
-      <c r="B22" s="28"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="25" t="inlineStr">
+      <c r="B22" s="12"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="26" t="inlineStr">
         <is>
           <t>交通量配分道路網の作成</t>
         </is>
       </c>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
       <c r="T22" s="13"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="12"/>
-      <c r="AA22" s="12"/>
-      <c r="AB22" s="12"/>
-      <c r="AC22" s="12"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11"/>
+      <c r="AA22" s="11"/>
+      <c r="AB22" s="11"/>
+      <c r="AC22" s="11"/>
       <c r="AD22" s="13"/>
-      <c r="AE22" s="11"/>
-      <c r="AF22" s="12"/>
-      <c r="AG22" s="12"/>
-      <c r="AH22" s="13"/>
-      <c r="AJ22" s="2" t="inlineStr">
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="11"/>
+      <c r="AG22" s="11"/>
+      <c r="AH22" s="14"/>
+      <c r="AI22" s="9"/>
+      <c r="AJ22" s="8" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="AM22" s="2" t="inlineStr">
+      <c r="AK22" s="4"/>
+      <c r="AL22" s="5"/>
+      <c r="AM22" s="7" t="inlineStr">
         <is>
           <t>2月10日</t>
         </is>
       </c>
-      <c r="AQ22" s="2" t="inlineStr">
+      <c r="AN22" s="4"/>
+      <c r="AO22" s="4"/>
+      <c r="AP22" s="22"/>
+      <c r="AQ22" s="7" t="inlineStr">
         <is>
           <t>4月10日</t>
         </is>
       </c>
-      <c r="AU22" s="11"/>
-      <c r="AV22" s="12"/>
-      <c r="AW22" s="12"/>
-      <c r="AX22" s="33" t="inlineStr">
+      <c r="AR22" s="4"/>
+      <c r="AS22" s="4"/>
+      <c r="AT22" s="5"/>
+      <c r="AU22" s="6"/>
+      <c r="AV22" s="11"/>
+      <c r="AW22" s="11"/>
+      <c r="AX22" s="34" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="AY22" s="11"/>
+      <c r="AY22" s="6"/>
       <c r="AZ22" s="13"/>
-      <c r="BA22" s="11"/>
+      <c r="BA22" s="6"/>
       <c r="BB22" s="13"/>
-      <c r="BC22" s="11"/>
+      <c r="BC22" s="6"/>
       <c r="BD22" s="13"/>
-      <c r="BE22" s="11"/>
+      <c r="BE22" s="6"/>
       <c r="BF22" s="13"/>
-      <c r="BW22" s="11"/>
+      <c r="BG22" s="9"/>
+      <c r="BH22" s="9"/>
+      <c r="BI22" s="5"/>
+      <c r="BJ22" s="9"/>
+      <c r="BK22" s="5"/>
+      <c r="BL22" s="9"/>
+      <c r="BM22" s="5"/>
+      <c r="BN22" s="9"/>
+      <c r="BO22" s="22"/>
+      <c r="BP22" s="9"/>
+      <c r="BQ22" s="5"/>
+      <c r="BR22" s="9"/>
+      <c r="BS22" s="9"/>
+      <c r="BT22" s="5"/>
+      <c r="BU22" s="9"/>
+      <c r="BV22" s="5"/>
+      <c r="BW22" s="6"/>
       <c r="BX22" s="13"/>
-      <c r="BY22" s="11"/>
+      <c r="BY22" s="6"/>
       <c r="BZ22" s="13"/>
-      <c r="CA22" s="11"/>
-      <c r="CB22" s="12"/>
-      <c r="CC22" s="13"/>
-      <c r="CD22" s="20"/>
-      <c r="CE22" s="11"/>
-      <c r="CF22" s="12"/>
+      <c r="CA22" s="6"/>
+      <c r="CB22" s="11"/>
+      <c r="CC22" s="14"/>
+      <c r="CD22" s="14"/>
+      <c r="CE22" s="6"/>
+      <c r="CF22" s="6"/>
       <c r="CG22" s="13"/>
-      <c r="CH22" s="11"/>
+      <c r="CH22" s="6"/>
       <c r="CI22" s="13"/>
-      <c r="CJ22" s="11"/>
-      <c r="CK22" s="12"/>
-      <c r="CL22" s="13"/>
-      <c r="CZ22" s="11"/>
+      <c r="CJ22" s="6"/>
+      <c r="CK22" s="11"/>
+      <c r="CL22" s="14"/>
+      <c r="CM22" s="9"/>
+      <c r="CN22" s="22"/>
+      <c r="CO22" s="9"/>
+      <c r="CP22" s="5"/>
+      <c r="CQ22" s="9"/>
+      <c r="CR22" s="5"/>
+      <c r="CS22" s="9"/>
+      <c r="CT22" s="5"/>
+      <c r="CU22" s="9"/>
+      <c r="CV22" s="5"/>
+      <c r="CW22" s="9"/>
+      <c r="CX22" s="4"/>
+      <c r="CY22" s="22"/>
+      <c r="CZ22" s="6"/>
       <c r="DA22" s="13"/>
-      <c r="DB22" s="11"/>
+      <c r="DB22" s="6"/>
       <c r="DC22" s="13"/>
-      <c r="DD22" s="11"/>
+      <c r="DD22" s="6"/>
       <c r="DE22" s="13"/>
-      <c r="DF22" s="11"/>
+      <c r="DF22" s="6"/>
       <c r="DG22" s="13"/>
-      <c r="DH22" s="11"/>
-      <c r="DI22" s="12"/>
-      <c r="DJ22" s="13"/>
-      <c r="DK22" s="11"/>
+      <c r="DH22" s="6"/>
+      <c r="DI22" s="11"/>
+      <c r="DJ22" s="14"/>
+      <c r="DK22" s="6"/>
       <c r="DL22" s="13"/>
-      <c r="DM22" s="11"/>
+      <c r="DM22" s="6"/>
       <c r="DN22" s="13"/>
-      <c r="DO22" s="11"/>
+      <c r="DO22" s="6"/>
       <c r="DP22" s="13"/>
-      <c r="DQ22" s="11"/>
+      <c r="DQ22" s="6"/>
       <c r="DR22" s="13"/>
-      <c r="DS22" s="11"/>
+      <c r="DS22" s="6"/>
       <c r="DT22" s="13"/>
-      <c r="DU22" s="11"/>
+      <c r="DU22" s="6"/>
       <c r="DV22" s="13"/>
-      <c r="DW22" s="11"/>
+      <c r="DW22" s="6"/>
       <c r="DX22" s="13"/>
+      <c r="DY22" s="12"/>
     </row>
     <row r="23">
-      <c r="B23" s="15"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="19" t="inlineStr">
+      <c r="B23" s="16"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="21" t="inlineStr">
         <is>
           <t>交通量配分道路網の作成</t>
         </is>
       </c>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
-      <c r="X23" s="16"/>
-      <c r="Y23" s="16"/>
-      <c r="Z23" s="16"/>
-      <c r="AA23" s="16"/>
-      <c r="AB23" s="16"/>
-      <c r="AC23" s="16"/>
-      <c r="AD23" s="18"/>
-      <c r="AE23" s="15"/>
-      <c r="AF23" s="17" t="inlineStr">
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="19"/>
+      <c r="U23" s="16"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="Y23" s="17"/>
+      <c r="Z23" s="17"/>
+      <c r="AA23" s="17"/>
+      <c r="AB23" s="17"/>
+      <c r="AC23" s="17"/>
+      <c r="AD23" s="19"/>
+      <c r="AE23" s="16"/>
+      <c r="AF23" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="AG23" s="16"/>
-      <c r="AH23" s="18"/>
-      <c r="AI23" s="8"/>
-      <c r="AJ23" s="7" t="inlineStr">
+      <c r="AG23" s="17"/>
+      <c r="AH23" s="20"/>
+      <c r="AI23" s="9"/>
+      <c r="AJ23" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
       <c r="AK23" s="4"/>
       <c r="AL23" s="5"/>
-      <c r="AM23" s="6" t="inlineStr">
+      <c r="AM23" s="7" t="inlineStr">
         <is>
           <t>2月10日</t>
         </is>
       </c>
       <c r="AN23" s="4"/>
       <c r="AO23" s="4"/>
-      <c r="AP23" s="5"/>
-      <c r="AQ23" s="6" t="inlineStr">
+      <c r="AP23" s="22"/>
+      <c r="AQ23" s="7" t="inlineStr">
         <is>
           <t>4月20日</t>
         </is>
@@ -3184,279 +3445,295 @@
       <c r="AR23" s="4"/>
       <c r="AS23" s="4"/>
       <c r="AT23" s="5"/>
-      <c r="AU23" s="15"/>
-      <c r="AV23" s="16"/>
-      <c r="AW23" s="16"/>
-      <c r="AX23" s="26" t="inlineStr">
+      <c r="AU23" s="9"/>
+      <c r="AV23" s="17"/>
+      <c r="AW23" s="17"/>
+      <c r="AX23" s="30" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="AY23" s="15"/>
-      <c r="AZ23" s="18"/>
-      <c r="BA23" s="15"/>
-      <c r="BB23" s="18"/>
-      <c r="BC23" s="15"/>
-      <c r="BD23" s="18"/>
-      <c r="BE23" s="15"/>
-      <c r="BF23" s="18"/>
-      <c r="BG23" s="8"/>
-      <c r="BH23" s="4"/>
+      <c r="AY23" s="16"/>
+      <c r="AZ23" s="19"/>
+      <c r="BA23" s="16"/>
+      <c r="BB23" s="19"/>
+      <c r="BC23" s="16"/>
+      <c r="BD23" s="19"/>
+      <c r="BE23" s="16"/>
+      <c r="BF23" s="19"/>
+      <c r="BG23" s="9"/>
+      <c r="BH23" s="9"/>
       <c r="BI23" s="5"/>
-      <c r="BJ23" s="8"/>
+      <c r="BJ23" s="9"/>
       <c r="BK23" s="5"/>
-      <c r="BL23" s="8"/>
+      <c r="BL23" s="9"/>
       <c r="BM23" s="5"/>
-      <c r="BN23" s="8"/>
+      <c r="BN23" s="9"/>
       <c r="BO23" s="5"/>
-      <c r="BP23" s="8"/>
+      <c r="BP23" s="9"/>
       <c r="BQ23" s="5"/>
-      <c r="BR23" s="8"/>
-      <c r="BS23" s="4"/>
+      <c r="BR23" s="9"/>
+      <c r="BS23" s="9"/>
       <c r="BT23" s="5"/>
-      <c r="BU23" s="8"/>
+      <c r="BU23" s="9"/>
       <c r="BV23" s="5"/>
-      <c r="BW23" s="15"/>
-      <c r="BX23" s="18"/>
-      <c r="BY23" s="15"/>
-      <c r="BZ23" s="18"/>
-      <c r="CA23" s="15"/>
-      <c r="CB23" s="16"/>
-      <c r="CC23" s="18"/>
-      <c r="CD23" s="21"/>
-      <c r="CE23" s="15"/>
+      <c r="BW23" s="9"/>
+      <c r="BX23" s="19"/>
+      <c r="BY23" s="16"/>
+      <c r="BZ23" s="19"/>
+      <c r="CA23" s="16"/>
+      <c r="CB23" s="17"/>
+      <c r="CC23" s="20"/>
+      <c r="CD23" s="20"/>
+      <c r="CE23" s="16"/>
       <c r="CF23" s="16"/>
-      <c r="CG23" s="18"/>
-      <c r="CH23" s="15"/>
-      <c r="CI23" s="18"/>
-      <c r="CJ23" s="15"/>
-      <c r="CK23" s="16"/>
-      <c r="CL23" s="18"/>
-      <c r="CM23" s="8"/>
-      <c r="CN23" s="5"/>
-      <c r="CO23" s="8"/>
+      <c r="CG23" s="19"/>
+      <c r="CH23" s="16"/>
+      <c r="CI23" s="19"/>
+      <c r="CJ23" s="16"/>
+      <c r="CK23" s="17"/>
+      <c r="CL23" s="20"/>
+      <c r="CM23" s="9"/>
+      <c r="CN23" s="22"/>
+      <c r="CO23" s="9"/>
       <c r="CP23" s="5"/>
-      <c r="CQ23" s="8"/>
+      <c r="CQ23" s="9"/>
       <c r="CR23" s="5"/>
-      <c r="CS23" s="8"/>
+      <c r="CS23" s="9"/>
       <c r="CT23" s="5"/>
-      <c r="CU23" s="8"/>
+      <c r="CU23" s="9"/>
       <c r="CV23" s="5"/>
-      <c r="CW23" s="8"/>
+      <c r="CW23" s="9"/>
       <c r="CX23" s="4"/>
-      <c r="CY23" s="5"/>
-      <c r="CZ23" s="15"/>
-      <c r="DA23" s="18"/>
-      <c r="DB23" s="15"/>
-      <c r="DC23" s="18"/>
-      <c r="DD23" s="15"/>
-      <c r="DE23" s="18"/>
-      <c r="DF23" s="15"/>
-      <c r="DG23" s="18"/>
-      <c r="DH23" s="15"/>
-      <c r="DI23" s="16"/>
-      <c r="DJ23" s="18"/>
-      <c r="DK23" s="15"/>
-      <c r="DL23" s="18"/>
-      <c r="DM23" s="15"/>
-      <c r="DN23" s="18"/>
-      <c r="DO23" s="15"/>
-      <c r="DP23" s="18"/>
-      <c r="DQ23" s="15"/>
-      <c r="DR23" s="18"/>
-      <c r="DS23" s="15"/>
-      <c r="DT23" s="18"/>
-      <c r="DU23" s="15"/>
-      <c r="DV23" s="18"/>
-      <c r="DW23" s="15"/>
-      <c r="DX23" s="18"/>
+      <c r="CY23" s="22"/>
+      <c r="CZ23" s="9"/>
+      <c r="DA23" s="19"/>
+      <c r="DB23" s="16"/>
+      <c r="DC23" s="19"/>
+      <c r="DD23" s="16"/>
+      <c r="DE23" s="19"/>
+      <c r="DF23" s="16"/>
+      <c r="DG23" s="19"/>
+      <c r="DH23" s="16"/>
+      <c r="DI23" s="17"/>
+      <c r="DJ23" s="20"/>
+      <c r="DK23" s="16"/>
+      <c r="DL23" s="19"/>
+      <c r="DM23" s="16"/>
+      <c r="DN23" s="19"/>
+      <c r="DO23" s="16"/>
+      <c r="DP23" s="19"/>
+      <c r="DQ23" s="16"/>
+      <c r="DR23" s="19"/>
+      <c r="DS23" s="16"/>
+      <c r="DT23" s="19"/>
+      <c r="DU23" s="16"/>
+      <c r="DV23" s="19"/>
+      <c r="DW23" s="16"/>
+      <c r="DX23" s="19"/>
+      <c r="DY23" s="12"/>
     </row>
     <row r="24">
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
       <c r="K24" s="13"/>
-      <c r="L24" s="25" t="inlineStr">
+      <c r="L24" s="26" t="inlineStr">
         <is>
           <t>現況配分計算</t>
         </is>
       </c>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
       <c r="T24" s="13"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="12"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="12"/>
-      <c r="Z24" s="12"/>
-      <c r="AA24" s="12"/>
-      <c r="AB24" s="12"/>
-      <c r="AC24" s="12"/>
+      <c r="U24" s="6"/>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="11"/>
+      <c r="AA24" s="11"/>
+      <c r="AB24" s="11"/>
+      <c r="AC24" s="11"/>
       <c r="AD24" s="13"/>
-      <c r="AE24" s="11"/>
-      <c r="AF24" s="12"/>
-      <c r="AG24" s="12"/>
-      <c r="AH24" s="13"/>
-      <c r="AJ24" s="2" t="inlineStr">
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="11"/>
+      <c r="AG24" s="11"/>
+      <c r="AH24" s="14"/>
+      <c r="AI24" s="9"/>
+      <c r="AJ24" s="8" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="AM24" s="2" t="inlineStr">
+      <c r="AK24" s="4"/>
+      <c r="AL24" s="5"/>
+      <c r="AM24" s="7" t="inlineStr">
         <is>
           <t>4月1日</t>
         </is>
       </c>
-      <c r="AQ24" s="2" t="inlineStr">
+      <c r="AN24" s="4"/>
+      <c r="AO24" s="4"/>
+      <c r="AP24" s="22"/>
+      <c r="AQ24" s="7" t="inlineStr">
         <is>
           <t>4月15日</t>
         </is>
       </c>
-      <c r="AU24" s="11"/>
-      <c r="AV24" s="12"/>
-      <c r="AW24" s="12"/>
-      <c r="AX24" s="33" t="inlineStr">
+      <c r="AR24" s="4"/>
+      <c r="AS24" s="4"/>
+      <c r="AT24" s="5"/>
+      <c r="AU24" s="6"/>
+      <c r="AV24" s="11"/>
+      <c r="AW24" s="11"/>
+      <c r="AX24" s="34" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AY24" s="11"/>
+      <c r="AY24" s="6"/>
       <c r="AZ24" s="13"/>
-      <c r="BA24" s="11"/>
+      <c r="BA24" s="6"/>
       <c r="BB24" s="13"/>
-      <c r="BC24" s="11"/>
+      <c r="BC24" s="6"/>
       <c r="BD24" s="13"/>
-      <c r="BE24" s="11"/>
+      <c r="BE24" s="6"/>
       <c r="BF24" s="13"/>
-      <c r="BG24" s="11"/>
-      <c r="BH24" s="12"/>
+      <c r="BG24" s="6"/>
+      <c r="BH24" s="6"/>
       <c r="BI24" s="13"/>
-      <c r="BJ24" s="11"/>
+      <c r="BJ24" s="6"/>
       <c r="BK24" s="13"/>
-      <c r="BL24" s="11"/>
+      <c r="BL24" s="6"/>
       <c r="BM24" s="13"/>
-      <c r="BN24" s="11"/>
+      <c r="BN24" s="6"/>
       <c r="BO24" s="13"/>
-      <c r="BP24" s="11"/>
+      <c r="BP24" s="6"/>
       <c r="BQ24" s="13"/>
-      <c r="BW24" s="11"/>
+      <c r="BR24" s="9"/>
+      <c r="BS24" s="9"/>
+      <c r="BT24" s="5"/>
+      <c r="BU24" s="9"/>
+      <c r="BV24" s="22"/>
+      <c r="BW24" s="6"/>
       <c r="BX24" s="13"/>
-      <c r="BY24" s="11"/>
+      <c r="BY24" s="6"/>
       <c r="BZ24" s="13"/>
-      <c r="CA24" s="11"/>
-      <c r="CB24" s="12"/>
-      <c r="CC24" s="13"/>
-      <c r="CD24" s="20"/>
-      <c r="CE24" s="11"/>
-      <c r="CF24" s="12"/>
+      <c r="CA24" s="6"/>
+      <c r="CB24" s="11"/>
+      <c r="CC24" s="14"/>
+      <c r="CD24" s="14"/>
+      <c r="CE24" s="6"/>
+      <c r="CF24" s="6"/>
       <c r="CG24" s="13"/>
-      <c r="CH24" s="11"/>
+      <c r="CH24" s="6"/>
       <c r="CI24" s="13"/>
-      <c r="CJ24" s="11"/>
-      <c r="CK24" s="12"/>
-      <c r="CL24" s="13"/>
-      <c r="CM24" s="11"/>
-      <c r="CN24" s="13"/>
-      <c r="CO24" s="11"/>
+      <c r="CJ24" s="6"/>
+      <c r="CK24" s="11"/>
+      <c r="CL24" s="14"/>
+      <c r="CM24" s="6"/>
+      <c r="CN24" s="14"/>
+      <c r="CO24" s="6"/>
       <c r="CP24" s="13"/>
-      <c r="CQ24" s="11"/>
+      <c r="CQ24" s="6"/>
       <c r="CR24" s="13"/>
-      <c r="CS24" s="11"/>
+      <c r="CS24" s="6"/>
       <c r="CT24" s="13"/>
-      <c r="CU24" s="11"/>
+      <c r="CU24" s="6"/>
       <c r="CV24" s="13"/>
-      <c r="CW24" s="11"/>
-      <c r="CX24" s="12"/>
-      <c r="CY24" s="13"/>
-      <c r="CZ24" s="11"/>
+      <c r="CW24" s="6"/>
+      <c r="CX24" s="11"/>
+      <c r="CY24" s="14"/>
+      <c r="CZ24" s="6"/>
       <c r="DA24" s="13"/>
-      <c r="DB24" s="11"/>
+      <c r="DB24" s="6"/>
       <c r="DC24" s="13"/>
-      <c r="DD24" s="11"/>
+      <c r="DD24" s="6"/>
       <c r="DE24" s="13"/>
-      <c r="DF24" s="11"/>
+      <c r="DF24" s="6"/>
       <c r="DG24" s="13"/>
-      <c r="DH24" s="11"/>
-      <c r="DI24" s="12"/>
-      <c r="DJ24" s="13"/>
-      <c r="DK24" s="11"/>
+      <c r="DH24" s="6"/>
+      <c r="DI24" s="11"/>
+      <c r="DJ24" s="14"/>
+      <c r="DK24" s="6"/>
       <c r="DL24" s="13"/>
-      <c r="DM24" s="11"/>
+      <c r="DM24" s="6"/>
       <c r="DN24" s="13"/>
-      <c r="DO24" s="11"/>
+      <c r="DO24" s="6"/>
       <c r="DP24" s="13"/>
-      <c r="DQ24" s="11"/>
+      <c r="DQ24" s="6"/>
       <c r="DR24" s="13"/>
-      <c r="DS24" s="11"/>
+      <c r="DS24" s="6"/>
       <c r="DT24" s="13"/>
-      <c r="DU24" s="11"/>
+      <c r="DU24" s="6"/>
       <c r="DV24" s="13"/>
-      <c r="DW24" s="11"/>
+      <c r="DW24" s="6"/>
       <c r="DX24" s="13"/>
+      <c r="DY24" s="12"/>
     </row>
     <row r="25">
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>交通量配分用データの作成現況配分計算</t>
         </is>
       </c>
-      <c r="K25" s="29"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="16"/>
-      <c r="T25" s="18"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="16"/>
-      <c r="Z25" s="16"/>
-      <c r="AA25" s="16"/>
-      <c r="AB25" s="16"/>
-      <c r="AC25" s="16"/>
-      <c r="AD25" s="18"/>
-      <c r="AE25" s="15"/>
-      <c r="AF25" s="17" t="inlineStr">
+      <c r="K25" s="28"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="16"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+      <c r="Y25" s="17"/>
+      <c r="Z25" s="17"/>
+      <c r="AA25" s="17"/>
+      <c r="AB25" s="17"/>
+      <c r="AC25" s="17"/>
+      <c r="AD25" s="19"/>
+      <c r="AE25" s="16"/>
+      <c r="AF25" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="AG25" s="16"/>
-      <c r="AH25" s="18"/>
-      <c r="AI25" s="8"/>
-      <c r="AJ25" s="7" t="inlineStr">
+      <c r="AG25" s="17"/>
+      <c r="AH25" s="20"/>
+      <c r="AI25" s="9"/>
+      <c r="AJ25" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
       <c r="AK25" s="4"/>
       <c r="AL25" s="5"/>
-      <c r="AM25" s="6" t="inlineStr">
+      <c r="AM25" s="7" t="inlineStr">
         <is>
           <t>4月1日</t>
         </is>
       </c>
       <c r="AN25" s="4"/>
       <c r="AO25" s="4"/>
-      <c r="AP25" s="5"/>
-      <c r="AQ25" s="6" t="inlineStr">
+      <c r="AP25" s="22"/>
+      <c r="AQ25" s="7" t="inlineStr">
         <is>
           <t>4月18日</t>
         </is>
@@ -3464,97 +3741,98 @@
       <c r="AR25" s="4"/>
       <c r="AS25" s="4"/>
       <c r="AT25" s="5"/>
-      <c r="AU25" s="15"/>
-      <c r="AV25" s="16"/>
-      <c r="AW25" s="16"/>
-      <c r="AX25" s="26" t="inlineStr">
+      <c r="AU25" s="9"/>
+      <c r="AV25" s="17"/>
+      <c r="AW25" s="17"/>
+      <c r="AX25" s="30" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="AY25" s="15"/>
-      <c r="AZ25" s="18"/>
-      <c r="BA25" s="15"/>
-      <c r="BB25" s="18"/>
-      <c r="BC25" s="15"/>
-      <c r="BD25" s="18"/>
-      <c r="BE25" s="15"/>
-      <c r="BF25" s="18"/>
-      <c r="BG25" s="15"/>
+      <c r="AY25" s="16"/>
+      <c r="AZ25" s="19"/>
+      <c r="BA25" s="16"/>
+      <c r="BB25" s="19"/>
+      <c r="BC25" s="16"/>
+      <c r="BD25" s="19"/>
+      <c r="BE25" s="16"/>
+      <c r="BF25" s="19"/>
+      <c r="BG25" s="16"/>
       <c r="BH25" s="16"/>
-      <c r="BI25" s="18"/>
-      <c r="BJ25" s="15"/>
-      <c r="BK25" s="18"/>
-      <c r="BL25" s="15"/>
-      <c r="BM25" s="18"/>
-      <c r="BN25" s="15"/>
-      <c r="BO25" s="18"/>
-      <c r="BP25" s="15"/>
-      <c r="BQ25" s="18"/>
-      <c r="BR25" s="8"/>
-      <c r="BS25" s="4"/>
+      <c r="BI25" s="19"/>
+      <c r="BJ25" s="16"/>
+      <c r="BK25" s="19"/>
+      <c r="BL25" s="16"/>
+      <c r="BM25" s="19"/>
+      <c r="BN25" s="16"/>
+      <c r="BO25" s="19"/>
+      <c r="BP25" s="16"/>
+      <c r="BQ25" s="19"/>
+      <c r="BR25" s="9"/>
+      <c r="BS25" s="9"/>
       <c r="BT25" s="5"/>
-      <c r="BU25" s="8"/>
-      <c r="BV25" s="5"/>
-      <c r="BW25" s="15"/>
-      <c r="BX25" s="18"/>
-      <c r="BY25" s="15"/>
-      <c r="BZ25" s="18"/>
-      <c r="CA25" s="15"/>
-      <c r="CB25" s="16"/>
-      <c r="CC25" s="18"/>
-      <c r="CD25" s="21"/>
-      <c r="CE25" s="15"/>
+      <c r="BU25" s="9"/>
+      <c r="BV25" s="22"/>
+      <c r="BW25" s="16"/>
+      <c r="BX25" s="19"/>
+      <c r="BY25" s="16"/>
+      <c r="BZ25" s="19"/>
+      <c r="CA25" s="16"/>
+      <c r="CB25" s="17"/>
+      <c r="CC25" s="20"/>
+      <c r="CD25" s="20"/>
+      <c r="CE25" s="16"/>
       <c r="CF25" s="16"/>
-      <c r="CG25" s="18"/>
-      <c r="CH25" s="15"/>
-      <c r="CI25" s="18"/>
-      <c r="CJ25" s="15"/>
-      <c r="CK25" s="16"/>
-      <c r="CL25" s="18"/>
-      <c r="CM25" s="15"/>
-      <c r="CN25" s="18"/>
-      <c r="CO25" s="15"/>
-      <c r="CP25" s="18"/>
-      <c r="CQ25" s="15"/>
-      <c r="CR25" s="18"/>
-      <c r="CS25" s="15"/>
-      <c r="CT25" s="18"/>
-      <c r="CU25" s="15"/>
-      <c r="CV25" s="18"/>
-      <c r="CW25" s="15"/>
-      <c r="CX25" s="16"/>
-      <c r="CY25" s="18"/>
-      <c r="CZ25" s="15"/>
-      <c r="DA25" s="18"/>
-      <c r="DB25" s="15"/>
-      <c r="DC25" s="18"/>
-      <c r="DD25" s="15"/>
-      <c r="DE25" s="18"/>
-      <c r="DF25" s="15"/>
-      <c r="DG25" s="18"/>
-      <c r="DH25" s="15"/>
-      <c r="DI25" s="16"/>
-      <c r="DJ25" s="18"/>
-      <c r="DK25" s="15"/>
-      <c r="DL25" s="18"/>
-      <c r="DM25" s="15"/>
-      <c r="DN25" s="18"/>
-      <c r="DO25" s="15"/>
-      <c r="DP25" s="18"/>
-      <c r="DQ25" s="15"/>
-      <c r="DR25" s="18"/>
-      <c r="DS25" s="15"/>
-      <c r="DT25" s="18"/>
-      <c r="DU25" s="15"/>
-      <c r="DV25" s="18"/>
-      <c r="DW25" s="15"/>
-      <c r="DX25" s="18"/>
+      <c r="CG25" s="19"/>
+      <c r="CH25" s="16"/>
+      <c r="CI25" s="19"/>
+      <c r="CJ25" s="16"/>
+      <c r="CK25" s="17"/>
+      <c r="CL25" s="20"/>
+      <c r="CM25" s="16"/>
+      <c r="CN25" s="20"/>
+      <c r="CO25" s="16"/>
+      <c r="CP25" s="19"/>
+      <c r="CQ25" s="16"/>
+      <c r="CR25" s="19"/>
+      <c r="CS25" s="16"/>
+      <c r="CT25" s="19"/>
+      <c r="CU25" s="16"/>
+      <c r="CV25" s="19"/>
+      <c r="CW25" s="16"/>
+      <c r="CX25" s="17"/>
+      <c r="CY25" s="20"/>
+      <c r="CZ25" s="16"/>
+      <c r="DA25" s="19"/>
+      <c r="DB25" s="16"/>
+      <c r="DC25" s="19"/>
+      <c r="DD25" s="16"/>
+      <c r="DE25" s="19"/>
+      <c r="DF25" s="16"/>
+      <c r="DG25" s="19"/>
+      <c r="DH25" s="16"/>
+      <c r="DI25" s="17"/>
+      <c r="DJ25" s="20"/>
+      <c r="DK25" s="16"/>
+      <c r="DL25" s="19"/>
+      <c r="DM25" s="16"/>
+      <c r="DN25" s="19"/>
+      <c r="DO25" s="16"/>
+      <c r="DP25" s="19"/>
+      <c r="DQ25" s="16"/>
+      <c r="DR25" s="19"/>
+      <c r="DS25" s="16"/>
+      <c r="DT25" s="19"/>
+      <c r="DU25" s="16"/>
+      <c r="DV25" s="19"/>
+      <c r="DW25" s="16"/>
+      <c r="DX25" s="19"/>
+      <c r="DY25" s="12"/>
     </row>
     <row r="26">
-      <c r="B26" s="28"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="6" t="inlineStr">
+      <c r="B26" s="12"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>将来配分計算</t>
         </is>
@@ -3567,7 +3845,7 @@
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
       <c r="T26" s="5"/>
-      <c r="U26" s="8"/>
+      <c r="U26" s="9"/>
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
       <c r="X26" s="4"/>
@@ -3577,158 +3855,173 @@
       <c r="AB26" s="4"/>
       <c r="AC26" s="4"/>
       <c r="AD26" s="5"/>
-      <c r="AE26" s="8"/>
-      <c r="AF26" s="35" t="inlineStr">
+      <c r="AE26" s="9"/>
+      <c r="AF26" s="36" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
       <c r="AG26" s="4"/>
-      <c r="AH26" s="5"/>
-      <c r="AJ26" s="2" t="inlineStr">
+      <c r="AH26" s="22"/>
+      <c r="AI26" s="9"/>
+      <c r="AJ26" s="8" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="AM26" s="2" t="inlineStr">
+      <c r="AK26" s="4"/>
+      <c r="AL26" s="5"/>
+      <c r="AM26" s="7" t="inlineStr">
         <is>
           <t>4月15日</t>
         </is>
       </c>
-      <c r="AQ26" s="2" t="inlineStr">
+      <c r="AN26" s="4"/>
+      <c r="AO26" s="4"/>
+      <c r="AP26" s="22"/>
+      <c r="AQ26" s="7" t="inlineStr">
         <is>
           <t>8月10日</t>
         </is>
       </c>
-      <c r="AU26" s="8"/>
+      <c r="AR26" s="4"/>
+      <c r="AS26" s="4"/>
+      <c r="AT26" s="5"/>
+      <c r="AU26" s="9"/>
       <c r="AV26" s="4"/>
-      <c r="AW26" s="7" t="inlineStr">
+      <c r="AW26" s="8" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
       <c r="AX26" s="5"/>
-      <c r="AY26" s="8"/>
+      <c r="AY26" s="9"/>
       <c r="AZ26" s="5"/>
-      <c r="BA26" s="8"/>
+      <c r="BA26" s="9"/>
       <c r="BB26" s="5"/>
-      <c r="BC26" s="8"/>
+      <c r="BC26" s="9"/>
       <c r="BD26" s="5"/>
-      <c r="BE26" s="8"/>
+      <c r="BE26" s="9"/>
       <c r="BF26" s="5"/>
-      <c r="BG26" s="8"/>
-      <c r="BH26" s="4"/>
+      <c r="BG26" s="9"/>
+      <c r="BH26" s="9"/>
       <c r="BI26" s="5"/>
-      <c r="BJ26" s="8"/>
+      <c r="BJ26" s="9"/>
       <c r="BK26" s="5"/>
-      <c r="BL26" s="8"/>
+      <c r="BL26" s="9"/>
       <c r="BM26" s="5"/>
-      <c r="BN26" s="8"/>
+      <c r="BN26" s="9"/>
       <c r="BO26" s="5"/>
-      <c r="BP26" s="8"/>
+      <c r="BP26" s="9"/>
       <c r="BQ26" s="5"/>
-      <c r="BW26" s="8"/>
+      <c r="BR26" s="9"/>
+      <c r="BS26" s="9"/>
+      <c r="BT26" s="5"/>
+      <c r="BU26" s="9"/>
+      <c r="BV26" s="22"/>
+      <c r="BW26" s="9"/>
       <c r="BX26" s="5"/>
-      <c r="BY26" s="8"/>
+      <c r="BY26" s="9"/>
       <c r="BZ26" s="5"/>
-      <c r="CA26" s="8"/>
+      <c r="CA26" s="9"/>
       <c r="CB26" s="4"/>
-      <c r="CC26" s="5"/>
-      <c r="CD26" s="23"/>
-      <c r="CE26" s="8"/>
-      <c r="CF26" s="4"/>
+      <c r="CC26" s="22"/>
+      <c r="CD26" s="22"/>
+      <c r="CE26" s="9"/>
+      <c r="CF26" s="9"/>
       <c r="CG26" s="5"/>
-      <c r="CH26" s="8"/>
+      <c r="CH26" s="9"/>
       <c r="CI26" s="5"/>
-      <c r="CJ26" s="8"/>
+      <c r="CJ26" s="9"/>
       <c r="CK26" s="4"/>
-      <c r="CL26" s="5"/>
-      <c r="CM26" s="8"/>
-      <c r="CN26" s="5"/>
-      <c r="CO26" s="8"/>
+      <c r="CL26" s="22"/>
+      <c r="CM26" s="9"/>
+      <c r="CN26" s="22"/>
+      <c r="CO26" s="9"/>
       <c r="CP26" s="5"/>
-      <c r="CQ26" s="8"/>
+      <c r="CQ26" s="9"/>
       <c r="CR26" s="5"/>
-      <c r="CS26" s="8"/>
+      <c r="CS26" s="9"/>
       <c r="CT26" s="5"/>
-      <c r="CU26" s="8"/>
+      <c r="CU26" s="9"/>
       <c r="CV26" s="5"/>
-      <c r="CW26" s="8"/>
+      <c r="CW26" s="9"/>
       <c r="CX26" s="4"/>
-      <c r="CY26" s="5"/>
-      <c r="CZ26" s="8"/>
+      <c r="CY26" s="22"/>
+      <c r="CZ26" s="9"/>
       <c r="DA26" s="5"/>
-      <c r="DB26" s="8"/>
+      <c r="DB26" s="9"/>
       <c r="DC26" s="5"/>
-      <c r="DD26" s="8"/>
+      <c r="DD26" s="9"/>
       <c r="DE26" s="5"/>
-      <c r="DF26" s="8"/>
+      <c r="DF26" s="9"/>
       <c r="DG26" s="5"/>
-      <c r="DH26" s="8"/>
+      <c r="DH26" s="9"/>
       <c r="DI26" s="4"/>
-      <c r="DJ26" s="5"/>
-      <c r="DK26" s="8"/>
+      <c r="DJ26" s="22"/>
+      <c r="DK26" s="9"/>
       <c r="DL26" s="5"/>
-      <c r="DM26" s="8"/>
+      <c r="DM26" s="9"/>
       <c r="DN26" s="5"/>
-      <c r="DO26" s="8"/>
+      <c r="DO26" s="9"/>
       <c r="DP26" s="5"/>
-      <c r="DQ26" s="8"/>
+      <c r="DQ26" s="9"/>
       <c r="DR26" s="5"/>
-      <c r="DS26" s="8"/>
+      <c r="DS26" s="9"/>
       <c r="DT26" s="5"/>
-      <c r="DU26" s="8"/>
+      <c r="DU26" s="9"/>
       <c r="DV26" s="5"/>
-      <c r="DW26" s="8"/>
+      <c r="DW26" s="9"/>
       <c r="DX26" s="5"/>
+      <c r="DY26" s="12"/>
     </row>
     <row r="27">
-      <c r="B27" s="28"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="25" t="inlineStr">
+      <c r="B27" s="12"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="26" t="inlineStr">
         <is>
           <t>集計整理</t>
         </is>
       </c>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
       <c r="T27" s="13"/>
-      <c r="U27" s="11"/>
-      <c r="V27" s="12"/>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12"/>
-      <c r="Y27" s="12"/>
-      <c r="Z27" s="12"/>
-      <c r="AA27" s="12"/>
-      <c r="AB27" s="12"/>
-      <c r="AC27" s="12"/>
+      <c r="U27" s="6"/>
+      <c r="V27" s="11"/>
+      <c r="W27" s="11"/>
+      <c r="X27" s="11"/>
+      <c r="Y27" s="11"/>
+      <c r="Z27" s="11"/>
+      <c r="AA27" s="11"/>
+      <c r="AB27" s="11"/>
+      <c r="AC27" s="11"/>
       <c r="AD27" s="13"/>
-      <c r="AE27" s="11"/>
-      <c r="AF27" s="12"/>
-      <c r="AG27" s="12"/>
-      <c r="AH27" s="13"/>
-      <c r="AI27" s="8"/>
-      <c r="AJ27" s="7" t="inlineStr">
+      <c r="AE27" s="6"/>
+      <c r="AF27" s="11"/>
+      <c r="AG27" s="11"/>
+      <c r="AH27" s="14"/>
+      <c r="AI27" s="9"/>
+      <c r="AJ27" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
       <c r="AK27" s="4"/>
       <c r="AL27" s="5"/>
-      <c r="AM27" s="6" t="inlineStr">
+      <c r="AM27" s="7" t="inlineStr">
         <is>
           <t>4月15日</t>
         </is>
       </c>
       <c r="AN27" s="4"/>
       <c r="AO27" s="4"/>
-      <c r="AP27" s="5"/>
-      <c r="AQ27" s="6" t="inlineStr">
+      <c r="AP27" s="22"/>
+      <c r="AQ27" s="7" t="inlineStr">
         <is>
           <t>9月20日</t>
         </is>
@@ -3736,253 +4029,275 @@
       <c r="AR27" s="4"/>
       <c r="AS27" s="4"/>
       <c r="AT27" s="5"/>
-      <c r="AU27" s="11"/>
-      <c r="AV27" s="12"/>
-      <c r="AW27" s="12"/>
+      <c r="AU27" s="6"/>
+      <c r="AV27" s="11"/>
+      <c r="AW27" s="11"/>
       <c r="AX27" s="13"/>
-      <c r="AY27" s="11"/>
+      <c r="AY27" s="6"/>
       <c r="AZ27" s="13"/>
-      <c r="BA27" s="11"/>
+      <c r="BA27" s="6"/>
       <c r="BB27" s="13"/>
-      <c r="BC27" s="11"/>
+      <c r="BC27" s="6"/>
       <c r="BD27" s="13"/>
-      <c r="BE27" s="11"/>
+      <c r="BE27" s="6"/>
       <c r="BF27" s="13"/>
-      <c r="BG27" s="11"/>
-      <c r="BH27" s="12"/>
+      <c r="BG27" s="6"/>
+      <c r="BH27" s="6"/>
       <c r="BI27" s="13"/>
-      <c r="BJ27" s="11"/>
+      <c r="BJ27" s="6"/>
       <c r="BK27" s="13"/>
-      <c r="BL27" s="11"/>
+      <c r="BL27" s="6"/>
       <c r="BM27" s="13"/>
-      <c r="BN27" s="11"/>
+      <c r="BN27" s="6"/>
       <c r="BO27" s="13"/>
-      <c r="BP27" s="11"/>
+      <c r="BP27" s="6"/>
       <c r="BQ27" s="13"/>
-      <c r="BR27" s="11"/>
-      <c r="BS27" s="12"/>
+      <c r="BR27" s="6"/>
+      <c r="BS27" s="6"/>
       <c r="BT27" s="13"/>
-      <c r="BU27" s="11"/>
+      <c r="BU27" s="6"/>
       <c r="BV27" s="13"/>
-      <c r="BW27" s="11"/>
-      <c r="BX27" s="13"/>
-      <c r="BY27" s="11"/>
-      <c r="BZ27" s="13"/>
-      <c r="CA27" s="11"/>
-      <c r="CB27" s="12"/>
-      <c r="CC27" s="13"/>
-      <c r="CD27" s="20"/>
-      <c r="CE27" s="11"/>
-      <c r="CF27" s="12"/>
-      <c r="CG27" s="13"/>
-      <c r="CH27" s="11"/>
-      <c r="CI27" s="13"/>
-      <c r="CJ27" s="11"/>
-      <c r="CK27" s="12"/>
-      <c r="CL27" s="13"/>
-      <c r="CM27" s="11"/>
-      <c r="CN27" s="13"/>
-      <c r="CO27" s="11"/>
-      <c r="CP27" s="13"/>
-      <c r="CQ27" s="11"/>
-      <c r="CR27" s="13"/>
-      <c r="CS27" s="11"/>
-      <c r="CT27" s="13"/>
-      <c r="DD27" s="11"/>
+      <c r="BW27" s="9"/>
+      <c r="BX27" s="5"/>
+      <c r="BY27" s="9"/>
+      <c r="BZ27" s="5"/>
+      <c r="CA27" s="9"/>
+      <c r="CB27" s="4"/>
+      <c r="CC27" s="22"/>
+      <c r="CD27" s="22"/>
+      <c r="CE27" s="9"/>
+      <c r="CF27" s="9"/>
+      <c r="CG27" s="5"/>
+      <c r="CH27" s="9"/>
+      <c r="CI27" s="5"/>
+      <c r="CJ27" s="9"/>
+      <c r="CK27" s="4"/>
+      <c r="CL27" s="22"/>
+      <c r="CM27" s="9"/>
+      <c r="CN27" s="22"/>
+      <c r="CO27" s="9"/>
+      <c r="CP27" s="5"/>
+      <c r="CQ27" s="9"/>
+      <c r="CR27" s="5"/>
+      <c r="CS27" s="9"/>
+      <c r="CT27" s="5"/>
+      <c r="CU27" s="9"/>
+      <c r="CV27" s="5"/>
+      <c r="CW27" s="9"/>
+      <c r="CX27" s="4"/>
+      <c r="CY27" s="22"/>
+      <c r="CZ27" s="9"/>
+      <c r="DA27" s="5"/>
+      <c r="DB27" s="9"/>
+      <c r="DC27" s="5"/>
+      <c r="DD27" s="6"/>
       <c r="DE27" s="13"/>
-      <c r="DF27" s="11"/>
+      <c r="DF27" s="6"/>
       <c r="DG27" s="13"/>
-      <c r="DH27" s="11"/>
-      <c r="DI27" s="12"/>
-      <c r="DJ27" s="13"/>
-      <c r="DK27" s="11"/>
+      <c r="DH27" s="6"/>
+      <c r="DI27" s="11"/>
+      <c r="DJ27" s="14"/>
+      <c r="DK27" s="6"/>
       <c r="DL27" s="13"/>
-      <c r="DM27" s="11"/>
+      <c r="DM27" s="6"/>
       <c r="DN27" s="13"/>
-      <c r="DO27" s="11"/>
+      <c r="DO27" s="6"/>
       <c r="DP27" s="13"/>
-      <c r="DQ27" s="11"/>
+      <c r="DQ27" s="6"/>
       <c r="DR27" s="13"/>
-      <c r="DS27" s="11"/>
+      <c r="DS27" s="6"/>
       <c r="DT27" s="13"/>
-      <c r="DU27" s="11"/>
+      <c r="DU27" s="6"/>
       <c r="DV27" s="13"/>
-      <c r="DW27" s="11"/>
+      <c r="DW27" s="6"/>
       <c r="DX27" s="13"/>
+      <c r="DY27" s="12"/>
     </row>
     <row r="28">
-      <c r="B28" s="28"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="19" t="inlineStr">
+      <c r="B28" s="12"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="21" t="inlineStr">
         <is>
           <t>集計整理</t>
         </is>
       </c>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="18"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
-      <c r="Z28" s="16"/>
-      <c r="AA28" s="16"/>
-      <c r="AB28" s="16"/>
-      <c r="AC28" s="16"/>
-      <c r="AD28" s="18"/>
-      <c r="AE28" s="15"/>
-      <c r="AF28" s="36" t="inlineStr">
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="16"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17"/>
+      <c r="AB28" s="17"/>
+      <c r="AC28" s="17"/>
+      <c r="AD28" s="19"/>
+      <c r="AE28" s="16"/>
+      <c r="AF28" s="37" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="AG28" s="16"/>
-      <c r="AH28" s="18"/>
-      <c r="AJ28" s="2" t="inlineStr">
+      <c r="AG28" s="17"/>
+      <c r="AH28" s="20"/>
+      <c r="AI28" s="9"/>
+      <c r="AJ28" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="AU28" s="15"/>
-      <c r="AV28" s="16"/>
-      <c r="AW28" s="16"/>
-      <c r="AX28" s="26" t="inlineStr">
+      <c r="AK28" s="4"/>
+      <c r="AL28" s="5"/>
+      <c r="AM28" s="9"/>
+      <c r="AN28" s="4"/>
+      <c r="AO28" s="4"/>
+      <c r="AP28" s="22"/>
+      <c r="AQ28" s="9"/>
+      <c r="AR28" s="4"/>
+      <c r="AS28" s="4"/>
+      <c r="AT28" s="5"/>
+      <c r="AU28" s="9"/>
+      <c r="AV28" s="17"/>
+      <c r="AW28" s="17"/>
+      <c r="AX28" s="30" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="AY28" s="15"/>
-      <c r="AZ28" s="18"/>
-      <c r="BA28" s="15"/>
-      <c r="BB28" s="18"/>
-      <c r="BC28" s="15"/>
-      <c r="BD28" s="18"/>
-      <c r="BE28" s="15"/>
-      <c r="BF28" s="18"/>
-      <c r="BG28" s="15"/>
+      <c r="AY28" s="16"/>
+      <c r="AZ28" s="19"/>
+      <c r="BA28" s="16"/>
+      <c r="BB28" s="19"/>
+      <c r="BC28" s="16"/>
+      <c r="BD28" s="19"/>
+      <c r="BE28" s="16"/>
+      <c r="BF28" s="19"/>
+      <c r="BG28" s="16"/>
       <c r="BH28" s="16"/>
-      <c r="BI28" s="18"/>
-      <c r="BJ28" s="15"/>
-      <c r="BK28" s="18"/>
-      <c r="BL28" s="15"/>
-      <c r="BM28" s="18"/>
-      <c r="BN28" s="15"/>
-      <c r="BO28" s="18"/>
-      <c r="BP28" s="15"/>
-      <c r="BQ28" s="18"/>
-      <c r="BR28" s="15"/>
+      <c r="BI28" s="19"/>
+      <c r="BJ28" s="16"/>
+      <c r="BK28" s="19"/>
+      <c r="BL28" s="16"/>
+      <c r="BM28" s="19"/>
+      <c r="BN28" s="16"/>
+      <c r="BO28" s="19"/>
+      <c r="BP28" s="16"/>
+      <c r="BQ28" s="19"/>
+      <c r="BR28" s="16"/>
       <c r="BS28" s="16"/>
-      <c r="BT28" s="18"/>
-      <c r="BU28" s="15"/>
-      <c r="BV28" s="18"/>
-      <c r="BW28" s="15"/>
-      <c r="BX28" s="18"/>
-      <c r="BY28" s="15"/>
-      <c r="BZ28" s="18"/>
-      <c r="CA28" s="15"/>
-      <c r="CB28" s="16"/>
-      <c r="CC28" s="18"/>
-      <c r="CD28" s="21"/>
-      <c r="CE28" s="15"/>
+      <c r="BT28" s="19"/>
+      <c r="BU28" s="16"/>
+      <c r="BV28" s="19"/>
+      <c r="BW28" s="16"/>
+      <c r="BX28" s="19"/>
+      <c r="BY28" s="16"/>
+      <c r="BZ28" s="19"/>
+      <c r="CA28" s="16"/>
+      <c r="CB28" s="17"/>
+      <c r="CC28" s="20"/>
+      <c r="CD28" s="20"/>
+      <c r="CE28" s="16"/>
       <c r="CF28" s="16"/>
-      <c r="CG28" s="18"/>
-      <c r="CH28" s="15"/>
-      <c r="CI28" s="18"/>
-      <c r="CJ28" s="15"/>
-      <c r="CK28" s="16"/>
-      <c r="CL28" s="18"/>
-      <c r="CM28" s="15"/>
-      <c r="CN28" s="18"/>
-      <c r="CO28" s="15"/>
-      <c r="CP28" s="18"/>
-      <c r="CQ28" s="15"/>
-      <c r="CR28" s="18"/>
-      <c r="CS28" s="15"/>
-      <c r="CT28" s="18"/>
-      <c r="CU28" s="8"/>
+      <c r="CG28" s="19"/>
+      <c r="CH28" s="16"/>
+      <c r="CI28" s="19"/>
+      <c r="CJ28" s="16"/>
+      <c r="CK28" s="17"/>
+      <c r="CL28" s="20"/>
+      <c r="CM28" s="16"/>
+      <c r="CN28" s="20"/>
+      <c r="CO28" s="16"/>
+      <c r="CP28" s="19"/>
+      <c r="CQ28" s="16"/>
+      <c r="CR28" s="19"/>
+      <c r="CS28" s="16"/>
+      <c r="CT28" s="19"/>
+      <c r="CU28" s="9"/>
       <c r="CV28" s="5"/>
-      <c r="CW28" s="8"/>
+      <c r="CW28" s="9"/>
       <c r="CX28" s="4"/>
-      <c r="CY28" s="5"/>
-      <c r="CZ28" s="8"/>
+      <c r="CY28" s="22"/>
+      <c r="CZ28" s="9"/>
       <c r="DA28" s="5"/>
-      <c r="DB28" s="8"/>
+      <c r="DB28" s="9"/>
       <c r="DC28" s="5"/>
-      <c r="DD28" s="15"/>
-      <c r="DE28" s="18"/>
-      <c r="DF28" s="15"/>
-      <c r="DG28" s="18"/>
-      <c r="DH28" s="15"/>
-      <c r="DI28" s="16"/>
-      <c r="DJ28" s="18"/>
-      <c r="DK28" s="15"/>
-      <c r="DL28" s="18"/>
-      <c r="DM28" s="15"/>
-      <c r="DN28" s="18"/>
-      <c r="DO28" s="15"/>
-      <c r="DP28" s="18"/>
-      <c r="DQ28" s="15"/>
-      <c r="DR28" s="18"/>
-      <c r="DS28" s="15"/>
-      <c r="DT28" s="18"/>
-      <c r="DU28" s="15"/>
-      <c r="DV28" s="18"/>
-      <c r="DW28" s="15"/>
-      <c r="DX28" s="18"/>
+      <c r="DD28" s="9"/>
+      <c r="DE28" s="19"/>
+      <c r="DF28" s="16"/>
+      <c r="DG28" s="19"/>
+      <c r="DH28" s="16"/>
+      <c r="DI28" s="17"/>
+      <c r="DJ28" s="20"/>
+      <c r="DK28" s="16"/>
+      <c r="DL28" s="19"/>
+      <c r="DM28" s="16"/>
+      <c r="DN28" s="19"/>
+      <c r="DO28" s="16"/>
+      <c r="DP28" s="19"/>
+      <c r="DQ28" s="16"/>
+      <c r="DR28" s="19"/>
+      <c r="DS28" s="16"/>
+      <c r="DT28" s="19"/>
+      <c r="DU28" s="16"/>
+      <c r="DV28" s="19"/>
+      <c r="DW28" s="16"/>
+      <c r="DX28" s="19"/>
+      <c r="DY28" s="12"/>
     </row>
     <row r="29">
-      <c r="B29" s="28"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="25" t="inlineStr">
+      <c r="B29" s="12"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="26" t="inlineStr">
         <is>
           <t>配分結果の整理</t>
         </is>
       </c>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
       <c r="T29" s="13"/>
-      <c r="U29" s="11"/>
-      <c r="V29" s="12"/>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12"/>
-      <c r="Y29" s="12"/>
-      <c r="Z29" s="12"/>
-      <c r="AA29" s="12"/>
-      <c r="AB29" s="12"/>
-      <c r="AC29" s="12"/>
+      <c r="U29" s="6"/>
+      <c r="V29" s="11"/>
+      <c r="W29" s="11"/>
+      <c r="X29" s="11"/>
+      <c r="Y29" s="11"/>
+      <c r="Z29" s="11"/>
+      <c r="AA29" s="11"/>
+      <c r="AB29" s="11"/>
+      <c r="AC29" s="11"/>
       <c r="AD29" s="13"/>
-      <c r="AE29" s="11"/>
-      <c r="AF29" s="12"/>
-      <c r="AG29" s="12"/>
-      <c r="AH29" s="13"/>
-      <c r="AI29" s="8"/>
-      <c r="AJ29" s="7" t="inlineStr">
+      <c r="AE29" s="6"/>
+      <c r="AF29" s="11"/>
+      <c r="AG29" s="11"/>
+      <c r="AH29" s="14"/>
+      <c r="AI29" s="9"/>
+      <c r="AJ29" s="8" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
       <c r="AK29" s="4"/>
       <c r="AL29" s="5"/>
-      <c r="AM29" s="6" t="inlineStr">
+      <c r="AM29" s="7" t="inlineStr">
         <is>
           <t>8月10日</t>
         </is>
       </c>
       <c r="AN29" s="4"/>
       <c r="AO29" s="4"/>
-      <c r="AP29" s="5"/>
-      <c r="AQ29" s="6" t="inlineStr">
+      <c r="AP29" s="22"/>
+      <c r="AQ29" s="7" t="inlineStr">
         <is>
           <t>9月20日</t>
         </is>
@@ -3990,281 +4305,303 @@
       <c r="AR29" s="4"/>
       <c r="AS29" s="4"/>
       <c r="AT29" s="5"/>
-      <c r="AU29" s="11"/>
-      <c r="AV29" s="12"/>
-      <c r="AW29" s="12"/>
-      <c r="AX29" s="33" t="inlineStr">
+      <c r="AU29" s="6"/>
+      <c r="AV29" s="11"/>
+      <c r="AW29" s="11"/>
+      <c r="AX29" s="34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AY29" s="11"/>
+      <c r="AY29" s="6"/>
       <c r="AZ29" s="13"/>
-      <c r="BA29" s="11"/>
+      <c r="BA29" s="6"/>
       <c r="BB29" s="13"/>
-      <c r="BC29" s="11"/>
+      <c r="BC29" s="6"/>
       <c r="BD29" s="13"/>
-      <c r="BE29" s="11"/>
+      <c r="BE29" s="6"/>
       <c r="BF29" s="13"/>
-      <c r="BG29" s="11"/>
-      <c r="BH29" s="12"/>
+      <c r="BG29" s="6"/>
+      <c r="BH29" s="6"/>
       <c r="BI29" s="13"/>
-      <c r="BJ29" s="11"/>
+      <c r="BJ29" s="6"/>
       <c r="BK29" s="13"/>
-      <c r="BL29" s="11"/>
+      <c r="BL29" s="6"/>
       <c r="BM29" s="13"/>
-      <c r="BN29" s="11"/>
+      <c r="BN29" s="6"/>
       <c r="BO29" s="13"/>
-      <c r="BP29" s="11"/>
+      <c r="BP29" s="6"/>
       <c r="BQ29" s="13"/>
-      <c r="BR29" s="11"/>
-      <c r="BS29" s="12"/>
+      <c r="BR29" s="6"/>
+      <c r="BS29" s="6"/>
       <c r="BT29" s="13"/>
-      <c r="BU29" s="11"/>
+      <c r="BU29" s="6"/>
       <c r="BV29" s="13"/>
-      <c r="BW29" s="11"/>
+      <c r="BW29" s="6"/>
       <c r="BX29" s="13"/>
-      <c r="BY29" s="11"/>
+      <c r="BY29" s="6"/>
       <c r="BZ29" s="13"/>
-      <c r="CA29" s="11"/>
-      <c r="CB29" s="12"/>
-      <c r="CC29" s="13"/>
-      <c r="CD29" s="20"/>
-      <c r="CE29" s="11"/>
-      <c r="CF29" s="12"/>
+      <c r="CA29" s="6"/>
+      <c r="CB29" s="11"/>
+      <c r="CC29" s="14"/>
+      <c r="CD29" s="14"/>
+      <c r="CE29" s="6"/>
+      <c r="CF29" s="6"/>
       <c r="CG29" s="13"/>
-      <c r="CH29" s="11"/>
+      <c r="CH29" s="6"/>
       <c r="CI29" s="13"/>
-      <c r="CJ29" s="11"/>
-      <c r="CK29" s="12"/>
-      <c r="CL29" s="13"/>
-      <c r="CM29" s="11"/>
-      <c r="CN29" s="13"/>
-      <c r="CO29" s="11"/>
+      <c r="CJ29" s="6"/>
+      <c r="CK29" s="11"/>
+      <c r="CL29" s="14"/>
+      <c r="CM29" s="6"/>
+      <c r="CN29" s="14"/>
+      <c r="CO29" s="6"/>
       <c r="CP29" s="13"/>
-      <c r="CQ29" s="11"/>
+      <c r="CQ29" s="6"/>
       <c r="CR29" s="13"/>
-      <c r="CS29" s="11"/>
+      <c r="CS29" s="6"/>
       <c r="CT29" s="13"/>
-      <c r="DD29" s="11"/>
+      <c r="CU29" s="9"/>
+      <c r="CV29" s="5"/>
+      <c r="CW29" s="9"/>
+      <c r="CX29" s="4"/>
+      <c r="CY29" s="22"/>
+      <c r="CZ29" s="9"/>
+      <c r="DA29" s="5"/>
+      <c r="DB29" s="9"/>
+      <c r="DC29" s="5"/>
+      <c r="DD29" s="6"/>
       <c r="DE29" s="13"/>
-      <c r="DF29" s="11"/>
+      <c r="DF29" s="6"/>
       <c r="DG29" s="13"/>
-      <c r="DH29" s="11"/>
-      <c r="DI29" s="12"/>
-      <c r="DJ29" s="13"/>
-      <c r="DK29" s="11"/>
+      <c r="DH29" s="6"/>
+      <c r="DI29" s="11"/>
+      <c r="DJ29" s="14"/>
+      <c r="DK29" s="6"/>
       <c r="DL29" s="13"/>
-      <c r="DM29" s="11"/>
+      <c r="DM29" s="6"/>
       <c r="DN29" s="13"/>
-      <c r="DO29" s="11"/>
+      <c r="DO29" s="6"/>
       <c r="DP29" s="13"/>
-      <c r="DQ29" s="11"/>
+      <c r="DQ29" s="6"/>
       <c r="DR29" s="13"/>
-      <c r="DS29" s="11"/>
+      <c r="DS29" s="6"/>
       <c r="DT29" s="13"/>
-      <c r="DU29" s="11"/>
+      <c r="DU29" s="6"/>
       <c r="DV29" s="13"/>
-      <c r="DW29" s="11"/>
+      <c r="DW29" s="6"/>
       <c r="DX29" s="13"/>
+      <c r="DY29" s="12"/>
     </row>
     <row r="30">
-      <c r="B30" s="15"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="19" t="inlineStr">
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="21" t="inlineStr">
         <is>
           <t>配分結果の整理</t>
         </is>
       </c>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="15"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
-      <c r="Z30" s="16"/>
-      <c r="AA30" s="16"/>
-      <c r="AB30" s="16"/>
-      <c r="AC30" s="16"/>
-      <c r="AD30" s="18"/>
-      <c r="AE30" s="15"/>
-      <c r="AF30" s="36" t="inlineStr">
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="16"/>
+      <c r="V30" s="17"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
+      <c r="Z30" s="17"/>
+      <c r="AA30" s="17"/>
+      <c r="AB30" s="17"/>
+      <c r="AC30" s="17"/>
+      <c r="AD30" s="19"/>
+      <c r="AE30" s="16"/>
+      <c r="AF30" s="37" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="AG30" s="16"/>
-      <c r="AH30" s="18"/>
-      <c r="AJ30" s="2" t="inlineStr">
+      <c r="AG30" s="17"/>
+      <c r="AH30" s="20"/>
+      <c r="AI30" s="9"/>
+      <c r="AJ30" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="AU30" s="15"/>
-      <c r="AV30" s="16"/>
-      <c r="AW30" s="16"/>
-      <c r="AX30" s="26" t="inlineStr">
+      <c r="AK30" s="4"/>
+      <c r="AL30" s="5"/>
+      <c r="AM30" s="9"/>
+      <c r="AN30" s="4"/>
+      <c r="AO30" s="4"/>
+      <c r="AP30" s="22"/>
+      <c r="AQ30" s="9"/>
+      <c r="AR30" s="4"/>
+      <c r="AS30" s="4"/>
+      <c r="AT30" s="5"/>
+      <c r="AU30" s="9"/>
+      <c r="AV30" s="17"/>
+      <c r="AW30" s="17"/>
+      <c r="AX30" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AY30" s="15"/>
-      <c r="AZ30" s="18"/>
-      <c r="BA30" s="15"/>
-      <c r="BB30" s="18"/>
-      <c r="BC30" s="15"/>
-      <c r="BD30" s="18"/>
-      <c r="BE30" s="15"/>
-      <c r="BF30" s="18"/>
-      <c r="BG30" s="15"/>
+      <c r="AY30" s="16"/>
+      <c r="AZ30" s="19"/>
+      <c r="BA30" s="16"/>
+      <c r="BB30" s="19"/>
+      <c r="BC30" s="16"/>
+      <c r="BD30" s="19"/>
+      <c r="BE30" s="16"/>
+      <c r="BF30" s="19"/>
+      <c r="BG30" s="16"/>
       <c r="BH30" s="16"/>
-      <c r="BI30" s="18"/>
-      <c r="BJ30" s="15"/>
-      <c r="BK30" s="18"/>
-      <c r="BL30" s="15"/>
-      <c r="BM30" s="18"/>
-      <c r="BN30" s="15"/>
-      <c r="BO30" s="18"/>
-      <c r="BP30" s="15"/>
-      <c r="BQ30" s="18"/>
-      <c r="BR30" s="15"/>
+      <c r="BI30" s="19"/>
+      <c r="BJ30" s="16"/>
+      <c r="BK30" s="19"/>
+      <c r="BL30" s="16"/>
+      <c r="BM30" s="19"/>
+      <c r="BN30" s="16"/>
+      <c r="BO30" s="19"/>
+      <c r="BP30" s="16"/>
+      <c r="BQ30" s="19"/>
+      <c r="BR30" s="16"/>
       <c r="BS30" s="16"/>
-      <c r="BT30" s="18"/>
-      <c r="BU30" s="15"/>
-      <c r="BV30" s="18"/>
-      <c r="BW30" s="15"/>
-      <c r="BX30" s="18"/>
-      <c r="BY30" s="15"/>
-      <c r="BZ30" s="18"/>
-      <c r="CA30" s="15"/>
-      <c r="CB30" s="16"/>
-      <c r="CC30" s="18"/>
-      <c r="CD30" s="21"/>
-      <c r="CE30" s="15"/>
+      <c r="BT30" s="19"/>
+      <c r="BU30" s="16"/>
+      <c r="BV30" s="19"/>
+      <c r="BW30" s="16"/>
+      <c r="BX30" s="19"/>
+      <c r="BY30" s="16"/>
+      <c r="BZ30" s="19"/>
+      <c r="CA30" s="16"/>
+      <c r="CB30" s="17"/>
+      <c r="CC30" s="20"/>
+      <c r="CD30" s="20"/>
+      <c r="CE30" s="16"/>
       <c r="CF30" s="16"/>
-      <c r="CG30" s="18"/>
-      <c r="CH30" s="15"/>
-      <c r="CI30" s="18"/>
-      <c r="CJ30" s="15"/>
-      <c r="CK30" s="16"/>
-      <c r="CL30" s="18"/>
-      <c r="CM30" s="15"/>
-      <c r="CN30" s="18"/>
-      <c r="CO30" s="15"/>
-      <c r="CP30" s="18"/>
-      <c r="CQ30" s="15"/>
-      <c r="CR30" s="18"/>
-      <c r="CS30" s="15"/>
-      <c r="CT30" s="18"/>
-      <c r="CU30" s="8"/>
+      <c r="CG30" s="19"/>
+      <c r="CH30" s="16"/>
+      <c r="CI30" s="19"/>
+      <c r="CJ30" s="16"/>
+      <c r="CK30" s="17"/>
+      <c r="CL30" s="20"/>
+      <c r="CM30" s="16"/>
+      <c r="CN30" s="20"/>
+      <c r="CO30" s="16"/>
+      <c r="CP30" s="19"/>
+      <c r="CQ30" s="16"/>
+      <c r="CR30" s="19"/>
+      <c r="CS30" s="16"/>
+      <c r="CT30" s="19"/>
+      <c r="CU30" s="9"/>
       <c r="CV30" s="5"/>
-      <c r="CW30" s="8"/>
+      <c r="CW30" s="9"/>
       <c r="CX30" s="4"/>
-      <c r="CY30" s="5"/>
-      <c r="CZ30" s="8"/>
+      <c r="CY30" s="22"/>
+      <c r="CZ30" s="9"/>
       <c r="DA30" s="5"/>
-      <c r="DB30" s="8"/>
+      <c r="DB30" s="9"/>
       <c r="DC30" s="5"/>
-      <c r="DD30" s="15"/>
-      <c r="DE30" s="18"/>
-      <c r="DF30" s="15"/>
-      <c r="DG30" s="18"/>
-      <c r="DH30" s="15"/>
-      <c r="DI30" s="16"/>
-      <c r="DJ30" s="18"/>
-      <c r="DK30" s="15"/>
-      <c r="DL30" s="18"/>
-      <c r="DM30" s="15"/>
-      <c r="DN30" s="18"/>
-      <c r="DO30" s="15"/>
-      <c r="DP30" s="18"/>
-      <c r="DQ30" s="15"/>
-      <c r="DR30" s="18"/>
-      <c r="DS30" s="15"/>
-      <c r="DT30" s="18"/>
-      <c r="DU30" s="15"/>
-      <c r="DV30" s="18"/>
-      <c r="DW30" s="15"/>
-      <c r="DX30" s="18"/>
+      <c r="DD30" s="9"/>
+      <c r="DE30" s="19"/>
+      <c r="DF30" s="16"/>
+      <c r="DG30" s="19"/>
+      <c r="DH30" s="16"/>
+      <c r="DI30" s="17"/>
+      <c r="DJ30" s="20"/>
+      <c r="DK30" s="16"/>
+      <c r="DL30" s="19"/>
+      <c r="DM30" s="16"/>
+      <c r="DN30" s="19"/>
+      <c r="DO30" s="16"/>
+      <c r="DP30" s="19"/>
+      <c r="DQ30" s="16"/>
+      <c r="DR30" s="19"/>
+      <c r="DS30" s="16"/>
+      <c r="DT30" s="19"/>
+      <c r="DU30" s="16"/>
+      <c r="DV30" s="19"/>
+      <c r="DW30" s="16"/>
+      <c r="DX30" s="19"/>
+      <c r="DY30" s="12"/>
     </row>
     <row r="31">
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>報告書作成</t>
         </is>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
       <c r="K31" s="13"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="11"/>
       <c r="T31" s="13"/>
-      <c r="U31" s="11"/>
-      <c r="V31" s="12"/>
-      <c r="W31" s="12"/>
-      <c r="X31" s="12"/>
-      <c r="Y31" s="12"/>
-      <c r="Z31" s="12"/>
-      <c r="AA31" s="12"/>
-      <c r="AB31" s="12"/>
-      <c r="AC31" s="12"/>
+      <c r="U31" s="6"/>
+      <c r="V31" s="11"/>
+      <c r="W31" s="11"/>
+      <c r="X31" s="11"/>
+      <c r="Y31" s="11"/>
+      <c r="Z31" s="11"/>
+      <c r="AA31" s="11"/>
+      <c r="AB31" s="11"/>
+      <c r="AC31" s="11"/>
       <c r="AD31" s="13"/>
-      <c r="AE31" s="11"/>
-      <c r="AF31" s="37" t="inlineStr">
+      <c r="AE31" s="6"/>
+      <c r="AF31" s="38" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="AG31" s="12"/>
-      <c r="AH31" s="13"/>
+      <c r="AG31" s="11"/>
+      <c r="AH31" s="14"/>
       <c r="AI31" s="10" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="AJ31" s="7" t="inlineStr">
+      <c r="AJ31" s="8" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
       <c r="AK31" s="4"/>
       <c r="AL31" s="5"/>
-      <c r="AM31" s="6" t="inlineStr">
+      <c r="AM31" s="7" t="inlineStr">
         <is>
           <t>10月1日</t>
         </is>
       </c>
       <c r="AN31" s="4"/>
       <c r="AO31" s="4"/>
-      <c r="AP31" s="5"/>
-      <c r="AQ31" s="6" t="inlineStr">
+      <c r="AP31" s="22"/>
+      <c r="AQ31" s="7" t="inlineStr">
         <is>
           <t>11月1日</t>
         </is>
@@ -4272,214 +4609,234 @@
       <c r="AR31" s="4"/>
       <c r="AS31" s="4"/>
       <c r="AT31" s="5"/>
-      <c r="AU31" s="11"/>
-      <c r="AV31" s="12"/>
-      <c r="AW31" s="12"/>
-      <c r="AX31" s="33" t="inlineStr">
+      <c r="AU31" s="6"/>
+      <c r="AV31" s="11"/>
+      <c r="AW31" s="11"/>
+      <c r="AX31" s="34" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="AY31" s="11"/>
+      <c r="AY31" s="6"/>
       <c r="AZ31" s="13"/>
-      <c r="BA31" s="11"/>
+      <c r="BA31" s="6"/>
       <c r="BB31" s="13"/>
-      <c r="BC31" s="11"/>
+      <c r="BC31" s="6"/>
       <c r="BD31" s="13"/>
-      <c r="BE31" s="11"/>
+      <c r="BE31" s="6"/>
       <c r="BF31" s="13"/>
-      <c r="BG31" s="11"/>
-      <c r="BH31" s="12"/>
+      <c r="BG31" s="6"/>
+      <c r="BH31" s="6"/>
       <c r="BI31" s="13"/>
-      <c r="BJ31" s="11"/>
+      <c r="BJ31" s="6"/>
       <c r="BK31" s="13"/>
-      <c r="BL31" s="11"/>
+      <c r="BL31" s="6"/>
       <c r="BM31" s="13"/>
-      <c r="BN31" s="11"/>
+      <c r="BN31" s="6"/>
       <c r="BO31" s="13"/>
-      <c r="BP31" s="11"/>
+      <c r="BP31" s="6"/>
       <c r="BQ31" s="13"/>
-      <c r="BR31" s="11"/>
-      <c r="BS31" s="12"/>
+      <c r="BR31" s="6"/>
+      <c r="BS31" s="6"/>
       <c r="BT31" s="13"/>
-      <c r="BU31" s="11"/>
+      <c r="BU31" s="6"/>
       <c r="BV31" s="13"/>
-      <c r="BW31" s="11"/>
+      <c r="BW31" s="6"/>
       <c r="BX31" s="13"/>
-      <c r="BY31" s="11"/>
+      <c r="BY31" s="6"/>
       <c r="BZ31" s="13"/>
-      <c r="CA31" s="11"/>
-      <c r="CB31" s="12"/>
-      <c r="CC31" s="13"/>
-      <c r="CD31" s="20"/>
-      <c r="CE31" s="11"/>
-      <c r="CF31" s="12"/>
+      <c r="CA31" s="6"/>
+      <c r="CB31" s="11"/>
+      <c r="CC31" s="14"/>
+      <c r="CD31" s="14"/>
+      <c r="CE31" s="6"/>
+      <c r="CF31" s="6"/>
       <c r="CG31" s="13"/>
-      <c r="CH31" s="11"/>
+      <c r="CH31" s="6"/>
       <c r="CI31" s="13"/>
-      <c r="CJ31" s="11"/>
-      <c r="CK31" s="12"/>
-      <c r="CL31" s="13"/>
-      <c r="CM31" s="11"/>
-      <c r="CN31" s="13"/>
-      <c r="CO31" s="11"/>
+      <c r="CJ31" s="6"/>
+      <c r="CK31" s="11"/>
+      <c r="CL31" s="14"/>
+      <c r="CM31" s="6"/>
+      <c r="CN31" s="14"/>
+      <c r="CO31" s="6"/>
       <c r="CP31" s="13"/>
-      <c r="CQ31" s="11"/>
+      <c r="CQ31" s="6"/>
       <c r="CR31" s="13"/>
-      <c r="CS31" s="11"/>
+      <c r="CS31" s="6"/>
       <c r="CT31" s="13"/>
-      <c r="CU31" s="11"/>
+      <c r="CU31" s="6"/>
       <c r="CV31" s="13"/>
-      <c r="CW31" s="11"/>
-      <c r="CX31" s="12"/>
-      <c r="CY31" s="13"/>
-      <c r="CZ31" s="11"/>
+      <c r="CW31" s="6"/>
+      <c r="CX31" s="11"/>
+      <c r="CY31" s="14"/>
+      <c r="CZ31" s="6"/>
       <c r="DA31" s="13"/>
-      <c r="DB31" s="11"/>
+      <c r="DB31" s="6"/>
       <c r="DC31" s="13"/>
-      <c r="DD31" s="11"/>
+      <c r="DD31" s="6"/>
       <c r="DE31" s="13"/>
-      <c r="DF31" s="8"/>
+      <c r="DF31" s="9"/>
       <c r="DG31" s="5"/>
-      <c r="DH31" s="8"/>
+      <c r="DH31" s="9"/>
       <c r="DI31" s="4"/>
-      <c r="DJ31" s="5"/>
-      <c r="DK31" s="8"/>
+      <c r="DJ31" s="22"/>
+      <c r="DK31" s="9"/>
       <c r="DL31" s="5"/>
-      <c r="DM31" s="11"/>
+      <c r="DM31" s="6"/>
       <c r="DN31" s="13"/>
-      <c r="DO31" s="11"/>
+      <c r="DO31" s="6"/>
       <c r="DP31" s="13"/>
-      <c r="DQ31" s="11"/>
+      <c r="DQ31" s="6"/>
       <c r="DR31" s="13"/>
-      <c r="DS31" s="11"/>
+      <c r="DS31" s="6"/>
       <c r="DT31" s="13"/>
-      <c r="DU31" s="11"/>
+      <c r="DU31" s="6"/>
       <c r="DV31" s="13"/>
-      <c r="DW31" s="11"/>
+      <c r="DW31" s="6"/>
       <c r="DX31" s="13"/>
+      <c r="DY31" s="12"/>
     </row>
     <row r="32">
-      <c r="B32" s="15"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="15"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
-      <c r="Y32" s="16"/>
-      <c r="Z32" s="16"/>
-      <c r="AA32" s="16"/>
-      <c r="AB32" s="16"/>
-      <c r="AC32" s="16"/>
-      <c r="AD32" s="18"/>
-      <c r="AE32" s="15"/>
-      <c r="AF32" s="16"/>
-      <c r="AG32" s="16"/>
-      <c r="AH32" s="18"/>
-      <c r="AJ32" s="2" t="inlineStr">
+      <c r="B32" s="16"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="16"/>
+      <c r="V32" s="17"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="17"/>
+      <c r="Y32" s="17"/>
+      <c r="Z32" s="17"/>
+      <c r="AA32" s="17"/>
+      <c r="AB32" s="17"/>
+      <c r="AC32" s="17"/>
+      <c r="AD32" s="19"/>
+      <c r="AE32" s="16"/>
+      <c r="AF32" s="17"/>
+      <c r="AG32" s="17"/>
+      <c r="AH32" s="20"/>
+      <c r="AI32" s="9"/>
+      <c r="AJ32" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="AU32" s="15"/>
-      <c r="AV32" s="16"/>
-      <c r="AW32" s="16"/>
-      <c r="AX32" s="26" t="inlineStr">
+      <c r="AK32" s="4"/>
+      <c r="AL32" s="5"/>
+      <c r="AM32" s="9"/>
+      <c r="AN32" s="4"/>
+      <c r="AO32" s="4"/>
+      <c r="AP32" s="22"/>
+      <c r="AQ32" s="9"/>
+      <c r="AR32" s="4"/>
+      <c r="AS32" s="4"/>
+      <c r="AT32" s="5"/>
+      <c r="AU32" s="9"/>
+      <c r="AV32" s="17"/>
+      <c r="AW32" s="17"/>
+      <c r="AX32" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AY32" s="15"/>
-      <c r="AZ32" s="18"/>
-      <c r="BA32" s="15"/>
-      <c r="BB32" s="18"/>
-      <c r="BC32" s="15"/>
-      <c r="BD32" s="18"/>
-      <c r="BE32" s="15"/>
-      <c r="BF32" s="18"/>
-      <c r="BG32" s="15"/>
+      <c r="AY32" s="16"/>
+      <c r="AZ32" s="19"/>
+      <c r="BA32" s="16"/>
+      <c r="BB32" s="19"/>
+      <c r="BC32" s="16"/>
+      <c r="BD32" s="19"/>
+      <c r="BE32" s="16"/>
+      <c r="BF32" s="19"/>
+      <c r="BG32" s="16"/>
       <c r="BH32" s="16"/>
-      <c r="BI32" s="18"/>
-      <c r="BJ32" s="15"/>
-      <c r="BK32" s="18"/>
-      <c r="BL32" s="15"/>
-      <c r="BM32" s="18"/>
-      <c r="BN32" s="15"/>
-      <c r="BO32" s="18"/>
-      <c r="BP32" s="15"/>
-      <c r="BQ32" s="18"/>
-      <c r="BR32" s="15"/>
+      <c r="BI32" s="19"/>
+      <c r="BJ32" s="16"/>
+      <c r="BK32" s="19"/>
+      <c r="BL32" s="16"/>
+      <c r="BM32" s="19"/>
+      <c r="BN32" s="16"/>
+      <c r="BO32" s="19"/>
+      <c r="BP32" s="16"/>
+      <c r="BQ32" s="19"/>
+      <c r="BR32" s="16"/>
       <c r="BS32" s="16"/>
-      <c r="BT32" s="18"/>
-      <c r="BU32" s="15"/>
-      <c r="BV32" s="18"/>
-      <c r="BW32" s="15"/>
-      <c r="BX32" s="18"/>
-      <c r="BY32" s="15"/>
-      <c r="BZ32" s="18"/>
-      <c r="CA32" s="15"/>
-      <c r="CB32" s="16"/>
-      <c r="CC32" s="18"/>
-      <c r="CD32" s="21"/>
-      <c r="CE32" s="15"/>
+      <c r="BT32" s="19"/>
+      <c r="BU32" s="16"/>
+      <c r="BV32" s="19"/>
+      <c r="BW32" s="16"/>
+      <c r="BX32" s="19"/>
+      <c r="BY32" s="16"/>
+      <c r="BZ32" s="19"/>
+      <c r="CA32" s="16"/>
+      <c r="CB32" s="17"/>
+      <c r="CC32" s="20"/>
+      <c r="CD32" s="20"/>
+      <c r="CE32" s="16"/>
       <c r="CF32" s="16"/>
-      <c r="CG32" s="18"/>
-      <c r="CH32" s="15"/>
-      <c r="CI32" s="18"/>
-      <c r="CJ32" s="15"/>
-      <c r="CK32" s="16"/>
-      <c r="CL32" s="18"/>
-      <c r="CM32" s="15"/>
-      <c r="CN32" s="18"/>
-      <c r="CO32" s="15"/>
-      <c r="CP32" s="18"/>
-      <c r="CQ32" s="15"/>
-      <c r="CR32" s="18"/>
-      <c r="CS32" s="15"/>
-      <c r="CT32" s="18"/>
-      <c r="CU32" s="15"/>
-      <c r="CV32" s="18"/>
-      <c r="CW32" s="15"/>
-      <c r="CX32" s="16"/>
-      <c r="CY32" s="18"/>
-      <c r="CZ32" s="15"/>
-      <c r="DA32" s="18"/>
-      <c r="DB32" s="15"/>
-      <c r="DC32" s="18"/>
-      <c r="DD32" s="15"/>
-      <c r="DE32" s="18"/>
-      <c r="DM32" s="15"/>
-      <c r="DN32" s="18"/>
-      <c r="DO32" s="15"/>
-      <c r="DP32" s="18"/>
-      <c r="DQ32" s="15"/>
-      <c r="DR32" s="18"/>
-      <c r="DS32" s="15"/>
-      <c r="DT32" s="18"/>
-      <c r="DU32" s="15"/>
-      <c r="DV32" s="18"/>
-      <c r="DW32" s="15"/>
-      <c r="DX32" s="18"/>
+      <c r="CG32" s="19"/>
+      <c r="CH32" s="16"/>
+      <c r="CI32" s="19"/>
+      <c r="CJ32" s="16"/>
+      <c r="CK32" s="17"/>
+      <c r="CL32" s="20"/>
+      <c r="CM32" s="16"/>
+      <c r="CN32" s="20"/>
+      <c r="CO32" s="16"/>
+      <c r="CP32" s="19"/>
+      <c r="CQ32" s="16"/>
+      <c r="CR32" s="19"/>
+      <c r="CS32" s="16"/>
+      <c r="CT32" s="19"/>
+      <c r="CU32" s="16"/>
+      <c r="CV32" s="19"/>
+      <c r="CW32" s="16"/>
+      <c r="CX32" s="17"/>
+      <c r="CY32" s="20"/>
+      <c r="CZ32" s="16"/>
+      <c r="DA32" s="19"/>
+      <c r="DB32" s="16"/>
+      <c r="DC32" s="19"/>
+      <c r="DD32" s="16"/>
+      <c r="DE32" s="19"/>
+      <c r="DF32" s="9"/>
+      <c r="DG32" s="5"/>
+      <c r="DH32" s="9"/>
+      <c r="DI32" s="4"/>
+      <c r="DJ32" s="22"/>
+      <c r="DK32" s="9"/>
+      <c r="DL32" s="5"/>
+      <c r="DM32" s="9"/>
+      <c r="DN32" s="19"/>
+      <c r="DO32" s="16"/>
+      <c r="DP32" s="19"/>
+      <c r="DQ32" s="16"/>
+      <c r="DR32" s="19"/>
+      <c r="DS32" s="16"/>
+      <c r="DT32" s="19"/>
+      <c r="DU32" s="16"/>
+      <c r="DV32" s="19"/>
+      <c r="DW32" s="16"/>
+      <c r="DX32" s="19"/>
+      <c r="DY32" s="12"/>
     </row>
     <row r="33">
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>照査</t>
         </is>
@@ -4493,7 +4850,7 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="8"/>
+      <c r="L33" s="9"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
@@ -4502,7 +4859,7 @@
       <c r="R33" s="4"/>
       <c r="S33" s="4"/>
       <c r="T33" s="5"/>
-      <c r="U33" s="8"/>
+      <c r="U33" s="9"/>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
       <c r="X33" s="4"/>
@@ -4512,190 +4869,325 @@
       <c r="AB33" s="4"/>
       <c r="AC33" s="4"/>
       <c r="AD33" s="5"/>
-      <c r="AE33" s="8"/>
-      <c r="AF33" s="35" t="inlineStr">
+      <c r="AE33" s="9"/>
+      <c r="AF33" s="36" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
       <c r="AG33" s="4"/>
-      <c r="AH33" s="5"/>
+      <c r="AH33" s="22"/>
       <c r="AI33" s="10" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="AJ33" s="7" t="inlineStr">
+      <c r="AJ33" s="8" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
       <c r="AK33" s="4"/>
       <c r="AL33" s="5"/>
-      <c r="AM33" s="8"/>
+      <c r="AM33" s="9"/>
       <c r="AN33" s="4"/>
       <c r="AO33" s="4"/>
-      <c r="AP33" s="5"/>
-      <c r="AQ33" s="8"/>
+      <c r="AP33" s="22"/>
+      <c r="AQ33" s="9"/>
       <c r="AR33" s="4"/>
       <c r="AS33" s="4"/>
       <c r="AT33" s="5"/>
-      <c r="AU33" s="8"/>
+      <c r="AU33" s="9"/>
       <c r="AV33" s="4"/>
       <c r="AW33" s="4"/>
-      <c r="AX33" s="22" t="inlineStr">
+      <c r="AX33" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AY33" s="8"/>
+      <c r="AY33" s="9"/>
       <c r="AZ33" s="5"/>
-      <c r="BA33" s="8"/>
+      <c r="BA33" s="9"/>
       <c r="BB33" s="5"/>
-      <c r="BC33" s="8"/>
+      <c r="BC33" s="9"/>
       <c r="BD33" s="5"/>
-      <c r="BE33" s="8"/>
+      <c r="BE33" s="9"/>
       <c r="BF33" s="5"/>
-      <c r="BG33" s="8"/>
-      <c r="BH33" s="4"/>
+      <c r="BG33" s="9"/>
+      <c r="BH33" s="9"/>
       <c r="BI33" s="5"/>
-      <c r="BJ33" s="8"/>
+      <c r="BJ33" s="9"/>
       <c r="BK33" s="5"/>
-      <c r="BL33" s="8"/>
+      <c r="BL33" s="9"/>
       <c r="BM33" s="5"/>
-      <c r="BN33" s="8"/>
+      <c r="BN33" s="9"/>
       <c r="BO33" s="5"/>
-      <c r="BP33" s="8"/>
+      <c r="BP33" s="9"/>
       <c r="BQ33" s="5"/>
-      <c r="BR33" s="8"/>
-      <c r="BS33" s="4"/>
+      <c r="BR33" s="9"/>
+      <c r="BS33" s="9"/>
       <c r="BT33" s="5"/>
-      <c r="BU33" s="8"/>
+      <c r="BU33" s="9"/>
       <c r="BV33" s="5"/>
-      <c r="BW33" s="8"/>
+      <c r="BW33" s="9"/>
       <c r="BX33" s="5"/>
-      <c r="BY33" s="8"/>
+      <c r="BY33" s="9"/>
       <c r="BZ33" s="5"/>
-      <c r="CA33" s="8"/>
+      <c r="CA33" s="9"/>
       <c r="CB33" s="4"/>
-      <c r="CC33" s="5"/>
-      <c r="CD33" s="23"/>
-      <c r="CE33" s="8"/>
-      <c r="CF33" s="4"/>
+      <c r="CC33" s="22"/>
+      <c r="CD33" s="22"/>
+      <c r="CE33" s="9"/>
+      <c r="CF33" s="9"/>
       <c r="CG33" s="5"/>
-      <c r="CH33" s="8"/>
+      <c r="CH33" s="9"/>
       <c r="CI33" s="5"/>
-      <c r="CJ33" s="8"/>
+      <c r="CJ33" s="9"/>
       <c r="CK33" s="4"/>
-      <c r="CL33" s="5"/>
-      <c r="CM33" s="8"/>
-      <c r="CN33" s="5"/>
-      <c r="CO33" s="8"/>
+      <c r="CL33" s="22"/>
+      <c r="CM33" s="9"/>
+      <c r="CN33" s="22"/>
+      <c r="CO33" s="9"/>
       <c r="CP33" s="5"/>
-      <c r="CQ33" s="8"/>
+      <c r="CQ33" s="9"/>
       <c r="CR33" s="5"/>
-      <c r="CS33" s="8"/>
+      <c r="CS33" s="9"/>
       <c r="CT33" s="5"/>
-      <c r="CU33" s="8"/>
+      <c r="CU33" s="9"/>
       <c r="CV33" s="5"/>
-      <c r="CW33" s="8"/>
+      <c r="CW33" s="9"/>
       <c r="CX33" s="4"/>
-      <c r="CY33" s="5"/>
-      <c r="CZ33" s="8"/>
+      <c r="CY33" s="22"/>
+      <c r="CZ33" s="9"/>
       <c r="DA33" s="5"/>
-      <c r="DB33" s="8"/>
+      <c r="DB33" s="9"/>
       <c r="DC33" s="5"/>
-      <c r="DD33" s="8"/>
+      <c r="DD33" s="9"/>
       <c r="DE33" s="5"/>
-      <c r="DF33" s="8"/>
+      <c r="DF33" s="9"/>
       <c r="DG33" s="5"/>
-      <c r="DH33" s="8"/>
+      <c r="DH33" s="9"/>
       <c r="DI33" s="4"/>
-      <c r="DJ33" s="5"/>
-      <c r="DK33" s="8"/>
+      <c r="DJ33" s="22"/>
+      <c r="DK33" s="9"/>
       <c r="DL33" s="5"/>
-      <c r="DM33" s="8"/>
+      <c r="DM33" s="9"/>
       <c r="DN33" s="5"/>
-      <c r="DO33" s="8"/>
+      <c r="DO33" s="9"/>
       <c r="DP33" s="5"/>
-      <c r="DQ33" s="8"/>
+      <c r="DQ33" s="9"/>
       <c r="DR33" s="5"/>
-      <c r="DS33" s="8"/>
+      <c r="DS33" s="9"/>
       <c r="DT33" s="5"/>
-      <c r="DU33" s="8"/>
+      <c r="DU33" s="9"/>
       <c r="DV33" s="5"/>
-      <c r="DW33" s="8"/>
+      <c r="DW33" s="9"/>
       <c r="DX33" s="5"/>
+      <c r="DY33" s="12"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="6"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
+      <c r="T34" s="11"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="11"/>
+      <c r="W34" s="11"/>
+      <c r="X34" s="11"/>
+      <c r="Y34" s="11"/>
+      <c r="Z34" s="11"/>
+      <c r="AA34" s="11"/>
+      <c r="AB34" s="11"/>
+      <c r="AC34" s="11"/>
+      <c r="AD34" s="11"/>
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="11"/>
+      <c r="AG34" s="11"/>
+      <c r="AH34" s="6"/>
+      <c r="AI34" s="6"/>
+      <c r="AJ34" s="11"/>
+      <c r="AK34" s="11"/>
+      <c r="AL34" s="11"/>
+      <c r="AM34" s="6"/>
+      <c r="AN34" s="11"/>
+      <c r="AO34" s="11"/>
+      <c r="AP34" s="6"/>
+      <c r="AQ34" s="6"/>
+      <c r="AR34" s="11"/>
+      <c r="AS34" s="11"/>
+      <c r="AT34" s="11"/>
+      <c r="AU34" s="6"/>
+      <c r="AV34" s="11"/>
+      <c r="AW34" s="11"/>
+      <c r="AX34" s="11"/>
+      <c r="AY34" s="6"/>
+      <c r="AZ34" s="11"/>
+      <c r="BA34" s="6"/>
+      <c r="BB34" s="11"/>
+      <c r="BC34" s="6"/>
+      <c r="BD34" s="11"/>
+      <c r="BE34" s="6"/>
+      <c r="BF34" s="11"/>
+      <c r="BG34" s="6"/>
+      <c r="BH34" s="6"/>
+      <c r="BI34" s="11"/>
+      <c r="BJ34" s="6"/>
+      <c r="BK34" s="11"/>
+      <c r="BL34" s="6"/>
+      <c r="BM34" s="11"/>
+      <c r="BN34" s="6"/>
+      <c r="BO34" s="11"/>
+      <c r="BP34" s="6"/>
+      <c r="BQ34" s="11"/>
+      <c r="BR34" s="6"/>
+      <c r="BS34" s="6"/>
+      <c r="BT34" s="11"/>
+      <c r="BU34" s="6"/>
+      <c r="BV34" s="11"/>
+      <c r="BW34" s="6"/>
+      <c r="BX34" s="11"/>
+      <c r="BY34" s="6"/>
+      <c r="BZ34" s="11"/>
+      <c r="CA34" s="6"/>
+      <c r="CB34" s="11"/>
+      <c r="CC34" s="6"/>
+      <c r="CD34" s="6"/>
+      <c r="CE34" s="11"/>
+      <c r="CF34" s="6"/>
+      <c r="CG34" s="11"/>
+      <c r="CH34" s="6"/>
+      <c r="CI34" s="11"/>
+      <c r="CJ34" s="6"/>
+      <c r="CK34" s="11"/>
+      <c r="CL34" s="6"/>
+      <c r="CM34" s="11"/>
+      <c r="CN34" s="6"/>
+      <c r="CO34" s="6"/>
+      <c r="CP34" s="11"/>
+      <c r="CQ34" s="6"/>
+      <c r="CR34" s="11"/>
+      <c r="CS34" s="6"/>
+      <c r="CT34" s="11"/>
+      <c r="CU34" s="6"/>
+      <c r="CV34" s="11"/>
+      <c r="CW34" s="6"/>
+      <c r="CX34" s="11"/>
+      <c r="CY34" s="6"/>
+      <c r="CZ34" s="6"/>
+      <c r="DA34" s="11"/>
+      <c r="DB34" s="6"/>
+      <c r="DC34" s="11"/>
+      <c r="DD34" s="6"/>
+      <c r="DE34" s="11"/>
+      <c r="DF34" s="6"/>
+      <c r="DG34" s="11"/>
+      <c r="DH34" s="6"/>
+      <c r="DI34" s="11"/>
+      <c r="DJ34" s="6"/>
+      <c r="DK34" s="6"/>
+      <c r="DL34" s="11"/>
+      <c r="DM34" s="6"/>
+      <c r="DN34" s="11"/>
+      <c r="DO34" s="6"/>
+      <c r="DP34" s="11"/>
+      <c r="DQ34" s="6"/>
+      <c r="DR34" s="11"/>
+      <c r="DS34" s="6"/>
+      <c r="DT34" s="11"/>
+      <c r="DU34" s="6"/>
+      <c r="DV34" s="11"/>
+      <c r="DW34" s="6"/>
+      <c r="DX34" s="11"/>
+      <c r="DY34" s="12"/>
     </row>
     <row r="35">
-      <c r="B35" s="11"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="38" t="inlineStr">
+      <c r="B35" s="6"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="39" t="inlineStr">
         <is>
           <t>行追加</t>
         </is>
       </c>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="13"/>
-      <c r="P35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="14"/>
+      <c r="P35" s="6"/>
       <c r="Q35" s="24" t="inlineStr">
         <is>
           <t>必要に応じて行を追加</t>
         </is>
       </c>
-      <c r="R35" s="12"/>
-      <c r="S35" s="12"/>
-      <c r="T35" s="12"/>
-      <c r="U35" s="12"/>
-      <c r="V35" s="12"/>
-      <c r="W35" s="12"/>
-      <c r="X35" s="12"/>
-      <c r="Y35" s="12"/>
-      <c r="Z35" s="12"/>
-      <c r="AA35" s="12"/>
-      <c r="AB35" s="12"/>
-      <c r="AC35" s="12"/>
-      <c r="AD35" s="13"/>
-      <c r="AY35" s="8"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+      <c r="T35" s="11"/>
+      <c r="U35" s="11"/>
+      <c r="V35" s="11"/>
+      <c r="W35" s="11"/>
+      <c r="X35" s="11"/>
+      <c r="Y35" s="11"/>
+      <c r="Z35" s="11"/>
+      <c r="AA35" s="11"/>
+      <c r="AB35" s="11"/>
+      <c r="AC35" s="11"/>
+      <c r="AD35" s="14"/>
+      <c r="AY35" s="9"/>
       <c r="AZ35" s="4"/>
       <c r="BA35" s="4"/>
       <c r="BB35" s="4"/>
-      <c r="BC35" s="22" t="inlineStr">
+      <c r="BC35" s="27" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="15"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="18"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
-      <c r="S36" s="16"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="16"/>
-      <c r="W36" s="16"/>
-      <c r="X36" s="16"/>
-      <c r="Y36" s="16"/>
-      <c r="Z36" s="16"/>
-      <c r="AA36" s="16"/>
-      <c r="AB36" s="16"/>
-      <c r="AC36" s="16"/>
-      <c r="AD36" s="18"/>
-      <c r="BC36" s="2" t="inlineStr">
+      <c r="B36" s="9"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="22"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="4"/>
+      <c r="T36" s="4"/>
+      <c r="U36" s="4"/>
+      <c r="V36" s="4"/>
+      <c r="W36" s="4"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="4"/>
+      <c r="AA36" s="4"/>
+      <c r="AB36" s="4"/>
+      <c r="AC36" s="4"/>
+      <c r="AD36" s="22"/>
+      <c r="AY36" s="9"/>
+      <c r="AZ36" s="4"/>
+      <c r="BA36" s="4"/>
+      <c r="BB36" s="4"/>
+      <c r="BC36" s="27" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
@@ -4708,7 +5200,7 @@
         </is>
       </c>
       <c r="C37" s="5"/>
-      <c r="D37" s="8"/>
+      <c r="D37" s="9"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
@@ -4735,11 +5227,11 @@
       <c r="AB37" s="4"/>
       <c r="AC37" s="4"/>
       <c r="AD37" s="5"/>
-      <c r="AE37" s="8"/>
+      <c r="AE37" s="9"/>
       <c r="AF37" s="4"/>
       <c r="AG37" s="4"/>
-      <c r="AH37" s="5"/>
-      <c r="AI37" s="6" t="inlineStr">
+      <c r="AH37" s="22"/>
+      <c r="AI37" s="7" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -4747,100 +5239,101 @@
       <c r="AJ37" s="4"/>
       <c r="AK37" s="4"/>
       <c r="AL37" s="4"/>
-      <c r="AM37" s="7" t="inlineStr">
+      <c r="AM37" s="8" t="inlineStr">
         <is>
           <t>受注者</t>
         </is>
       </c>
       <c r="AN37" s="4"/>
       <c r="AO37" s="4"/>
-      <c r="AP37" s="5"/>
-      <c r="AQ37" s="8"/>
+      <c r="AP37" s="22"/>
+      <c r="AQ37" s="9"/>
       <c r="AR37" s="4"/>
       <c r="AS37" s="4"/>
       <c r="AT37" s="5"/>
-      <c r="AU37" s="8"/>
+      <c r="AU37" s="9"/>
       <c r="AV37" s="4"/>
       <c r="AW37" s="4"/>
       <c r="AX37" s="5"/>
-      <c r="AY37" s="8"/>
+      <c r="AY37" s="9"/>
       <c r="AZ37" s="4"/>
       <c r="BA37" s="4"/>
       <c r="BB37" s="5"/>
-      <c r="BC37" s="11"/>
-      <c r="BD37" s="12"/>
-      <c r="BE37" s="12"/>
-      <c r="BF37" s="12"/>
-      <c r="BG37" s="12"/>
-      <c r="BH37" s="12"/>
-      <c r="BI37" s="12"/>
-      <c r="BJ37" s="12"/>
-      <c r="BK37" s="12"/>
-      <c r="BL37" s="12"/>
-      <c r="BM37" s="12"/>
-      <c r="BN37" s="12"/>
-      <c r="BO37" s="12"/>
-      <c r="BP37" s="12"/>
-      <c r="BQ37" s="12"/>
-      <c r="BR37" s="12"/>
-      <c r="BS37" s="12"/>
-      <c r="BT37" s="12"/>
-      <c r="BU37" s="12"/>
-      <c r="BV37" s="13"/>
+      <c r="BC37" s="6"/>
+      <c r="BD37" s="11"/>
+      <c r="BE37" s="11"/>
+      <c r="BF37" s="11"/>
+      <c r="BG37" s="11"/>
+      <c r="BH37" s="11"/>
+      <c r="BI37" s="11"/>
+      <c r="BJ37" s="11"/>
+      <c r="BK37" s="11"/>
+      <c r="BL37" s="11"/>
+      <c r="BM37" s="11"/>
+      <c r="BN37" s="11"/>
+      <c r="BO37" s="11"/>
+      <c r="BP37" s="11"/>
+      <c r="BQ37" s="11"/>
+      <c r="BR37" s="11"/>
+      <c r="BS37" s="11"/>
+      <c r="BT37" s="11"/>
+      <c r="BU37" s="11"/>
+      <c r="BV37" s="14"/>
+      <c r="BW37" s="6"/>
     </row>
     <row r="38">
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>No,</t>
         </is>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="17" t="inlineStr">
+      <c r="C38" s="19"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="18" t="inlineStr">
         <is>
           <t>作業事項</t>
         </is>
       </c>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="16"/>
-      <c r="V38" s="16"/>
-      <c r="W38" s="16"/>
-      <c r="X38" s="16"/>
-      <c r="Y38" s="16"/>
-      <c r="Z38" s="16"/>
-      <c r="AA38" s="16"/>
-      <c r="AB38" s="16"/>
-      <c r="AC38" s="16"/>
-      <c r="AD38" s="18"/>
-      <c r="AE38" s="15"/>
-      <c r="AF38" s="17" t="inlineStr">
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17"/>
+      <c r="Z38" s="17"/>
+      <c r="AA38" s="17"/>
+      <c r="AB38" s="17"/>
+      <c r="AC38" s="17"/>
+      <c r="AD38" s="19"/>
+      <c r="AE38" s="16"/>
+      <c r="AF38" s="18" t="inlineStr">
         <is>
           <t>実施状況</t>
         </is>
       </c>
-      <c r="AG38" s="16"/>
-      <c r="AH38" s="18"/>
+      <c r="AG38" s="17"/>
+      <c r="AH38" s="20"/>
       <c r="AI38" s="10" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
       <c r="AJ38" s="4"/>
-      <c r="AK38" s="7" t="inlineStr">
+      <c r="AK38" s="8" t="inlineStr">
         <is>
           <t>作業担当</t>
         </is>
@@ -4853,59 +5346,60 @@
       </c>
       <c r="AN38" s="4"/>
       <c r="AO38" s="4"/>
-      <c r="AP38" s="5"/>
-      <c r="AQ38" s="19" t="inlineStr">
+      <c r="AP38" s="22"/>
+      <c r="AQ38" s="7" t="inlineStr">
         <is>
           <t>依頼日</t>
         </is>
       </c>
-      <c r="AR38" s="16"/>
-      <c r="AS38" s="16"/>
-      <c r="AT38" s="18"/>
-      <c r="AU38" s="19" t="inlineStr">
+      <c r="AR38" s="17"/>
+      <c r="AS38" s="17"/>
+      <c r="AT38" s="19"/>
+      <c r="AU38" s="21" t="inlineStr">
         <is>
           <t>着手日</t>
         </is>
       </c>
-      <c r="AV38" s="16"/>
-      <c r="AW38" s="16"/>
-      <c r="AX38" s="18"/>
-      <c r="AY38" s="15"/>
-      <c r="AZ38" s="17" t="inlineStr">
+      <c r="AV38" s="17"/>
+      <c r="AW38" s="17"/>
+      <c r="AX38" s="19"/>
+      <c r="AY38" s="16"/>
+      <c r="AZ38" s="18" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="BA38" s="16"/>
-      <c r="BB38" s="18"/>
-      <c r="BC38" s="15"/>
-      <c r="BD38" s="16"/>
-      <c r="BE38" s="16"/>
-      <c r="BF38" s="16"/>
-      <c r="BG38" s="16"/>
-      <c r="BH38" s="16"/>
-      <c r="BI38" s="16"/>
-      <c r="BJ38" s="16"/>
-      <c r="BK38" s="16"/>
-      <c r="BL38" s="17" t="inlineStr">
+      <c r="BA38" s="17"/>
+      <c r="BB38" s="19"/>
+      <c r="BC38" s="16"/>
+      <c r="BD38" s="17"/>
+      <c r="BE38" s="17"/>
+      <c r="BF38" s="17"/>
+      <c r="BG38" s="17"/>
+      <c r="BH38" s="17"/>
+      <c r="BI38" s="17"/>
+      <c r="BJ38" s="17"/>
+      <c r="BK38" s="17"/>
+      <c r="BL38" s="18" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="BM38" s="16"/>
-      <c r="BN38" s="16"/>
-      <c r="BO38" s="16"/>
-      <c r="BP38" s="16"/>
-      <c r="BQ38" s="16"/>
-      <c r="BR38" s="16"/>
-      <c r="BS38" s="16"/>
-      <c r="BT38" s="16"/>
-      <c r="BU38" s="16"/>
-      <c r="BV38" s="18"/>
+      <c r="BM38" s="17"/>
+      <c r="BN38" s="17"/>
+      <c r="BO38" s="17"/>
+      <c r="BP38" s="17"/>
+      <c r="BQ38" s="17"/>
+      <c r="BR38" s="17"/>
+      <c r="BS38" s="17"/>
+      <c r="BT38" s="17"/>
+      <c r="BU38" s="17"/>
+      <c r="BV38" s="20"/>
+      <c r="BW38" s="12"/>
     </row>
     <row r="39">
-      <c r="B39" s="8"/>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="B39" s="9"/>
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>1着手時、経歴書、技術者届等</t>
         </is>
@@ -4941,44 +5435,51 @@
       <c r="AB39" s="4"/>
       <c r="AC39" s="4"/>
       <c r="AD39" s="5"/>
-      <c r="AE39" s="8"/>
-      <c r="AF39" s="7" t="inlineStr">
+      <c r="AE39" s="9"/>
+      <c r="AF39" s="8" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
       <c r="AG39" s="4"/>
-      <c r="AH39" s="5"/>
-      <c r="AN39" s="2" t="inlineStr">
+      <c r="AH39" s="22"/>
+      <c r="AI39" s="9"/>
+      <c r="AJ39" s="4"/>
+      <c r="AK39" s="4"/>
+      <c r="AL39" s="5"/>
+      <c r="AM39" s="9"/>
+      <c r="AN39" s="8" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="AQ39" s="8"/>
-      <c r="AR39" s="7" t="inlineStr">
+      <c r="AO39" s="4"/>
+      <c r="AP39" s="22"/>
+      <c r="AQ39" s="9"/>
+      <c r="AR39" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="AS39" s="4"/>
       <c r="AT39" s="5"/>
-      <c r="AU39" s="8"/>
-      <c r="AV39" s="7" t="inlineStr">
+      <c r="AU39" s="9"/>
+      <c r="AV39" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="AW39" s="4"/>
       <c r="AX39" s="5"/>
-      <c r="AY39" s="8"/>
-      <c r="AZ39" s="7" t="inlineStr">
+      <c r="AY39" s="9"/>
+      <c r="AZ39" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="BA39" s="4"/>
       <c r="BB39" s="5"/>
-      <c r="BC39" s="8"/>
+      <c r="BC39" s="9"/>
       <c r="BD39" s="4"/>
       <c r="BE39" s="4"/>
       <c r="BF39" s="4"/>
@@ -4997,55 +5498,116 @@
       <c r="BS39" s="4"/>
       <c r="BT39" s="4"/>
       <c r="BU39" s="4"/>
-      <c r="BV39" s="5"/>
+      <c r="BV39" s="22"/>
+      <c r="BW39" s="12"/>
     </row>
     <row r="40">
-      <c r="C40" s="2" t="inlineStr">
+      <c r="B40" s="9"/>
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>2業務計画書作成</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>業務計画書作成</t>
         </is>
       </c>
-      <c r="AF40" s="2" t="inlineStr">
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="4"/>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="4"/>
+      <c r="AA40" s="4"/>
+      <c r="AB40" s="4"/>
+      <c r="AC40" s="4"/>
+      <c r="AD40" s="5"/>
+      <c r="AE40" s="9"/>
+      <c r="AF40" s="8" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="AI40" s="8"/>
+      <c r="AG40" s="4"/>
+      <c r="AH40" s="22"/>
+      <c r="AI40" s="9"/>
       <c r="AJ40" s="4"/>
       <c r="AK40" s="4"/>
       <c r="AL40" s="5"/>
-      <c r="AM40" s="8"/>
-      <c r="AN40" s="7" t="inlineStr">
+      <c r="AM40" s="9"/>
+      <c r="AN40" s="8" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
       <c r="AO40" s="4"/>
-      <c r="AP40" s="5"/>
-      <c r="AR40" s="2" t="inlineStr">
+      <c r="AP40" s="22"/>
+      <c r="AQ40" s="9"/>
+      <c r="AR40" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AV40" s="2" t="inlineStr">
+      <c r="AS40" s="4"/>
+      <c r="AT40" s="5"/>
+      <c r="AU40" s="9"/>
+      <c r="AV40" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AZ40" s="2" t="inlineStr">
+      <c r="AW40" s="4"/>
+      <c r="AX40" s="5"/>
+      <c r="AY40" s="9"/>
+      <c r="AZ40" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="BA40" s="4"/>
+      <c r="BB40" s="5"/>
+      <c r="BC40" s="9"/>
+      <c r="BD40" s="4"/>
+      <c r="BE40" s="4"/>
+      <c r="BF40" s="4"/>
+      <c r="BG40" s="4"/>
+      <c r="BH40" s="4"/>
+      <c r="BI40" s="4"/>
+      <c r="BJ40" s="4"/>
+      <c r="BK40" s="4"/>
+      <c r="BL40" s="4"/>
+      <c r="BM40" s="4"/>
+      <c r="BN40" s="4"/>
+      <c r="BO40" s="4"/>
+      <c r="BP40" s="4"/>
+      <c r="BQ40" s="4"/>
+      <c r="BR40" s="4"/>
+      <c r="BS40" s="4"/>
+      <c r="BT40" s="4"/>
+      <c r="BU40" s="4"/>
+      <c r="BV40" s="22"/>
+      <c r="BW40" s="6"/>
     </row>
     <row r="41">
-      <c r="B41" s="8"/>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="B41" s="9"/>
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>3交通量配分用データの作成</t>
         </is>
@@ -5081,20 +5643,27 @@
       <c r="AB41" s="4"/>
       <c r="AC41" s="4"/>
       <c r="AD41" s="5"/>
-      <c r="AE41" s="8"/>
-      <c r="AF41" s="7" t="inlineStr">
+      <c r="AE41" s="9"/>
+      <c r="AF41" s="8" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
       <c r="AG41" s="4"/>
-      <c r="AH41" s="5"/>
-      <c r="AN41" s="2" t="inlineStr">
+      <c r="AH41" s="22"/>
+      <c r="AI41" s="9"/>
+      <c r="AJ41" s="4"/>
+      <c r="AK41" s="4"/>
+      <c r="AL41" s="5"/>
+      <c r="AM41" s="9"/>
+      <c r="AN41" s="8" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="AQ41" s="6" t="inlineStr">
+      <c r="AO41" s="4"/>
+      <c r="AP41" s="22"/>
+      <c r="AQ41" s="7" t="inlineStr">
         <is>
           <t>5月20日</t>
         </is>
@@ -5102,7 +5671,7 @@
       <c r="AR41" s="4"/>
       <c r="AS41" s="4"/>
       <c r="AT41" s="5"/>
-      <c r="AU41" s="6" t="inlineStr">
+      <c r="AU41" s="7" t="inlineStr">
         <is>
           <t>5月23日</t>
         </is>
@@ -5110,7 +5679,7 @@
       <c r="AV41" s="4"/>
       <c r="AW41" s="4"/>
       <c r="AX41" s="5"/>
-      <c r="AY41" s="6" t="inlineStr">
+      <c r="AY41" s="7" t="inlineStr">
         <is>
           <t>6月10日</t>
         </is>
@@ -5118,7 +5687,7 @@
       <c r="AZ41" s="4"/>
       <c r="BA41" s="4"/>
       <c r="BB41" s="5"/>
-      <c r="BC41" s="8"/>
+      <c r="BC41" s="9"/>
       <c r="BD41" s="4"/>
       <c r="BE41" s="4"/>
       <c r="BF41" s="4"/>
@@ -5137,22 +5706,89 @@
       <c r="BS41" s="4"/>
       <c r="BT41" s="4"/>
       <c r="BU41" s="4"/>
-      <c r="BV41" s="5"/>
+      <c r="BV41" s="22"/>
+      <c r="BW41" s="6"/>
     </row>
     <row r="42">
-      <c r="AI42" s="8"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="4"/>
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="4"/>
+      <c r="AC42" s="4"/>
+      <c r="AD42" s="5"/>
+      <c r="AE42" s="9"/>
+      <c r="AF42" s="4"/>
+      <c r="AG42" s="4"/>
+      <c r="AH42" s="22"/>
+      <c r="AI42" s="9"/>
       <c r="AJ42" s="4"/>
       <c r="AK42" s="4"/>
       <c r="AL42" s="5"/>
-      <c r="AM42" s="8"/>
+      <c r="AM42" s="9"/>
       <c r="AN42" s="4"/>
       <c r="AO42" s="4"/>
-      <c r="AP42" s="5"/>
+      <c r="AP42" s="22"/>
+      <c r="AQ42" s="9"/>
+      <c r="AR42" s="4"/>
+      <c r="AS42" s="4"/>
+      <c r="AT42" s="5"/>
+      <c r="AU42" s="9"/>
+      <c r="AV42" s="4"/>
+      <c r="AW42" s="4"/>
+      <c r="AX42" s="5"/>
+      <c r="AY42" s="9"/>
+      <c r="AZ42" s="4"/>
+      <c r="BA42" s="4"/>
+      <c r="BB42" s="5"/>
+      <c r="BC42" s="9"/>
+      <c r="BD42" s="4"/>
+      <c r="BE42" s="4"/>
+      <c r="BF42" s="4"/>
+      <c r="BG42" s="4"/>
+      <c r="BH42" s="4"/>
+      <c r="BI42" s="4"/>
+      <c r="BJ42" s="4"/>
+      <c r="BK42" s="4"/>
+      <c r="BL42" s="4"/>
+      <c r="BM42" s="4"/>
+      <c r="BN42" s="4"/>
+      <c r="BO42" s="4"/>
+      <c r="BP42" s="4"/>
+      <c r="BQ42" s="4"/>
+      <c r="BR42" s="4"/>
+      <c r="BS42" s="4"/>
+      <c r="BT42" s="4"/>
+      <c r="BU42" s="4"/>
+      <c r="BV42" s="22"/>
+      <c r="BW42" s="6"/>
     </row>
     <row r="43">
-      <c r="B43" s="8"/>
+      <c r="B43" s="9"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="8"/>
+      <c r="D43" s="9"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -5179,23 +5815,31 @@
       <c r="AB43" s="4"/>
       <c r="AC43" s="4"/>
       <c r="AD43" s="5"/>
-      <c r="AE43" s="8"/>
+      <c r="AE43" s="9"/>
       <c r="AF43" s="4"/>
       <c r="AG43" s="4"/>
-      <c r="AH43" s="5"/>
-      <c r="AQ43" s="8"/>
+      <c r="AH43" s="22"/>
+      <c r="AI43" s="9"/>
+      <c r="AJ43" s="4"/>
+      <c r="AK43" s="4"/>
+      <c r="AL43" s="5"/>
+      <c r="AM43" s="9"/>
+      <c r="AN43" s="4"/>
+      <c r="AO43" s="4"/>
+      <c r="AP43" s="22"/>
+      <c r="AQ43" s="9"/>
       <c r="AR43" s="4"/>
       <c r="AS43" s="4"/>
       <c r="AT43" s="5"/>
-      <c r="AU43" s="8"/>
+      <c r="AU43" s="9"/>
       <c r="AV43" s="4"/>
       <c r="AW43" s="4"/>
       <c r="AX43" s="5"/>
-      <c r="AY43" s="8"/>
+      <c r="AY43" s="9"/>
       <c r="AZ43" s="4"/>
       <c r="BA43" s="4"/>
       <c r="BB43" s="5"/>
-      <c r="BC43" s="8"/>
+      <c r="BC43" s="9"/>
       <c r="BD43" s="4"/>
       <c r="BE43" s="4"/>
       <c r="BF43" s="4"/>
@@ -5214,149 +5858,160 @@
       <c r="BS43" s="4"/>
       <c r="BT43" s="4"/>
       <c r="BU43" s="4"/>
-      <c r="BV43" s="5"/>
+      <c r="BV43" s="22"/>
+      <c r="BW43" s="6"/>
     </row>
     <row r="44">
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="16"/>
-      <c r="O44" s="16"/>
-      <c r="P44" s="16"/>
-      <c r="Q44" s="16"/>
-      <c r="R44" s="16"/>
-      <c r="S44" s="16"/>
-      <c r="T44" s="16"/>
-      <c r="U44" s="16"/>
-      <c r="V44" s="16"/>
-      <c r="W44" s="16"/>
-      <c r="X44" s="16"/>
-      <c r="Y44" s="16"/>
-      <c r="Z44" s="16"/>
-      <c r="AA44" s="16"/>
-      <c r="AB44" s="16"/>
-      <c r="AC44" s="16"/>
-      <c r="AD44" s="16"/>
-      <c r="AE44" s="16"/>
-      <c r="AF44" s="16"/>
-      <c r="AG44" s="16"/>
-      <c r="AH44" s="16"/>
-      <c r="AI44" s="8"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4"/>
+      <c r="T44" s="4"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="4"/>
+      <c r="W44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="4"/>
+      <c r="AC44" s="4"/>
+      <c r="AD44" s="5"/>
+      <c r="AE44" s="9"/>
+      <c r="AF44" s="4"/>
+      <c r="AG44" s="4"/>
+      <c r="AH44" s="22"/>
+      <c r="AI44" s="9"/>
       <c r="AJ44" s="4"/>
       <c r="AK44" s="4"/>
       <c r="AL44" s="5"/>
-      <c r="AM44" s="8"/>
+      <c r="AM44" s="9"/>
       <c r="AN44" s="4"/>
       <c r="AO44" s="4"/>
-      <c r="AP44" s="5"/>
-      <c r="AQ44" s="16"/>
-      <c r="AR44" s="16"/>
-      <c r="AS44" s="16"/>
-      <c r="AT44" s="16"/>
-      <c r="AU44" s="16"/>
-      <c r="AV44" s="16"/>
-      <c r="AW44" s="16"/>
-      <c r="AX44" s="16"/>
-      <c r="AY44" s="16"/>
-      <c r="AZ44" s="16"/>
-      <c r="BA44" s="16"/>
-      <c r="BB44" s="16"/>
-      <c r="BC44" s="16"/>
-      <c r="BD44" s="16"/>
-      <c r="BE44" s="16"/>
-      <c r="BF44" s="16"/>
-      <c r="BG44" s="16"/>
-      <c r="BH44" s="16"/>
-      <c r="BI44" s="16"/>
-      <c r="BJ44" s="16"/>
-      <c r="BK44" s="16"/>
-      <c r="BL44" s="16"/>
-      <c r="BM44" s="16"/>
-      <c r="BN44" s="16"/>
-      <c r="BO44" s="16"/>
-      <c r="BP44" s="16"/>
-      <c r="BQ44" s="16"/>
-      <c r="BR44" s="16"/>
-      <c r="BS44" s="16"/>
-      <c r="BT44" s="16"/>
-      <c r="BU44" s="16"/>
-      <c r="BV44" s="16"/>
+      <c r="AP44" s="22"/>
+      <c r="AQ44" s="9"/>
+      <c r="AR44" s="4"/>
+      <c r="AS44" s="4"/>
+      <c r="AT44" s="5"/>
+      <c r="AU44" s="9"/>
+      <c r="AV44" s="4"/>
+      <c r="AW44" s="4"/>
+      <c r="AX44" s="5"/>
+      <c r="AY44" s="9"/>
+      <c r="AZ44" s="4"/>
+      <c r="BA44" s="4"/>
+      <c r="BB44" s="5"/>
+      <c r="BC44" s="9"/>
+      <c r="BD44" s="4"/>
+      <c r="BE44" s="4"/>
+      <c r="BF44" s="4"/>
+      <c r="BG44" s="4"/>
+      <c r="BH44" s="4"/>
+      <c r="BI44" s="4"/>
+      <c r="BJ44" s="4"/>
+      <c r="BK44" s="4"/>
+      <c r="BL44" s="4"/>
+      <c r="BM44" s="4"/>
+      <c r="BN44" s="4"/>
+      <c r="BO44" s="4"/>
+      <c r="BP44" s="4"/>
+      <c r="BQ44" s="4"/>
+      <c r="BR44" s="4"/>
+      <c r="BS44" s="4"/>
+      <c r="BT44" s="4"/>
+      <c r="BU44" s="4"/>
+      <c r="BV44" s="22"/>
+      <c r="BW44" s="6"/>
     </row>
     <row r="45">
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
-      <c r="L45" s="12"/>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="12"/>
-      <c r="P45" s="12"/>
-      <c r="Q45" s="12"/>
-      <c r="R45" s="12"/>
-      <c r="S45" s="12"/>
-      <c r="T45" s="12"/>
-      <c r="U45" s="12"/>
-      <c r="V45" s="12"/>
-      <c r="W45" s="12"/>
-      <c r="X45" s="12"/>
-      <c r="Y45" s="12"/>
-      <c r="Z45" s="12"/>
-      <c r="AA45" s="12"/>
-      <c r="AB45" s="12"/>
-      <c r="AC45" s="12"/>
-      <c r="AD45" s="12"/>
-      <c r="AE45" s="12"/>
-      <c r="AF45" s="12"/>
-      <c r="AG45" s="12"/>
-      <c r="AH45" s="12"/>
-      <c r="AQ45" s="12"/>
-      <c r="AR45" s="12"/>
-      <c r="AS45" s="12"/>
-      <c r="AT45" s="12"/>
-      <c r="AU45" s="12"/>
-      <c r="AV45" s="12"/>
-      <c r="AW45" s="12"/>
-      <c r="AX45" s="12"/>
-      <c r="AY45" s="12"/>
-      <c r="AZ45" s="12"/>
-      <c r="BA45" s="12"/>
-      <c r="BB45" s="12"/>
-      <c r="BC45" s="12"/>
-      <c r="BD45" s="12"/>
-      <c r="BE45" s="12"/>
-      <c r="BF45" s="12"/>
-      <c r="BG45" s="12"/>
-      <c r="BH45" s="12"/>
-      <c r="BI45" s="12"/>
-      <c r="BJ45" s="12"/>
-      <c r="BK45" s="12"/>
-      <c r="BL45" s="12"/>
-      <c r="BM45" s="12"/>
-      <c r="BN45" s="12"/>
-      <c r="BO45" s="12"/>
-      <c r="BP45" s="12"/>
-      <c r="BQ45" s="12"/>
-      <c r="BR45" s="12"/>
-      <c r="BS45" s="12"/>
-      <c r="BT45" s="12"/>
-      <c r="BU45" s="12"/>
-      <c r="BV45" s="12"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="11"/>
+      <c r="Q45" s="11"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="11"/>
+      <c r="T45" s="11"/>
+      <c r="U45" s="11"/>
+      <c r="V45" s="11"/>
+      <c r="W45" s="11"/>
+      <c r="X45" s="11"/>
+      <c r="Y45" s="11"/>
+      <c r="Z45" s="11"/>
+      <c r="AA45" s="11"/>
+      <c r="AB45" s="11"/>
+      <c r="AC45" s="11"/>
+      <c r="AD45" s="11"/>
+      <c r="AE45" s="11"/>
+      <c r="AF45" s="11"/>
+      <c r="AG45" s="11"/>
+      <c r="AH45" s="11"/>
+      <c r="AI45" s="11"/>
+      <c r="AJ45" s="11"/>
+      <c r="AK45" s="11"/>
+      <c r="AL45" s="11"/>
+      <c r="AM45" s="11"/>
+      <c r="AN45" s="11"/>
+      <c r="AO45" s="11"/>
+      <c r="AP45" s="11"/>
+      <c r="AQ45" s="11"/>
+      <c r="AR45" s="11"/>
+      <c r="AS45" s="11"/>
+      <c r="AT45" s="11"/>
+      <c r="AU45" s="11"/>
+      <c r="AV45" s="11"/>
+      <c r="AW45" s="11"/>
+      <c r="AX45" s="11"/>
+      <c r="AY45" s="11"/>
+      <c r="AZ45" s="11"/>
+      <c r="BA45" s="11"/>
+      <c r="BB45" s="11"/>
+      <c r="BC45" s="11"/>
+      <c r="BD45" s="11"/>
+      <c r="BE45" s="11"/>
+      <c r="BF45" s="11"/>
+      <c r="BG45" s="11"/>
+      <c r="BH45" s="11"/>
+      <c r="BI45" s="11"/>
+      <c r="BJ45" s="11"/>
+      <c r="BK45" s="11"/>
+      <c r="BL45" s="11"/>
+      <c r="BM45" s="11"/>
+      <c r="BN45" s="11"/>
+      <c r="BO45" s="11"/>
+      <c r="BP45" s="11"/>
+      <c r="BQ45" s="11"/>
+      <c r="BR45" s="11"/>
+      <c r="BS45" s="11"/>
+      <c r="BT45" s="11"/>
+      <c r="BU45" s="11"/>
+      <c r="BV45" s="11"/>
+      <c r="BW45" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.43" right="0.43" top="0.41" bottom="0.41" header="0.5" footer="0.5"/>

--- a/data/out/test2/001317375_Python版_1pt.xlsx
+++ b/data/out/test2/001317375_Python版_1pt.xlsx
@@ -28,33 +28,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="8.300000000000001"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="6.5"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="6"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <color rgb="00FFFFFF"/>
       <sz val="6.5"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="7"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <color rgb="00FF0000"/>
       <sz val="6.5"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <color rgb="000000FF"/>
       <sz val="6.5"/>
     </font>
@@ -172,88 +172,88 @@
   <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -621,122 +621,122 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:DJ46"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="1.74" defaultRowHeight="18.25" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="1.65" defaultRowHeight="18.25" customHeight="1"/>
   <cols>
-    <col width="1.74" customWidth="1" min="1" max="1"/>
-    <col width="1.74" customWidth="1" min="2" max="2"/>
-    <col width="1.74" customWidth="1" min="3" max="3"/>
-    <col width="1.74" customWidth="1" min="4" max="4"/>
-    <col width="1.74" customWidth="1" min="5" max="5"/>
-    <col width="1.74" customWidth="1" min="6" max="6"/>
-    <col width="1.74" customWidth="1" min="7" max="7"/>
-    <col width="1.74" customWidth="1" min="8" max="8"/>
-    <col width="1.74" customWidth="1" min="9" max="9"/>
-    <col width="1.74" customWidth="1" min="10" max="10"/>
-    <col width="1.74" customWidth="1" min="11" max="11"/>
-    <col width="1.74" customWidth="1" min="12" max="12"/>
-    <col width="1.74" customWidth="1" min="13" max="13"/>
-    <col width="1.74" customWidth="1" min="14" max="14"/>
-    <col width="1.74" customWidth="1" min="15" max="15"/>
-    <col width="1.74" customWidth="1" min="16" max="16"/>
-    <col width="1.74" customWidth="1" min="17" max="17"/>
-    <col width="1.74" customWidth="1" min="18" max="18"/>
-    <col width="1.74" customWidth="1" min="19" max="19"/>
-    <col width="1.74" customWidth="1" min="20" max="20"/>
-    <col width="1.74" customWidth="1" min="21" max="21"/>
-    <col width="1.74" customWidth="1" min="22" max="22"/>
-    <col width="1.74" customWidth="1" min="23" max="23"/>
-    <col width="1.74" customWidth="1" min="24" max="24"/>
-    <col width="1.74" customWidth="1" min="25" max="25"/>
-    <col width="1.74" customWidth="1" min="26" max="26"/>
-    <col width="1.74" customWidth="1" min="27" max="27"/>
-    <col width="1.74" customWidth="1" min="28" max="28"/>
-    <col width="1.74" customWidth="1" min="29" max="29"/>
-    <col width="1.74" customWidth="1" min="30" max="30"/>
-    <col width="1.74" customWidth="1" min="31" max="31"/>
-    <col width="1.74" customWidth="1" min="32" max="32"/>
-    <col width="1.74" customWidth="1" min="33" max="33"/>
-    <col width="1.74" customWidth="1" min="34" max="34"/>
-    <col width="1.74" customWidth="1" min="35" max="35"/>
-    <col width="1.74" customWidth="1" min="36" max="36"/>
-    <col width="1.74" customWidth="1" min="37" max="37"/>
-    <col width="1.74" customWidth="1" min="38" max="38"/>
-    <col width="1.74" customWidth="1" min="39" max="39"/>
-    <col width="1.74" customWidth="1" min="40" max="40"/>
-    <col width="1.74" customWidth="1" min="41" max="41"/>
-    <col width="1.74" customWidth="1" min="42" max="42"/>
-    <col width="1.74" customWidth="1" min="43" max="43"/>
-    <col width="1.74" customWidth="1" min="44" max="44"/>
-    <col width="1.74" customWidth="1" min="45" max="45"/>
-    <col width="1.74" customWidth="1" min="46" max="46"/>
-    <col width="1.74" customWidth="1" min="47" max="47"/>
-    <col width="1.74" customWidth="1" min="48" max="48"/>
-    <col width="1.74" customWidth="1" min="49" max="49"/>
-    <col width="1.74" customWidth="1" min="50" max="50"/>
-    <col width="1.74" customWidth="1" min="51" max="51"/>
-    <col width="1.74" customWidth="1" min="52" max="52"/>
-    <col width="1.74" customWidth="1" min="53" max="53"/>
-    <col width="1.74" customWidth="1" min="54" max="54"/>
-    <col width="1.74" customWidth="1" min="55" max="55"/>
-    <col width="1.74" customWidth="1" min="56" max="56"/>
-    <col width="1.74" customWidth="1" min="57" max="57"/>
-    <col width="1.74" customWidth="1" min="58" max="58"/>
-    <col width="1.74" customWidth="1" min="59" max="59"/>
-    <col width="1.74" customWidth="1" min="60" max="60"/>
-    <col width="1.74" customWidth="1" min="61" max="61"/>
-    <col width="1.74" customWidth="1" min="62" max="62"/>
-    <col width="1.74" customWidth="1" min="63" max="63"/>
-    <col width="1.74" customWidth="1" min="64" max="64"/>
-    <col width="1.74" customWidth="1" min="65" max="65"/>
-    <col width="1.74" customWidth="1" min="66" max="66"/>
-    <col width="1.74" customWidth="1" min="67" max="67"/>
-    <col width="1.74" customWidth="1" min="68" max="68"/>
-    <col width="1.74" customWidth="1" min="69" max="69"/>
-    <col width="1.74" customWidth="1" min="70" max="70"/>
-    <col width="1.74" customWidth="1" min="71" max="71"/>
-    <col width="1.74" customWidth="1" min="72" max="72"/>
-    <col width="1.74" customWidth="1" min="73" max="73"/>
-    <col width="1.74" customWidth="1" min="74" max="74"/>
-    <col width="1.74" customWidth="1" min="75" max="75"/>
-    <col width="1.74" customWidth="1" min="76" max="76"/>
-    <col width="1.74" customWidth="1" min="77" max="77"/>
-    <col width="1.74" customWidth="1" min="78" max="78"/>
-    <col width="1.74" customWidth="1" min="79" max="79"/>
-    <col width="1.74" customWidth="1" min="80" max="80"/>
-    <col width="1.74" customWidth="1" min="81" max="81"/>
-    <col width="1.74" customWidth="1" min="82" max="82"/>
-    <col width="1.74" customWidth="1" min="83" max="83"/>
-    <col width="1.74" customWidth="1" min="84" max="84"/>
-    <col width="1.74" customWidth="1" min="85" max="85"/>
-    <col width="1.74" customWidth="1" min="86" max="86"/>
-    <col width="1.74" customWidth="1" min="87" max="87"/>
-    <col width="1.74" customWidth="1" min="88" max="88"/>
-    <col width="1.74" customWidth="1" min="89" max="89"/>
-    <col width="1.74" customWidth="1" min="90" max="90"/>
-    <col width="1.74" customWidth="1" min="91" max="91"/>
-    <col width="1.74" customWidth="1" min="92" max="92"/>
-    <col width="1.74" customWidth="1" min="93" max="93"/>
-    <col width="1.74" customWidth="1" min="94" max="94"/>
-    <col width="1.74" customWidth="1" min="95" max="95"/>
-    <col width="1.74" customWidth="1" min="96" max="96"/>
-    <col width="1.74" customWidth="1" min="97" max="97"/>
-    <col width="1.74" customWidth="1" min="98" max="98"/>
-    <col width="1.74" customWidth="1" min="99" max="99"/>
-    <col width="1.74" customWidth="1" min="100" max="100"/>
-    <col width="1.74" customWidth="1" min="101" max="101"/>
-    <col width="1.74" customWidth="1" min="102" max="102"/>
-    <col width="1.74" customWidth="1" min="103" max="103"/>
-    <col width="1.74" customWidth="1" min="104" max="104"/>
-    <col width="1.74" customWidth="1" min="105" max="105"/>
-    <col width="1.74" customWidth="1" min="106" max="106"/>
-    <col width="1.74" customWidth="1" min="107" max="107"/>
-    <col width="1.74" customWidth="1" min="108" max="108"/>
-    <col width="1.74" customWidth="1" min="109" max="109"/>
-    <col width="1.74" customWidth="1" min="110" max="110"/>
-    <col width="1.74" customWidth="1" min="111" max="111"/>
-    <col width="1.74" customWidth="1" min="112" max="112"/>
-    <col width="1.74" customWidth="1" min="113" max="113"/>
-    <col width="1.74" customWidth="1" min="114" max="114"/>
+    <col width="1.65" customWidth="1" min="1" max="1"/>
+    <col width="1.65" customWidth="1" min="2" max="2"/>
+    <col width="1.65" customWidth="1" min="3" max="3"/>
+    <col width="1.65" customWidth="1" min="4" max="4"/>
+    <col width="1.65" customWidth="1" min="5" max="5"/>
+    <col width="1.65" customWidth="1" min="6" max="6"/>
+    <col width="1.65" customWidth="1" min="7" max="7"/>
+    <col width="1.65" customWidth="1" min="8" max="8"/>
+    <col width="1.65" customWidth="1" min="9" max="9"/>
+    <col width="1.65" customWidth="1" min="10" max="10"/>
+    <col width="1.65" customWidth="1" min="11" max="11"/>
+    <col width="1.65" customWidth="1" min="12" max="12"/>
+    <col width="1.65" customWidth="1" min="13" max="13"/>
+    <col width="1.65" customWidth="1" min="14" max="14"/>
+    <col width="1.65" customWidth="1" min="15" max="15"/>
+    <col width="1.65" customWidth="1" min="16" max="16"/>
+    <col width="1.65" customWidth="1" min="17" max="17"/>
+    <col width="1.65" customWidth="1" min="18" max="18"/>
+    <col width="1.65" customWidth="1" min="19" max="19"/>
+    <col width="1.65" customWidth="1" min="20" max="20"/>
+    <col width="1.65" customWidth="1" min="21" max="21"/>
+    <col width="1.65" customWidth="1" min="22" max="22"/>
+    <col width="1.65" customWidth="1" min="23" max="23"/>
+    <col width="1.65" customWidth="1" min="24" max="24"/>
+    <col width="1.65" customWidth="1" min="25" max="25"/>
+    <col width="1.65" customWidth="1" min="26" max="26"/>
+    <col width="1.65" customWidth="1" min="27" max="27"/>
+    <col width="1.65" customWidth="1" min="28" max="28"/>
+    <col width="1.65" customWidth="1" min="29" max="29"/>
+    <col width="1.65" customWidth="1" min="30" max="30"/>
+    <col width="1.65" customWidth="1" min="31" max="31"/>
+    <col width="1.65" customWidth="1" min="32" max="32"/>
+    <col width="1.65" customWidth="1" min="33" max="33"/>
+    <col width="1.65" customWidth="1" min="34" max="34"/>
+    <col width="1.65" customWidth="1" min="35" max="35"/>
+    <col width="1.65" customWidth="1" min="36" max="36"/>
+    <col width="1.65" customWidth="1" min="37" max="37"/>
+    <col width="1.65" customWidth="1" min="38" max="38"/>
+    <col width="1.65" customWidth="1" min="39" max="39"/>
+    <col width="1.65" customWidth="1" min="40" max="40"/>
+    <col width="1.65" customWidth="1" min="41" max="41"/>
+    <col width="1.65" customWidth="1" min="42" max="42"/>
+    <col width="1.65" customWidth="1" min="43" max="43"/>
+    <col width="1.65" customWidth="1" min="44" max="44"/>
+    <col width="1.65" customWidth="1" min="45" max="45"/>
+    <col width="1.65" customWidth="1" min="46" max="46"/>
+    <col width="1.65" customWidth="1" min="47" max="47"/>
+    <col width="1.65" customWidth="1" min="48" max="48"/>
+    <col width="1.65" customWidth="1" min="49" max="49"/>
+    <col width="1.65" customWidth="1" min="50" max="50"/>
+    <col width="1.65" customWidth="1" min="51" max="51"/>
+    <col width="1.65" customWidth="1" min="52" max="52"/>
+    <col width="1.65" customWidth="1" min="53" max="53"/>
+    <col width="1.65" customWidth="1" min="54" max="54"/>
+    <col width="1.65" customWidth="1" min="55" max="55"/>
+    <col width="1.65" customWidth="1" min="56" max="56"/>
+    <col width="1.65" customWidth="1" min="57" max="57"/>
+    <col width="1.65" customWidth="1" min="58" max="58"/>
+    <col width="1.65" customWidth="1" min="59" max="59"/>
+    <col width="1.65" customWidth="1" min="60" max="60"/>
+    <col width="1.65" customWidth="1" min="61" max="61"/>
+    <col width="1.65" customWidth="1" min="62" max="62"/>
+    <col width="1.65" customWidth="1" min="63" max="63"/>
+    <col width="1.65" customWidth="1" min="64" max="64"/>
+    <col width="1.65" customWidth="1" min="65" max="65"/>
+    <col width="1.65" customWidth="1" min="66" max="66"/>
+    <col width="1.65" customWidth="1" min="67" max="67"/>
+    <col width="1.65" customWidth="1" min="68" max="68"/>
+    <col width="1.65" customWidth="1" min="69" max="69"/>
+    <col width="1.65" customWidth="1" min="70" max="70"/>
+    <col width="1.65" customWidth="1" min="71" max="71"/>
+    <col width="1.65" customWidth="1" min="72" max="72"/>
+    <col width="1.65" customWidth="1" min="73" max="73"/>
+    <col width="1.65" customWidth="1" min="74" max="74"/>
+    <col width="1.65" customWidth="1" min="75" max="75"/>
+    <col width="1.65" customWidth="1" min="76" max="76"/>
+    <col width="1.65" customWidth="1" min="77" max="77"/>
+    <col width="1.65" customWidth="1" min="78" max="78"/>
+    <col width="1.65" customWidth="1" min="79" max="79"/>
+    <col width="1.65" customWidth="1" min="80" max="80"/>
+    <col width="1.65" customWidth="1" min="81" max="81"/>
+    <col width="1.65" customWidth="1" min="82" max="82"/>
+    <col width="1.65" customWidth="1" min="83" max="83"/>
+    <col width="1.65" customWidth="1" min="84" max="84"/>
+    <col width="1.65" customWidth="1" min="85" max="85"/>
+    <col width="1.65" customWidth="1" min="86" max="86"/>
+    <col width="1.65" customWidth="1" min="87" max="87"/>
+    <col width="1.65" customWidth="1" min="88" max="88"/>
+    <col width="1.65" customWidth="1" min="89" max="89"/>
+    <col width="1.65" customWidth="1" min="90" max="90"/>
+    <col width="1.65" customWidth="1" min="91" max="91"/>
+    <col width="1.65" customWidth="1" min="92" max="92"/>
+    <col width="1.65" customWidth="1" min="93" max="93"/>
+    <col width="1.65" customWidth="1" min="94" max="94"/>
+    <col width="1.65" customWidth="1" min="95" max="95"/>
+    <col width="1.65" customWidth="1" min="96" max="96"/>
+    <col width="1.65" customWidth="1" min="97" max="97"/>
+    <col width="1.65" customWidth="1" min="98" max="98"/>
+    <col width="1.65" customWidth="1" min="99" max="99"/>
+    <col width="1.65" customWidth="1" min="100" max="100"/>
+    <col width="1.65" customWidth="1" min="101" max="101"/>
+    <col width="1.65" customWidth="1" min="102" max="102"/>
+    <col width="1.65" customWidth="1" min="103" max="103"/>
+    <col width="1.65" customWidth="1" min="104" max="104"/>
+    <col width="1.65" customWidth="1" min="105" max="105"/>
+    <col width="1.65" customWidth="1" min="106" max="106"/>
+    <col width="1.65" customWidth="1" min="107" max="107"/>
+    <col width="1.65" customWidth="1" min="108" max="108"/>
+    <col width="1.65" customWidth="1" min="109" max="109"/>
+    <col width="1.65" customWidth="1" min="110" max="110"/>
+    <col width="1.65" customWidth="1" min="111" max="111"/>
+    <col width="1.65" customWidth="1" min="112" max="112"/>
+    <col width="1.65" customWidth="1" min="113" max="113"/>
+    <col width="1.65" customWidth="1" min="114" max="114"/>
   </cols>
   <sheetData>
     <row r="2">
